--- a/ter/dist/20261028_泰瑞達個股模型_v0.2.xlsx
+++ b/ter/dist/20261028_泰瑞達個股模型_v0.2.xlsx
@@ -7679,7 +7679,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -7698,7 +7698,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7840,7 +7840,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -7859,7 +7859,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7961,7 +7961,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -7980,7 +7980,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8082,7 +8082,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -8101,7 +8101,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8203,7 +8203,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -8222,7 +8222,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8324,7 +8324,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -8343,7 +8343,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/ter/dist/20261028_泰瑞達個股模型_v0.2.xlsx
+++ b/ter/dist/20261028_泰瑞達個股模型_v0.2.xlsx
@@ -36522,7 +36522,7 @@
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="str">
         <f aca="false">"重點觀察 1：目標價 US$"&amp;TEXT(Val!$B$126,"#,##0.00")&amp;"（DCF "&amp;TEXT(Val!$B$111,"#,##0.00")&amp;"、Comparable（相對倍數調整後）"&amp;TEXT(tp_comp_adj,"#,##0.00")&amp;"；DCF 權重 "&amp;TEXT(tp_w_dcf,"0%")&amp;"），比現價 "&amp;TEXT(px,"#,##0.00")&amp;"（2026-10-23）"&amp;IF(Val!$B$129&gt;=0,"高 "&amp;TEXT(Val!$B$129,"0.0%"),"低 "&amp;TEXT(-Val!$B$129,"0.0%"))&amp;"，級距 "&amp;Val!$B$137&amp;"、投資建議 "&amp;Val!$B$138&amp;"。相對倍數調整係數 "&amp;TEXT(rm_factor,"0.00")&amp;"（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 "&amp;TEXT((tp_w_dcf*Val!$B$111+(1-tp_w_dcf)*Val!$B$122)/px-1,"+0.0%;−0.0%")&amp;"；Comparable 單獨（市場主流同業法、未調整）為 "&amp;TEXT(Val!$B$130,"+0.0%;−0.0%")&amp;"。"&amp;"以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：兩法分歧大：同業（Advantest、KLA、Cohu、FormFactor、應用材料）前瞻 P/E 中位數 28.2 倍 × 12 個月後前瞻 EPS 14.38 得 405，DCF 只有 219（比現價低 29.0%）；本模型前瞻 EPS 比共識 FY2027 EPS 11.30 高 27.3%（期間約早一年），共識目標"&amp;"價 446.47 隱含 39.5 倍。"</f>
-        <v>重點觀察 1：目標價 US$356.37（DCF 219.30、Comparable（相對倍數調整後）493.44；DCF 權重 50%），比現價 308.85（2026-10-23）高 15.4%，級距 0%–25%、投資建議 中立。相對倍數調整係數 1.22（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 +1.1%；Comparable 單獨（市場主流同業法、未調整）為 +31.2%。以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：兩法分歧大：同業（Advantest、KLA、Cohu、FormFactor、應用材料）前瞻 P/E 中位數 28.2 倍 × 12 個月後前瞻 EPS 14.38 得 405，DCF 只有 219（比現價低 29.0%）；本模型前瞻 EPS 比共識 FY2027 EPS 11.30 高 27.3%（期間約早一年），共識目標價 446.47 隱含 39.5 倍。</v>
+        <v>重點觀察 1：目標價 US$354.25（DCF 218.29、Comparable（相對倍數調整後）490.22；DCF 權重 50%），比現價 308.85（2026-10-23）高 14.7%，級距 0%–25%、投資建議 中立。相對倍數調整係數 1.22（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 +0.5%；Comparable 單獨（市場主流同業法、未調整）為 +30.3%。以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：兩法分歧大：同業（Advantest、KLA、Cohu、FormFactor、應用材料）前瞻 P/E 中位數 28.2 倍 × 12 個月後前瞻 EPS 14.38 得 405，DCF 只有 219（比現價低 29.0%）；本模型前瞻 EPS 比共識 FY2027 EPS 11.30 高 27.3%（期間約早一年），共識目標價 446.47 隱含 39.5 倍。</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36969,7 +36969,7 @@
         <v>31</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>41</v>
@@ -36992,7 +36992,7 @@
         <v>31</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>41</v>
@@ -37015,7 +37015,7 @@
         <v>31</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>41</v>
@@ -37061,7 +37061,7 @@
         <v>31</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>41</v>
@@ -37084,7 +37084,7 @@
         <v>31</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>4.8492815003257</v>
+        <v>4.73784910426688</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>41</v>
@@ -37107,7 +37107,7 @@
         <v>31</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>5.89583446540914</v>
+        <v>5.78997368915325</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>41</v>
@@ -37153,7 +37153,7 @@
         <v>31</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>41</v>
@@ -37176,7 +37176,7 @@
         <v>31</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>3.72997394923451</v>
+        <v>3.64082803238745</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>41</v>
@@ -37199,7 +37199,7 @@
         <v>31</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>4.40250457885175</v>
+        <v>4.31335866200469</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>41</v>
@@ -37659,7 +37659,7 @@
         <v>31</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="G50" s="8" t="s">
         <v>41</v>
@@ -37774,7 +37774,7 @@
         <v>31</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>41</v>
@@ -37889,7 +37889,7 @@
         <v>31</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="G60" s="8" t="s">
         <v>41</v>
@@ -40717,15 +40717,15 @@
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G6" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40828,19 +40828,19 @@
       </c>
       <c r="D10" s="11" t="n">
         <f aca="false">(ms_A_2026+mm_A_2026)/wfe_A_2026</f>
-        <v>0.0880523802786935</v>
+        <v>0.0859133291658267</v>
       </c>
       <c r="E10" s="11" t="n">
         <f aca="false">(ms_A_2027+mm_A_2027)/wfe_A_2027</f>
-        <v>0.100655189777327</v>
+        <v>0.100077207336046</v>
       </c>
       <c r="F10" s="11" t="n">
         <f aca="false">(ms_A_2028+mm_A_2028)/wfe_A_2028</f>
-        <v>0.103725344659339</v>
+        <v>0.103150082185545</v>
       </c>
       <c r="G10" s="11" t="n">
         <f aca="false">(ms_A_2029+mm_A_2029)/wfe_A_2029</f>
-        <v>0.111696683927443</v>
+        <v>0.111131517724348</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>467</v>
@@ -40896,15 +40896,15 @@
       </c>
       <c r="E14" s="18" t="n">
         <f aca="false">mm_B_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F14" s="18" t="n">
         <f aca="false">mm_B_2028</f>
-        <v>4.8492815003257</v>
+        <v>4.73784910426688</v>
       </c>
       <c r="G14" s="18" t="n">
         <f aca="false">mm_B_2029</f>
-        <v>5.89583446540914</v>
+        <v>5.78997368915325</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41007,19 +41007,19 @@
       </c>
       <c r="D18" s="11" t="n">
         <f aca="false">(ms_B_2026+mm_B_2026)/wfe_B_2026</f>
-        <v>0.0880523802786935</v>
+        <v>0.0859133291658267</v>
       </c>
       <c r="E18" s="11" t="n">
         <f aca="false">(ms_B_2027+mm_B_2027)/wfe_B_2027</f>
-        <v>0.100655189777327</v>
+        <v>0.100077207336046</v>
       </c>
       <c r="F18" s="11" t="n">
         <f aca="false">(ms_B_2028+mm_B_2028)/wfe_B_2028</f>
-        <v>0.10175967564377</v>
+        <v>0.101181693202489</v>
       </c>
       <c r="G18" s="11" t="n">
         <f aca="false">(ms_B_2029+mm_B_2029)/wfe_B_2029</f>
-        <v>0.12542400825863</v>
+        <v>0.124846025817348</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>467</v>
@@ -41075,15 +41075,15 @@
       </c>
       <c r="E22" s="18" t="n">
         <f aca="false">mm_C_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F22" s="18" t="n">
         <f aca="false">mm_C_2028</f>
-        <v>3.72997394923451</v>
+        <v>3.64082803238745</v>
       </c>
       <c r="G22" s="18" t="n">
         <f aca="false">mm_C_2029</f>
-        <v>4.40250457885175</v>
+        <v>4.31335866200469</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41186,19 +41186,19 @@
       </c>
       <c r="D26" s="11" t="n">
         <f aca="false">(ms_C_2026+mm_C_2026)/wfe_C_2026</f>
-        <v>0.0880523802786935</v>
+        <v>0.0859133291658267</v>
       </c>
       <c r="E26" s="11" t="n">
         <f aca="false">(ms_C_2027+mm_C_2027)/wfe_C_2027</f>
-        <v>0.100655189777327</v>
+        <v>0.100077207336046</v>
       </c>
       <c r="F26" s="11" t="n">
         <f aca="false">(ms_C_2028+mm_C_2028)/wfe_C_2028</f>
-        <v>0.103541308553797</v>
+        <v>0.102963326112516</v>
       </c>
       <c r="G26" s="11" t="n">
         <f aca="false">(ms_C_2029+mm_C_2029)/wfe_C_2029</f>
-        <v>0.115919323967898</v>
+        <v>0.115341341526616</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>467</v>
@@ -41284,15 +41284,15 @@
       </c>
       <c r="E5" s="20" t="n">
         <f aca="false">E61</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="F5" s="20" t="n">
         <f aca="false">F61</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G5" s="20" t="n">
         <f aca="false">G61</f>
-        <v>9060.66378455651</v>
+        <v>9019.68544869644</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41340,15 +41340,15 @@
       </c>
       <c r="E7" s="20" t="n">
         <f aca="false">E51</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F7" s="20" t="n">
         <f aca="false">F51</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G7" s="20" t="n">
         <f aca="false">G51</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41396,15 +41396,15 @@
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">E71</f>
-        <v>0.600140940959489</v>
+        <v>0.601175024106483</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">F71</f>
-        <v>0.595296697214342</v>
+        <v>0.596278377073082</v>
       </c>
       <c r="G9" s="11" t="n">
         <f aca="false">G71</f>
-        <v>0.591716820200892</v>
+        <v>0.592600095867661</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41424,15 +41424,15 @@
       </c>
       <c r="E10" s="20" t="n">
         <f aca="false">E63</f>
-        <v>2514.52879496834</v>
+        <v>2497.49251627273</v>
       </c>
       <c r="F10" s="20" t="n">
         <f aca="false">F63</f>
-        <v>3006.74059733587</v>
+        <v>2987.68839621597</v>
       </c>
       <c r="G10" s="20" t="n">
         <f aca="false">G63</f>
-        <v>3502.04562107711</v>
+        <v>3482.26717188148</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41452,15 +41452,15 @@
       </c>
       <c r="E11" s="11" t="n">
         <f aca="false">E64</f>
-        <v>0.361336390848749</v>
+        <v>0.36071790160331</v>
       </c>
       <c r="F11" s="11" t="n">
         <f aca="false">F64</f>
-        <v>0.375796907877763</v>
+        <v>0.375267092151479</v>
       </c>
       <c r="G11" s="11" t="n">
         <f aca="false">G64</f>
-        <v>0.386510933894953</v>
+        <v>0.386074125498994</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41480,15 +41480,15 @@
       </c>
       <c r="E12" s="20" t="n">
         <f aca="false">E67</f>
-        <v>2144.87574133212</v>
+        <v>2130.2544811385</v>
       </c>
       <c r="F12" s="20" t="n">
         <f aca="false">F67</f>
-        <v>2567.31288041451</v>
+        <v>2550.96146970961</v>
       </c>
       <c r="G12" s="20" t="n">
         <f aca="false">G67</f>
-        <v>2992.40475386405</v>
+        <v>2975.43004611933</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41508,15 +41508,15 @@
       </c>
       <c r="E13" s="18" t="n">
         <f aca="false">E69</f>
-        <v>13.7383712927123</v>
+        <v>13.6447191069765</v>
       </c>
       <c r="F13" s="18" t="n">
         <f aca="false">F69</f>
-        <v>16.6102709642527</v>
+        <v>16.5044788870469</v>
       </c>
       <c r="G13" s="18" t="n">
         <f aca="false">G69</f>
-        <v>19.5561364528184</v>
+        <v>19.4452023619426</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41541,15 +41541,15 @@
       </c>
       <c r="E16" s="20" t="n">
         <f aca="false">E91</f>
-        <v>6947.14404523867</v>
+        <v>6911.84712467179</v>
       </c>
       <c r="F16" s="20" t="n">
         <f aca="false">F91</f>
-        <v>7081.7701876497</v>
+        <v>7046.47326708282</v>
       </c>
       <c r="G16" s="20" t="n">
         <f aca="false">G91</f>
-        <v>8205.98597224243</v>
+        <v>8172.45389770389</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41597,15 +41597,15 @@
       </c>
       <c r="E18" s="20" t="n">
         <f aca="false">E81</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F18" s="20" t="n">
         <f aca="false">F81</f>
-        <v>1536.04077429226</v>
+        <v>1500.74385372538</v>
       </c>
       <c r="G18" s="20" t="n">
         <f aca="false">G81</f>
-        <v>1867.54308586494</v>
+        <v>1834.01101132641</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41653,15 +41653,15 @@
       </c>
       <c r="E20" s="11" t="n">
         <f aca="false">E101</f>
-        <v>0.600486206837982</v>
+        <v>0.601523822319888</v>
       </c>
       <c r="F20" s="11" t="n">
         <f aca="false">F101</f>
-        <v>0.588285216577344</v>
+        <v>0.589241891206701</v>
       </c>
       <c r="G20" s="11" t="n">
         <f aca="false">G101</f>
-        <v>0.58786265322457</v>
+        <v>0.588644542452108</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41681,15 +41681,15 @@
       </c>
       <c r="E21" s="20" t="n">
         <f aca="false">E93</f>
-        <v>2508.82133675476</v>
+        <v>2491.78505805915</v>
       </c>
       <c r="F21" s="20" t="n">
         <f aca="false">F93</f>
-        <v>2563.08203708442</v>
+        <v>2546.04575838881</v>
       </c>
       <c r="G21" s="20" t="n">
         <f aca="false">G93</f>
-        <v>3089.53004828231</v>
+        <v>3073.34558352147</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41709,15 +41709,15 @@
       </c>
       <c r="E22" s="11" t="n">
         <f aca="false">E94</f>
-        <v>0.361129885952807</v>
+        <v>0.3605092840038</v>
       </c>
       <c r="F22" s="11" t="n">
         <f aca="false">F94</f>
-        <v>0.361926745597355</v>
+        <v>0.361321992135061</v>
       </c>
       <c r="G22" s="11" t="n">
         <f aca="false">G94</f>
-        <v>0.376497115487761</v>
+        <v>0.376061538185606</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41737,15 +41737,15 @@
       </c>
       <c r="E23" s="20" t="n">
         <f aca="false">E97</f>
-        <v>2139.97735753153</v>
+        <v>2125.35609733791</v>
       </c>
       <c r="F23" s="20" t="n">
         <f aca="false">F97</f>
-        <v>2186.54620228823</v>
+        <v>2171.92494209461</v>
       </c>
       <c r="G23" s="20" t="n">
         <f aca="false">G97</f>
-        <v>2638.36631439515</v>
+        <v>2624.47611721122</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41765,15 +41765,15 @@
       </c>
       <c r="E24" s="18" t="n">
         <f aca="false">E99</f>
-        <v>13.70699613466</v>
+        <v>13.6133439489243</v>
       </c>
       <c r="F24" s="18" t="n">
         <f aca="false">F99</f>
-        <v>14.1467466520876</v>
+        <v>14.0521484846777</v>
       </c>
       <c r="G24" s="18" t="n">
         <f aca="false">G99</f>
-        <v>17.2424039863611</v>
+        <v>17.1516279671294</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41798,15 +41798,15 @@
       </c>
       <c r="E27" s="20" t="n">
         <f aca="false">E121</f>
-        <v>6935.31894523867</v>
+        <v>6900.02202467179</v>
       </c>
       <c r="F27" s="20" t="n">
         <f aca="false">F121</f>
-        <v>6522.53289805538</v>
+        <v>6494.29536160187</v>
       </c>
       <c r="G27" s="20" t="n">
         <f aca="false">G121</f>
-        <v>7915.26566715332</v>
+        <v>7887.02813069982</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41854,15 +41854,15 @@
       </c>
       <c r="E29" s="20" t="n">
         <f aca="false">E111</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F29" s="20" t="n">
         <f aca="false">F111</f>
-        <v>1181.49298461789</v>
+        <v>1153.25544816439</v>
       </c>
       <c r="G29" s="20" t="n">
         <f aca="false">G111</f>
-        <v>1394.52134128952</v>
+        <v>1366.28380483602</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41910,15 +41910,15 @@
       </c>
       <c r="E31" s="11" t="n">
         <f aca="false">E131</f>
-        <v>0.600832650111076</v>
+        <v>0.601873816058102</v>
       </c>
       <c r="F31" s="11" t="n">
         <f aca="false">F131</f>
-        <v>0.588231824899232</v>
+        <v>0.589105486037201</v>
       </c>
       <c r="G31" s="11" t="n">
         <f aca="false">G131</f>
-        <v>0.585996256851265</v>
+        <v>0.586743440937406</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41938,15 +41938,15 @@
       </c>
       <c r="E32" s="20" t="n">
         <f aca="false">E123</f>
-        <v>2503.11387854118</v>
+        <v>2486.07759984557</v>
       </c>
       <c r="F32" s="20" t="n">
         <f aca="false">F123</f>
-        <v>2232.79573689892</v>
+        <v>2219.44908930696</v>
       </c>
       <c r="G32" s="20" t="n">
         <f aca="false">G123</f>
-        <v>2801.59523020703</v>
+        <v>2788.53095797961</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41966,15 +41966,15 @@
       </c>
       <c r="E33" s="11" t="n">
         <f aca="false">E124</f>
-        <v>0.360922676852469</v>
+        <v>0.360299951356144</v>
       </c>
       <c r="F33" s="11" t="n">
         <f aca="false">F124</f>
-        <v>0.342320348827156</v>
+        <v>0.341753641577447</v>
       </c>
       <c r="G33" s="11" t="n">
         <f aca="false">G124</f>
-        <v>0.353948350948353</v>
+        <v>0.353559149500864</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41994,15 +41994,15 @@
       </c>
       <c r="E34" s="20" t="n">
         <f aca="false">E127</f>
-        <v>2135.07897373094</v>
+        <v>2120.45771353732</v>
       </c>
       <c r="F34" s="20" t="n">
         <f aca="false">F127</f>
-        <v>1903.08042788509</v>
+        <v>1891.62576629842</v>
       </c>
       <c r="G34" s="20" t="n">
         <f aca="false">G127</f>
-        <v>2391.24838629008</v>
+        <v>2380.03607127163</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42022,15 +42022,15 @@
       </c>
       <c r="E35" s="18" t="n">
         <f aca="false">E129</f>
-        <v>13.6756209766078</v>
+        <v>13.5819687908721</v>
       </c>
       <c r="F35" s="18" t="n">
         <f aca="false">F129</f>
-        <v>12.3127499632354</v>
+        <v>12.2386393886303</v>
       </c>
       <c r="G35" s="18" t="n">
         <f aca="false">G129</f>
-        <v>15.6274246237865</v>
+        <v>15.5541492548145</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42118,15 +42118,15 @@
       </c>
       <c r="E47" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F47" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G47" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42236,15 +42236,15 @@
       </c>
       <c r="E51" s="9" t="n">
         <f aca="false">E47*1000*E50</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F51" s="9" t="n">
         <f aca="false">F47*1000*F50</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G51" s="9" t="n">
         <f aca="false">G47*1000*G50</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42295,15 +42295,15 @@
       </c>
       <c r="E53" s="9" t="n">
         <f aca="false">E49+E51+E52</f>
-        <v>6091.59354523868</v>
+        <v>6056.29662467179</v>
       </c>
       <c r="F53" s="9" t="n">
         <f aca="false">F49+F51+F52</f>
-        <v>7055.37307091378</v>
+        <v>7015.89942519757</v>
       </c>
       <c r="G53" s="9" t="n">
         <f aca="false">G49+G51+G52</f>
-        <v>8029.69998551651</v>
+        <v>7988.72164965644</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42351,15 +42351,15 @@
       </c>
       <c r="E55" s="9" t="n">
         <f aca="false">E53+E54</f>
-        <v>6517.29714523868</v>
+        <v>6482.00022467179</v>
       </c>
       <c r="F55" s="9" t="n">
         <f aca="false">F53+F54</f>
-        <v>7515.13295891378</v>
+        <v>7475.65931319757</v>
       </c>
       <c r="G55" s="9" t="n">
         <f aca="false">G53+G54</f>
-        <v>8526.24066455651</v>
+        <v>8485.26232869644</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42379,15 +42379,15 @@
       </c>
       <c r="E56" s="9" t="n">
         <f aca="false">t_inc*E55-t_fix+0*E55</f>
-        <v>2516.09535496834</v>
+        <v>2499.05907627273</v>
       </c>
       <c r="F56" s="9" t="n">
         <f aca="false">t_inc*F55-t_fix+0*F55</f>
-        <v>2997.70702933587</v>
+        <v>2978.65482821597</v>
       </c>
       <c r="G56" s="9" t="n">
         <f aca="false">t_inc*G55-t_fix+0*G55</f>
-        <v>3485.72446507711</v>
+        <v>3465.94601588148</v>
       </c>
       <c r="H56" s="4" t="s">
         <v>500</v>
@@ -42410,15 +42410,15 @@
       </c>
       <c r="E57" s="11" t="n">
         <f aca="false">E56/E55</f>
-        <v>0.386064237811609</v>
+        <v>0.385538258200117</v>
       </c>
       <c r="F57" s="11" t="n">
         <f aca="false">F56/F55</f>
-        <v>0.398889420283677</v>
+        <v>0.398447107261488</v>
       </c>
       <c r="G57" s="11" t="n">
         <f aca="false">G56/G55</f>
-        <v>0.408823138146597</v>
+        <v>0.408466571995063</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42522,15 +42522,15 @@
       </c>
       <c r="E61" s="9" t="n">
         <f aca="false">E55+E58</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="F61" s="9" t="n">
         <f aca="false">F55+F58</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G61" s="9" t="n">
         <f aca="false">G55+G58</f>
-        <v>9060.66378455651</v>
+        <v>9019.68544869644</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42569,15 +42569,15 @@
       </c>
       <c r="E63" s="9" t="n">
         <f aca="false">E56+E59+E60</f>
-        <v>2514.52879496834</v>
+        <v>2497.49251627273</v>
       </c>
       <c r="F63" s="9" t="n">
         <f aca="false">F56+F59+F60</f>
-        <v>3006.74059733587</v>
+        <v>2987.68839621597</v>
       </c>
       <c r="G63" s="9" t="n">
         <f aca="false">G56+G59+G60</f>
-        <v>3502.04562107711</v>
+        <v>3482.26717188148</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42597,15 +42597,15 @@
       </c>
       <c r="E64" s="11" t="n">
         <f aca="false">E63/E61</f>
-        <v>0.361336390848749</v>
+        <v>0.36071790160331</v>
       </c>
       <c r="F64" s="11" t="n">
         <f aca="false">F63/F61</f>
-        <v>0.375796907877763</v>
+        <v>0.375267092151479</v>
       </c>
       <c r="G64" s="11" t="n">
         <f aca="false">G63/G61</f>
-        <v>0.386510933894953</v>
+        <v>0.386074125498994</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42625,15 +42625,15 @@
       </c>
       <c r="E65" s="9" t="n">
         <f aca="false">E63*etr</f>
-        <v>356.453053636225</v>
+        <v>354.038035134229</v>
       </c>
       <c r="F65" s="9" t="n">
         <f aca="false">F63*etr</f>
-        <v>426.227716921361</v>
+        <v>423.526926506366</v>
       </c>
       <c r="G65" s="9" t="n">
         <f aca="false">G63*etr</f>
-        <v>496.440867213065</v>
+        <v>493.63712576215</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42681,15 +42681,15 @@
       </c>
       <c r="E67" s="9" t="n">
         <f aca="false">E63-E65+E66</f>
-        <v>2144.87574133212</v>
+        <v>2130.2544811385</v>
       </c>
       <c r="F67" s="9" t="n">
         <f aca="false">F63-F65+F66</f>
-        <v>2567.31288041451</v>
+        <v>2550.96146970961</v>
       </c>
       <c r="G67" s="9" t="n">
         <f aca="false">G63-G65+G66</f>
-        <v>2992.40475386405</v>
+        <v>2975.43004611933</v>
       </c>
       <c r="H67" s="8" t="s">
         <v>505</v>
@@ -42740,15 +42740,15 @@
       </c>
       <c r="E69" s="18" t="n">
         <f aca="false">E67/E68</f>
-        <v>13.7383712927123</v>
+        <v>13.6447191069765</v>
       </c>
       <c r="F69" s="18" t="n">
         <f aca="false">F67/F68</f>
-        <v>16.6102709642527</v>
+        <v>16.5044788870469</v>
       </c>
       <c r="G69" s="18" t="n">
         <f aca="false">G67/G68</f>
-        <v>19.5561364528184</v>
+        <v>19.4452023619426</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42768,15 +42768,15 @@
       </c>
       <c r="E70" s="11" t="n">
         <f aca="false">E49/E61</f>
-        <v>0.654305138730523</v>
+        <v>0.657640790066815</v>
       </c>
       <c r="F70" s="11" t="n">
         <f aca="false">F49/F61</f>
-        <v>0.638679017979199</v>
+        <v>0.641845631555813</v>
       </c>
       <c r="G70" s="11" t="n">
         <f aca="false">G49/G61</f>
-        <v>0.627131376400865</v>
+        <v>0.629980566687679</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42796,15 +42796,15 @@
       </c>
       <c r="E71" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E70-D70)</f>
-        <v>0.600140940959489</v>
+        <v>0.601175024106483</v>
       </c>
       <c r="F71" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F70-D70)</f>
-        <v>0.595296697214342</v>
+        <v>0.596278377073082</v>
       </c>
       <c r="G71" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G70-D70)</f>
-        <v>0.591716820200892</v>
+        <v>0.592600095867661</v>
       </c>
       <c r="H71" s="8" t="s">
         <v>509</v>
@@ -42886,15 +42886,15 @@
       </c>
       <c r="E77" s="18" t="n">
         <f aca="false">mm_B_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F77" s="18" t="n">
         <f aca="false">mm_B_2028</f>
-        <v>4.8492815003257</v>
+        <v>4.73784910426688</v>
       </c>
       <c r="G77" s="18" t="n">
         <f aca="false">mm_B_2029</f>
-        <v>5.89583446540914</v>
+        <v>5.78997368915325</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43004,15 +43004,15 @@
       </c>
       <c r="E81" s="9" t="n">
         <f aca="false">E77*1000*E80</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F81" s="9" t="n">
         <f aca="false">F77*1000*F80</f>
-        <v>1536.04077429226</v>
+        <v>1500.74385372538</v>
       </c>
       <c r="G81" s="9" t="n">
         <f aca="false">G77*1000*G80</f>
-        <v>1867.54308586494</v>
+        <v>1834.01101132641</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43063,15 +43063,15 @@
       </c>
       <c r="E83" s="9" t="n">
         <f aca="false">E79+E81+E82</f>
-        <v>6091.59354523868</v>
+        <v>6056.29662467179</v>
       </c>
       <c r="F83" s="9" t="n">
         <f aca="false">F79+F81+F82</f>
-        <v>6161.3585626497</v>
+        <v>6126.06164208282</v>
       </c>
       <c r="G83" s="9" t="n">
         <f aca="false">G79+G81+G82</f>
-        <v>7215.26180599243</v>
+        <v>7181.72973145389</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43119,15 +43119,15 @@
       </c>
       <c r="E85" s="9" t="n">
         <f aca="false">E83+E84</f>
-        <v>6505.47204523868</v>
+        <v>6470.17512467179</v>
       </c>
       <c r="F85" s="9" t="n">
         <f aca="false">F83+F84</f>
-        <v>6595.9309876497</v>
+        <v>6560.63406708282</v>
       </c>
       <c r="G85" s="9" t="n">
         <f aca="false">G83+G84</f>
-        <v>7671.56285224243</v>
+        <v>7638.03077770389</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43147,15 +43147,15 @@
       </c>
       <c r="E86" s="9" t="n">
         <f aca="false">t_inc*E85-t_fix+0*E85</f>
-        <v>2510.38789675476</v>
+        <v>2493.35161805915</v>
       </c>
       <c r="F86" s="9" t="n">
         <f aca="false">t_inc*F85-t_fix+0*F85</f>
-        <v>2554.04846908442</v>
+        <v>2537.01219038881</v>
       </c>
       <c r="G86" s="9" t="n">
         <f aca="false">t_inc*G85-t_fix+0*G85</f>
-        <v>3073.20889228231</v>
+        <v>3057.02442752147</v>
       </c>
       <c r="H86" s="4" t="s">
         <v>500</v>
@@ -43178,15 +43178,15 @@
       </c>
       <c r="E87" s="11" t="n">
         <f aca="false">E86/E85</f>
-        <v>0.385888661006868</v>
+        <v>0.385360762269264</v>
       </c>
       <c r="F87" s="11" t="n">
         <f aca="false">F86/F85</f>
-        <v>0.38721576588152</v>
+        <v>0.38670228585343</v>
       </c>
       <c r="G87" s="11" t="n">
         <f aca="false">G86/G85</f>
-        <v>0.400597499032938</v>
+        <v>0.400237249167051</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43290,15 +43290,15 @@
       </c>
       <c r="E91" s="9" t="n">
         <f aca="false">E85+E88</f>
-        <v>6947.14404523867</v>
+        <v>6911.84712467179</v>
       </c>
       <c r="F91" s="9" t="n">
         <f aca="false">F85+F88</f>
-        <v>7081.7701876497</v>
+        <v>7046.47326708282</v>
       </c>
       <c r="G91" s="9" t="n">
         <f aca="false">G85+G88</f>
-        <v>8205.98597224243</v>
+        <v>8172.45389770389</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43337,15 +43337,15 @@
       </c>
       <c r="E93" s="9" t="n">
         <f aca="false">E86+E89+E90</f>
-        <v>2508.82133675476</v>
+        <v>2491.78505805915</v>
       </c>
       <c r="F93" s="9" t="n">
         <f aca="false">F86+F89+F90</f>
-        <v>2563.08203708442</v>
+        <v>2546.04575838881</v>
       </c>
       <c r="G93" s="9" t="n">
         <f aca="false">G86+G89+G90</f>
-        <v>3089.53004828231</v>
+        <v>3073.34558352147</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43365,15 +43365,15 @@
       </c>
       <c r="E94" s="11" t="n">
         <f aca="false">E93/E91</f>
-        <v>0.361129885952807</v>
+        <v>0.3605092840038</v>
       </c>
       <c r="F94" s="11" t="n">
         <f aca="false">F93/F91</f>
-        <v>0.361926745597355</v>
+        <v>0.361321992135061</v>
       </c>
       <c r="G94" s="11" t="n">
         <f aca="false">G93/G91</f>
-        <v>0.376497115487761</v>
+        <v>0.376061538185606</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43393,15 +43393,15 @@
       </c>
       <c r="E95" s="9" t="n">
         <f aca="false">E93*etr</f>
-        <v>355.643979223237</v>
+        <v>353.228960721241</v>
       </c>
       <c r="F95" s="9" t="n">
         <f aca="false">F93*etr</f>
-        <v>363.335834796198</v>
+        <v>360.920816294202</v>
       </c>
       <c r="G95" s="9" t="n">
         <f aca="false">G93*etr</f>
-        <v>437.963733887154</v>
+        <v>435.669466310259</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43449,15 +43449,15 @@
       </c>
       <c r="E97" s="9" t="n">
         <f aca="false">E93-E95+E96</f>
-        <v>2139.97735753153</v>
+        <v>2125.35609733791</v>
       </c>
       <c r="F97" s="9" t="n">
         <f aca="false">F93-F95+F96</f>
-        <v>2186.54620228823</v>
+        <v>2171.92494209461</v>
       </c>
       <c r="G97" s="9" t="n">
         <f aca="false">G93-G95+G96</f>
-        <v>2638.36631439515</v>
+        <v>2624.47611721122</v>
       </c>
       <c r="H97" s="8" t="s">
         <v>505</v>
@@ -43508,15 +43508,15 @@
       </c>
       <c r="E99" s="18" t="n">
         <f aca="false">E97/E98</f>
-        <v>13.70699613466</v>
+        <v>13.6133439489243</v>
       </c>
       <c r="F99" s="18" t="n">
         <f aca="false">F97/F98</f>
-        <v>14.1467466520876</v>
+        <v>14.0521484846777</v>
       </c>
       <c r="G99" s="18" t="n">
         <f aca="false">G97/G98</f>
-        <v>17.2424039863611</v>
+        <v>17.1516279671294</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43536,15 +43536,15 @@
       </c>
       <c r="E100" s="11" t="n">
         <f aca="false">E79/E91</f>
-        <v>0.655418865989612</v>
+        <v>0.658765911610499</v>
       </c>
       <c r="F100" s="11" t="n">
         <f aca="false">F79/F91</f>
-        <v>0.616062021633993</v>
+        <v>0.619147975616599</v>
       </c>
       <c r="G100" s="11" t="n">
         <f aca="false">G79/G91</f>
-        <v>0.614698955214771</v>
+        <v>0.617221102349895</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43564,15 +43564,15 @@
       </c>
       <c r="E101" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E100-D100)</f>
-        <v>0.600486206837982</v>
+        <v>0.601523822319888</v>
       </c>
       <c r="F101" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F100-D100)</f>
-        <v>0.588285216577344</v>
+        <v>0.589241891206701</v>
       </c>
       <c r="G101" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G100-D100)</f>
-        <v>0.58786265322457</v>
+        <v>0.588644542452108</v>
       </c>
       <c r="H101" s="8" t="s">
         <v>509</v>
@@ -43654,15 +43654,15 @@
       </c>
       <c r="E107" s="18" t="n">
         <f aca="false">mm_C_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F107" s="18" t="n">
         <f aca="false">mm_C_2028</f>
-        <v>3.72997394923451</v>
+        <v>3.64082803238745</v>
       </c>
       <c r="G107" s="18" t="n">
         <f aca="false">mm_C_2029</f>
-        <v>4.40250457885175</v>
+        <v>4.31335866200469</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43772,15 +43772,15 @@
       </c>
       <c r="E111" s="9" t="n">
         <f aca="false">E107*1000*E110</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F111" s="9" t="n">
         <f aca="false">F107*1000*F110</f>
-        <v>1181.49298461789</v>
+        <v>1153.25544816439</v>
       </c>
       <c r="G111" s="9" t="n">
         <f aca="false">G107*1000*G110</f>
-        <v>1394.52134128952</v>
+        <v>1366.28380483602</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43831,15 +43831,15 @@
       </c>
       <c r="E113" s="9" t="n">
         <f aca="false">E109+E111+E112</f>
-        <v>6091.59354523868</v>
+        <v>6056.29662467179</v>
       </c>
       <c r="F113" s="9" t="n">
         <f aca="false">F109+F111+F112</f>
-        <v>5626.59923005537</v>
+        <v>5598.36169360187</v>
       </c>
       <c r="G113" s="9" t="n">
         <f aca="false">G109+G111+G112</f>
-        <v>6962.54618979332</v>
+        <v>6934.30865333982</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43887,15 +43887,15 @@
       </c>
       <c r="E115" s="9" t="n">
         <f aca="false">E113+E114</f>
-        <v>6493.64694523868</v>
+        <v>6458.35002467179</v>
       </c>
       <c r="F115" s="9" t="n">
         <f aca="false">F113+F114</f>
-        <v>6036.69369805538</v>
+        <v>6008.45616160187</v>
       </c>
       <c r="G115" s="9" t="n">
         <f aca="false">G113+G114</f>
-        <v>7380.84254715332</v>
+        <v>7352.60501069982</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43915,15 +43915,15 @@
       </c>
       <c r="E116" s="9" t="n">
         <f aca="false">t_inc*E115-t_fix+0*E115</f>
-        <v>2504.68043854118</v>
+        <v>2487.64415984557</v>
       </c>
       <c r="F116" s="9" t="n">
         <f aca="false">t_inc*F115-t_fix+gm_adj_C28*F115</f>
-        <v>2223.76216889892</v>
+        <v>2210.41552130696</v>
       </c>
       <c r="G116" s="9" t="n">
         <f aca="false">t_inc*G115-t_fix+gm_adj_C29*G115</f>
-        <v>2785.27407420703</v>
+        <v>2772.20980197961</v>
       </c>
       <c r="H116" s="4" t="s">
         <v>500</v>
@@ -43946,15 +43946,15 @@
       </c>
       <c r="E117" s="11" t="n">
         <f aca="false">E116/E115</f>
-        <v>0.38571244474227</v>
+        <v>0.385182616355946</v>
       </c>
       <c r="F117" s="11" t="n">
         <f aca="false">F116/F115</f>
-        <v>0.368374192915448</v>
+        <v>0.367884105643148</v>
       </c>
       <c r="G117" s="11" t="n">
         <f aca="false">G116/G115</f>
-        <v>0.377365328743027</v>
+        <v>0.377037770687447</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44058,15 +44058,15 @@
       </c>
       <c r="E121" s="9" t="n">
         <f aca="false">E115+E118</f>
-        <v>6935.31894523867</v>
+        <v>6900.02202467179</v>
       </c>
       <c r="F121" s="9" t="n">
         <f aca="false">F115+F118</f>
-        <v>6522.53289805538</v>
+        <v>6494.29536160187</v>
       </c>
       <c r="G121" s="9" t="n">
         <f aca="false">G115+G118</f>
-        <v>7915.26566715332</v>
+        <v>7887.02813069982</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44105,15 +44105,15 @@
       </c>
       <c r="E123" s="9" t="n">
         <f aca="false">E116+E119+E120</f>
-        <v>2503.11387854118</v>
+        <v>2486.07759984557</v>
       </c>
       <c r="F123" s="9" t="n">
         <f aca="false">F116+F119+F120</f>
-        <v>2232.79573689892</v>
+        <v>2219.44908930696</v>
       </c>
       <c r="G123" s="9" t="n">
         <f aca="false">G116+G119+G120</f>
-        <v>2801.59523020703</v>
+        <v>2788.53095797961</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44133,15 +44133,15 @@
       </c>
       <c r="E124" s="11" t="n">
         <f aca="false">E123/E121</f>
-        <v>0.360922676852469</v>
+        <v>0.360299951356144</v>
       </c>
       <c r="F124" s="11" t="n">
         <f aca="false">F123/F121</f>
-        <v>0.342320348827156</v>
+        <v>0.341753641577447</v>
       </c>
       <c r="G124" s="11" t="n">
         <f aca="false">G123/G121</f>
-        <v>0.353948350948353</v>
+        <v>0.353559149500864</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44161,15 +44161,15 @@
       </c>
       <c r="E125" s="9" t="n">
         <f aca="false">E123*etr</f>
-        <v>354.834904810248</v>
+        <v>352.419886308253</v>
       </c>
       <c r="F125" s="9" t="n">
         <f aca="false">F123*etr</f>
-        <v>316.515309013825</v>
+        <v>314.623323008542</v>
       </c>
       <c r="G125" s="9" t="n">
         <f aca="false">G123*etr</f>
-        <v>397.146843916954</v>
+        <v>395.294886707986</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44217,15 +44217,15 @@
       </c>
       <c r="E127" s="9" t="n">
         <f aca="false">E123-E125+E126</f>
-        <v>2135.07897373094</v>
+        <v>2120.45771353732</v>
       </c>
       <c r="F127" s="9" t="n">
         <f aca="false">F123-F125+F126</f>
-        <v>1903.08042788509</v>
+        <v>1891.62576629842</v>
       </c>
       <c r="G127" s="9" t="n">
         <f aca="false">G123-G125+G126</f>
-        <v>2391.24838629008</v>
+        <v>2380.03607127163</v>
       </c>
       <c r="H127" s="8" t="s">
         <v>505</v>
@@ -44276,15 +44276,15 @@
       </c>
       <c r="E129" s="18" t="n">
         <f aca="false">E127/E128</f>
-        <v>13.6756209766078</v>
+        <v>13.5819687908721</v>
       </c>
       <c r="F129" s="18" t="n">
         <f aca="false">F127/F128</f>
-        <v>12.3127499632354</v>
+        <v>12.2386393886303</v>
       </c>
       <c r="G129" s="18" t="n">
         <f aca="false">G127/G128</f>
-        <v>15.6274246237865</v>
+        <v>15.5541492548145</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44304,15 +44304,15 @@
       </c>
       <c r="E130" s="11" t="n">
         <f aca="false">E109/E121</f>
-        <v>0.656536391181086</v>
+        <v>0.659894889569342</v>
       </c>
       <c r="F130" s="11" t="n">
         <f aca="false">F109/F121</f>
-        <v>0.648146885831759</v>
+        <v>0.650965062446286</v>
       </c>
       <c r="G130" s="11" t="n">
         <f aca="false">G109/G121</f>
-        <v>0.673192684026665</v>
+        <v>0.675602882474093</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44332,15 +44332,15 @@
       </c>
       <c r="E131" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E130-D130)</f>
-        <v>0.600832650111076</v>
+        <v>0.601873816058102</v>
       </c>
       <c r="F131" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F130-D130)+gm_adj_C28</f>
-        <v>0.588231824899232</v>
+        <v>0.589105486037201</v>
       </c>
       <c r="G131" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G130-D130)+gm_adj_C29</f>
-        <v>0.585996256851265</v>
+        <v>0.586743440937406</v>
       </c>
       <c r="H131" s="8" t="s">
         <v>509</v>
@@ -44413,27 +44413,27 @@
       </c>
       <c r="E138" s="20" t="n">
         <f aca="false">E5</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="F138" s="20" t="n">
         <f aca="false">F5</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G138" s="20" t="n">
         <f aca="false">G5</f>
-        <v>9060.66378455651</v>
+        <v>9019.68544869644</v>
       </c>
       <c r="H138" s="22" t="n">
         <f aca="false">G138*(1+H139)</f>
-        <v>10041.9056354887</v>
+        <v>9999.30167323895</v>
       </c>
       <c r="I138" s="22" t="n">
         <f aca="false">H138*(1+I139)</f>
-        <v>10886.9164580908</v>
+        <v>10842.286253336</v>
       </c>
       <c r="J138" s="22" t="n">
         <f aca="false">I138*(1+J139)</f>
-        <v>11540.1314455762</v>
+        <v>11492.8234285362</v>
       </c>
       <c r="K138" s="8" t="s">
         <v>520</v>
@@ -44452,23 +44452,23 @@
       </c>
       <c r="E139" s="11" t="n">
         <f aca="false">E138/D138-1</f>
-        <v>0.361407219899576</v>
+        <v>0.35450196116124</v>
       </c>
       <c r="F139" s="11" t="n">
         <f aca="false">F138/E138-1</f>
-        <v>0.149735254163045</v>
+        <v>0.149895352473155</v>
       </c>
       <c r="G139" s="11" t="n">
         <f aca="false">G138/F138-1</f>
-        <v>0.132445358463364</v>
+        <v>0.132913035623224</v>
       </c>
       <c r="H139" s="23" t="n">
         <f aca="false">$G139+((tp_g+0.02)-$G139)*1/3</f>
-        <v>0.108296905642243</v>
+        <v>0.108608690415483</v>
       </c>
       <c r="I139" s="23" t="n">
         <f aca="false">$G139+((tp_g+0.02)-$G139)*2/3</f>
-        <v>0.0841484528211213</v>
+        <v>0.0843043452077415</v>
       </c>
       <c r="J139" s="23" t="n">
         <f aca="false">$G139+((tp_g+0.02)-$G139)*3/3</f>
@@ -44492,27 +44492,27 @@
       </c>
       <c r="E140" s="11" t="n">
         <f aca="false">E141/E138</f>
-        <v>0.308217452408112</v>
+        <v>0.307676968523663</v>
       </c>
       <c r="F140" s="11" t="n">
         <f aca="false">F141/F138</f>
-        <v>0.320875117351121</v>
+        <v>0.320412227105355</v>
       </c>
       <c r="G140" s="11" t="n">
         <f aca="false">G141/G138</f>
-        <v>0.33026330355227</v>
+        <v>0.329881797213821</v>
       </c>
       <c r="H140" s="23" t="n">
         <f aca="false">$G140+($G140-$G140)*1/3</f>
-        <v>0.33026330355227</v>
+        <v>0.329881797213821</v>
       </c>
       <c r="I140" s="23" t="n">
         <f aca="false">$G140+($G140-$G140)*2/3</f>
-        <v>0.33026330355227</v>
+        <v>0.329881797213821</v>
       </c>
       <c r="J140" s="23" t="n">
         <f aca="false">$G140+($G140-$G140)*3/3</f>
-        <v>0.33026330355227</v>
+        <v>0.329881797213821</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44532,27 +44532,27 @@
       </c>
       <c r="E141" s="20" t="n">
         <f aca="false">E12</f>
-        <v>2144.87574133212</v>
+        <v>2130.2544811385</v>
       </c>
       <c r="F141" s="20" t="n">
         <f aca="false">F12</f>
-        <v>2567.31288041451</v>
+        <v>2550.96146970961</v>
       </c>
       <c r="G141" s="20" t="n">
         <f aca="false">G12</f>
-        <v>2992.40475386405</v>
+        <v>2975.43004611933</v>
       </c>
       <c r="H141" s="22" t="n">
         <f aca="false">H138*H140</f>
-        <v>3316.47292913666</v>
+        <v>3298.58760685123</v>
       </c>
       <c r="I141" s="22" t="n">
         <f aca="false">I138*I140</f>
-        <v>3595.54899494664</v>
+        <v>3576.67287515719</v>
       </c>
       <c r="J141" s="22" t="n">
         <f aca="false">J138*J140</f>
-        <v>3811.28193464344</v>
+        <v>3791.27324766662</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44572,27 +44572,27 @@
       </c>
       <c r="E142" s="14" t="n">
         <f aca="false">E13</f>
-        <v>13.7383712927123</v>
+        <v>13.6447191069765</v>
       </c>
       <c r="F142" s="14" t="n">
         <f aca="false">F13</f>
-        <v>16.6102709642527</v>
+        <v>16.5044788870469</v>
       </c>
       <c r="G142" s="14" t="n">
         <f aca="false">G13</f>
-        <v>19.5561364528184</v>
+        <v>19.4452023619426</v>
       </c>
       <c r="H142" s="24" t="n">
         <f aca="false">$G142*H141/$G141</f>
-        <v>21.6740055169761</v>
+        <v>21.5571203253372</v>
       </c>
       <c r="I142" s="24" t="n">
         <f aca="false">$G142*I141/$G141</f>
-        <v>23.4978395476661</v>
+        <v>23.3744792389293</v>
       </c>
       <c r="J142" s="24" t="n">
         <f aca="false">$G142*J141/$G141</f>
-        <v>24.9077099205261</v>
+        <v>24.7769479932651</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44617,27 +44617,27 @@
       </c>
       <c r="E145" s="20" t="n">
         <f aca="false">E16</f>
-        <v>6947.14404523867</v>
+        <v>6911.84712467179</v>
       </c>
       <c r="F145" s="20" t="n">
         <f aca="false">F16</f>
-        <v>7081.7701876497</v>
+        <v>7046.47326708282</v>
       </c>
       <c r="G145" s="20" t="n">
         <f aca="false">G16</f>
-        <v>8205.98597224243</v>
+        <v>8172.45389770389</v>
       </c>
       <c r="H145" s="22" t="n">
         <f aca="false">G145*(1+H146)</f>
-        <v>9183.85420003166</v>
+        <v>9152.02329451199</v>
       </c>
       <c r="I145" s="22" t="n">
         <f aca="false">H145*(1+I146)</f>
-        <v>9914.72934537662</v>
+        <v>9883.55519580191</v>
       </c>
       <c r="J145" s="22" t="n">
         <f aca="false">I145*(1+J146)</f>
-        <v>10311.3185191917</v>
+        <v>10278.897403634</v>
       </c>
       <c r="K145" s="8" t="s">
         <v>520</v>
@@ -44656,23 +44656,23 @@
       </c>
       <c r="E146" s="11" t="n">
         <f aca="false">E145/D145-1</f>
-        <v>0.359093834658164</v>
+        <v>0.352188575919828</v>
       </c>
       <c r="F146" s="11" t="n">
         <f aca="false">F145/E145-1</f>
-        <v>0.0193786312093658</v>
+        <v>0.0194775926004611</v>
       </c>
       <c r="G146" s="11" t="n">
         <f aca="false">G145/F145-1</f>
-        <v>0.158747849026973</v>
+        <v>0.159793500655289</v>
       </c>
       <c r="H146" s="23" t="n">
         <f aca="false">$G146+((tp_g)-$G146)*1/3</f>
-        <v>0.119165232684649</v>
+        <v>0.119862333770193</v>
       </c>
       <c r="I146" s="23" t="n">
         <f aca="false">$G146+((tp_g)-$G146)*2/3</f>
-        <v>0.0795826163423243</v>
+        <v>0.0799311668850963</v>
       </c>
       <c r="J146" s="23" t="n">
         <f aca="false">$G146+((tp_g)-$G146)*3/3</f>
@@ -44696,27 +44696,27 @@
       </c>
       <c r="E147" s="11" t="n">
         <f aca="false">E148/E145</f>
-        <v>0.308036992409592</v>
+        <v>0.307494662280863</v>
       </c>
       <c r="F147" s="11" t="n">
         <f aca="false">F148/F145</f>
-        <v>0.308757011926407</v>
+        <v>0.308228649960347</v>
       </c>
       <c r="G147" s="11" t="n">
         <f aca="false">G148/G145</f>
-        <v>0.32151728303213</v>
+        <v>0.321136851925048</v>
       </c>
       <c r="H147" s="23" t="n">
         <f aca="false">$G147+(($G147+nim10)/2-$G147)*1/3</f>
-        <v>0.297936241526097</v>
+        <v>0.297619215603529</v>
       </c>
       <c r="I147" s="23" t="n">
         <f aca="false">$G147+(($G147+nim10)/2-$G147)*2/3</f>
-        <v>0.274355200020065</v>
+        <v>0.274101579282011</v>
       </c>
       <c r="J147" s="23" t="n">
         <f aca="false">$G147+(($G147+nim10)/2-$G147)*3/3</f>
-        <v>0.250774158514033</v>
+        <v>0.250583942960492</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44736,27 +44736,27 @@
       </c>
       <c r="E148" s="20" t="n">
         <f aca="false">E23</f>
-        <v>2139.97735753153</v>
+        <v>2125.35609733791</v>
       </c>
       <c r="F148" s="20" t="n">
         <f aca="false">F23</f>
-        <v>2186.54620228823</v>
+        <v>2171.92494209461</v>
       </c>
       <c r="G148" s="20" t="n">
         <f aca="false">G23</f>
-        <v>2638.36631439515</v>
+        <v>2624.47611721122</v>
       </c>
       <c r="H148" s="22" t="n">
         <f aca="false">H145*H147</f>
-        <v>2736.2030030811</v>
+        <v>2723.81799409789</v>
       </c>
       <c r="I148" s="22" t="n">
         <f aca="false">I145*I147</f>
-        <v>2720.15755269561</v>
+        <v>2709.09808809023</v>
       </c>
       <c r="J148" s="22" t="n">
         <f aca="false">J145*J147</f>
-        <v>2585.81222482046</v>
+        <v>2575.72664068897</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44776,27 +44776,27 @@
       </c>
       <c r="E149" s="14" t="n">
         <f aca="false">E24</f>
-        <v>13.70699613466</v>
+        <v>13.6133439489243</v>
       </c>
       <c r="F149" s="14" t="n">
         <f aca="false">F24</f>
-        <v>14.1467466520876</v>
+        <v>14.0521484846777</v>
       </c>
       <c r="G149" s="14" t="n">
         <f aca="false">G24</f>
-        <v>17.2424039863611</v>
+        <v>17.1516279671294</v>
       </c>
       <c r="H149" s="24" t="n">
         <f aca="false">$G149*H148/$G148</f>
-        <v>17.8817919674033</v>
+        <v>17.8008527410729</v>
       </c>
       <c r="I149" s="24" t="n">
         <f aca="false">$G149*I148/$G148</f>
-        <v>17.7769308129153</v>
+        <v>17.7046543607947</v>
       </c>
       <c r="J149" s="24" t="n">
         <f aca="false">$G149*J148/$G148</f>
-        <v>16.8989494635231</v>
+        <v>16.8330375713478</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44821,27 +44821,27 @@
       </c>
       <c r="E152" s="20" t="n">
         <f aca="false">E27</f>
-        <v>6935.31894523867</v>
+        <v>6900.02202467179</v>
       </c>
       <c r="F152" s="20" t="n">
         <f aca="false">F27</f>
-        <v>6522.53289805538</v>
+        <v>6494.29536160187</v>
       </c>
       <c r="G152" s="20" t="n">
         <f aca="false">G27</f>
-        <v>7915.26566715332</v>
+        <v>7887.02813069982</v>
       </c>
       <c r="H152" s="22" t="n">
         <f aca="false">G152*(1+H153)</f>
-        <v>9094.77939883154</v>
+        <v>9067.21564300574</v>
       </c>
       <c r="I152" s="22" t="n">
         <f aca="false">H152*(1+I153)</f>
-        <v>9863.36819936387</v>
+        <v>9836.281136947</v>
       </c>
       <c r="J152" s="22" t="n">
         <f aca="false">I152*(1+J153)</f>
-        <v>10060.6355633511</v>
+        <v>10033.0067596859</v>
       </c>
       <c r="K152" s="8" t="s">
         <v>520</v>
@@ -44860,23 +44860,23 @@
       </c>
       <c r="E153" s="11" t="n">
         <f aca="false">E152/D152-1</f>
-        <v>0.356780449416753</v>
+        <v>0.349875190678416</v>
       </c>
       <c r="F153" s="11" t="n">
         <f aca="false">F152/E152-1</f>
-        <v>-0.059519403569275</v>
+        <v>-0.0588007779713169</v>
       </c>
       <c r="G153" s="11" t="n">
         <f aca="false">G152/F152-1</f>
-        <v>0.213526369412897</v>
+        <v>0.214454793253262</v>
       </c>
       <c r="H153" s="23" t="n">
         <f aca="false">$G153+((tp_g-0.02)-$G153)*1/3</f>
-        <v>0.149017579608598</v>
+        <v>0.149636528835508</v>
       </c>
       <c r="I153" s="23" t="n">
         <f aca="false">$G153+((tp_g-0.02)-$G153)*2/3</f>
-        <v>0.084508789804299</v>
+        <v>0.0848182644177539</v>
       </c>
       <c r="J153" s="23" t="n">
         <f aca="false">$G153+((tp_g-0.02)-$G153)*3/3</f>
@@ -44900,23 +44900,23 @@
       </c>
       <c r="E154" s="11" t="n">
         <f aca="false">E155/E152</f>
-        <v>0.307855917022639</v>
+        <v>0.307311731173522</v>
       </c>
       <c r="F154" s="11" t="n">
         <f aca="false">F155/F152</f>
-        <v>0.291770153961581</v>
+        <v>0.291274982268721</v>
       </c>
       <c r="G154" s="11" t="n">
         <f aca="false">G155/G152</f>
-        <v>0.302105890925841</v>
+        <v>0.30176589100874</v>
       </c>
       <c r="H154" s="23" t="n">
         <f aca="false">$G154+(nim10-$G154)*1/3</f>
-        <v>0.261414271949206</v>
+        <v>0.261187605337805</v>
       </c>
       <c r="I154" s="23" t="n">
         <f aca="false">$G154+(nim10-$G154)*2/3</f>
-        <v>0.220722652972571</v>
+        <v>0.220609319666871</v>
       </c>
       <c r="J154" s="23" t="n">
         <f aca="false">$G154+(nim10-$G154)*3/3</f>
@@ -44940,27 +44940,27 @@
       </c>
       <c r="E155" s="20" t="n">
         <f aca="false">E34</f>
-        <v>2135.07897373094</v>
+        <v>2120.45771353732</v>
       </c>
       <c r="F155" s="20" t="n">
         <f aca="false">F34</f>
-        <v>1903.08042788509</v>
+        <v>1891.62576629842</v>
       </c>
       <c r="G155" s="20" t="n">
         <f aca="false">G34</f>
-        <v>2391.24838629008</v>
+        <v>2380.03607127163</v>
       </c>
       <c r="H155" s="22" t="n">
         <f aca="false">H152*H154</f>
-        <v>2377.50513508419</v>
+        <v>2368.24434087816</v>
       </c>
       <c r="I155" s="22" t="n">
         <f aca="false">I152*I154</f>
-        <v>2177.06879620888</v>
+        <v>2169.97528967395</v>
       </c>
       <c r="J155" s="22" t="n">
         <f aca="false">J152*J154</f>
-        <v>1811.22662312639</v>
+        <v>1806.25258103447</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44980,27 +44980,27 @@
       </c>
       <c r="E156" s="14" t="n">
         <f aca="false">E35</f>
-        <v>13.6756209766078</v>
+        <v>13.5819687908721</v>
       </c>
       <c r="F156" s="14" t="n">
         <f aca="false">F35</f>
-        <v>12.3127499632354</v>
+        <v>12.2386393886303</v>
       </c>
       <c r="G156" s="14" t="n">
         <f aca="false">G35</f>
-        <v>15.6274246237865</v>
+        <v>15.5541492548145</v>
       </c>
       <c r="H156" s="24" t="n">
         <f aca="false">$G156*H155/$G155</f>
-        <v>15.5376089344013</v>
+        <v>15.4770872570043</v>
       </c>
       <c r="I156" s="24" t="n">
         <f aca="false">$G156*I155/$G155</f>
-        <v>14.2277057910891</v>
+        <v>14.1813478973092</v>
       </c>
       <c r="J156" s="24" t="n">
         <f aca="false">$G156*J155/$G155</f>
-        <v>11.8368328826838</v>
+        <v>11.8043262353975</v>
       </c>
     </row>
   </sheetData>
@@ -45895,7 +45895,7 @@
       </c>
       <c r="C49" s="28" t="n">
         <f aca="false">PL!E13</f>
-        <v>13.7383712927123</v>
+        <v>13.6447191069765</v>
       </c>
       <c r="D49" s="27" t="str">
         <f aca="false">"規則值："&amp;D43</f>
@@ -45907,11 +45907,11 @@
       </c>
       <c r="F49" s="30" t="n">
         <f aca="false">C49*E49</f>
-        <v>399.00900783409</v>
+        <v>396.289029976764</v>
       </c>
       <c r="G49" s="31" t="n">
         <f aca="false">F49/px-1</f>
-        <v>0.291918432359042</v>
+        <v>0.283111639879436</v>
       </c>
       <c r="H49" s="27"/>
     </row>
@@ -45924,7 +45924,7 @@
       </c>
       <c r="C50" s="18" t="n">
         <f aca="false">PL!E13</f>
-        <v>13.7383712927123</v>
+        <v>13.6447191069765</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>592</v>
@@ -45935,11 +45935,11 @@
       </c>
       <c r="F50" s="14" t="n">
         <f aca="false">C50*E50</f>
-        <v>351.028596501195</v>
+        <v>348.635693105469</v>
       </c>
       <c r="G50" s="32" t="n">
         <f aca="false">F50/px-1</f>
-        <v>0.136566606770909</v>
+        <v>0.128818821775843</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45951,7 +45951,7 @@
       </c>
       <c r="C51" s="18" t="n">
         <f aca="false">PL!E13</f>
-        <v>13.7383712927123</v>
+        <v>13.6447191069765</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>593</v>
@@ -45962,11 +45962,11 @@
       </c>
       <c r="F51" s="14" t="n">
         <f aca="false">C51*E51</f>
-        <v>399.00900783409</v>
+        <v>396.289029976764</v>
       </c>
       <c r="G51" s="32" t="n">
         <f aca="false">F51/px-1</f>
-        <v>0.291918432359042</v>
+        <v>0.283111639879436</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45978,7 +45978,7 @@
       </c>
       <c r="C52" s="18" t="n">
         <f aca="false">PL!E13</f>
-        <v>13.7383712927123</v>
+        <v>13.6447191069765</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>594</v>
@@ -45989,11 +45989,11 @@
       </c>
       <c r="F52" s="14" t="n">
         <f aca="false">C52*E52</f>
-        <v>518.391784735915</v>
+        <v>514.857994399813</v>
       </c>
       <c r="G52" s="32" t="n">
         <f aca="false">F52/px-1</f>
-        <v>0.678458101783762</v>
+        <v>0.667016332847056</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46005,7 +46005,7 @@
       </c>
       <c r="C53" s="18" t="n">
         <f aca="false">PL!F13</f>
-        <v>16.6102709642527</v>
+        <v>16.5044788870469</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>592</v>
@@ -46016,11 +46016,11 @@
       </c>
       <c r="F53" s="14" t="n">
         <f aca="false">C53*E53</f>
-        <v>424.408394551046</v>
+        <v>421.705305255287</v>
       </c>
       <c r="G53" s="32" t="n">
         <f aca="false">F53/px-1</f>
-        <v>0.374157016516257</v>
+        <v>0.365404906120405</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46032,7 +46032,7 @@
       </c>
       <c r="C54" s="18" t="n">
         <f aca="false">PL!F13</f>
-        <v>16.6102709642527</v>
+        <v>16.5044788870469</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>593</v>
@@ -46043,11 +46043,11 @@
       </c>
       <c r="F54" s="14" t="n">
         <f aca="false">C54*E54</f>
-        <v>482.418737715846</v>
+        <v>479.346176138989</v>
       </c>
       <c r="G54" s="32" t="n">
         <f aca="false">F54/px-1</f>
-        <v>0.561983933028481</v>
+        <v>0.552035538737216</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46059,7 +46059,7 @@
       </c>
       <c r="C55" s="18" t="n">
         <f aca="false">PL!F13</f>
-        <v>16.6102709642527</v>
+        <v>16.5044788870469</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>594</v>
@@ -46070,11 +46070,11 @@
       </c>
       <c r="F55" s="14" t="n">
         <f aca="false">C55*E55</f>
-        <v>626.75755565536</v>
+        <v>622.765689185518</v>
       </c>
       <c r="G55" s="32" t="n">
         <f aca="false">F55/px-1</f>
-        <v>1.02932671411805</v>
+        <v>1.0164017781626</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46086,7 +46086,7 @@
       </c>
       <c r="C56" s="28" t="n">
         <f aca="false">PL!E24</f>
-        <v>13.70699613466</v>
+        <v>13.6133439489243</v>
       </c>
       <c r="D56" s="27" t="str">
         <f aca="false">"規則值："&amp;D44</f>
@@ -46098,11 +46098,11 @@
       </c>
       <c r="F56" s="30" t="n">
         <f aca="false">C56*E56</f>
-        <v>398.097766580063</v>
+        <v>395.377788722736</v>
       </c>
       <c r="G56" s="31" t="n">
         <f aca="false">F56/px-1</f>
-        <v>0.288967999287883</v>
+        <v>0.280161206808277</v>
       </c>
       <c r="H56" s="27"/>
     </row>
@@ -46115,7 +46115,7 @@
       </c>
       <c r="C57" s="18" t="n">
         <f aca="false">PL!E24</f>
-        <v>13.70699613466</v>
+        <v>13.6133439489243</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>592</v>
@@ -46126,11 +46126,11 @@
       </c>
       <c r="F57" s="14" t="n">
         <f aca="false">C57*E57</f>
-        <v>350.226931044539</v>
+        <v>347.834027648813</v>
       </c>
       <c r="G57" s="32" t="n">
         <f aca="false">F57/px-1</f>
-        <v>0.133970960157161</v>
+        <v>0.126223175162095</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46142,7 +46142,7 @@
       </c>
       <c r="C58" s="18" t="n">
         <f aca="false">PL!E24</f>
-        <v>13.70699613466</v>
+        <v>13.6133439489243</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>593</v>
@@ -46153,11 +46153,11 @@
       </c>
       <c r="F58" s="14" t="n">
         <f aca="false">C58*E58</f>
-        <v>398.097766580063</v>
+        <v>395.377788722736</v>
       </c>
       <c r="G58" s="32" t="n">
         <f aca="false">F58/px-1</f>
-        <v>0.288967999287883</v>
+        <v>0.280161206808277</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46169,7 +46169,7 @@
       </c>
       <c r="C59" s="18" t="n">
         <f aca="false">PL!E24</f>
-        <v>13.70699613466</v>
+        <v>13.6133439489243</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>594</v>
@@ -46180,11 +46180,11 @@
       </c>
       <c r="F59" s="14" t="n">
         <f aca="false">C59*E59</f>
-        <v>517.207901738976</v>
+        <v>513.674111402875</v>
       </c>
       <c r="G59" s="32" t="n">
         <f aca="false">F59/px-1</f>
-        <v>0.674624904448683</v>
+        <v>0.663183135511978</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46196,7 +46196,7 @@
       </c>
       <c r="C60" s="18" t="n">
         <f aca="false">PL!F24</f>
-        <v>14.1467466520876</v>
+        <v>14.0521484846777</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>592</v>
@@ -46207,11 +46207,11 @@
       </c>
       <c r="F60" s="14" t="n">
         <f aca="false">C60*E60</f>
-        <v>361.462979601849</v>
+        <v>359.045905464752</v>
       </c>
       <c r="G60" s="32" t="n">
         <f aca="false">F60/px-1</f>
-        <v>0.170351237176133</v>
+        <v>0.162525191726572</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46223,7 +46223,7 @@
       </c>
       <c r="C61" s="18" t="n">
         <f aca="false">PL!F24</f>
-        <v>14.1467466520876</v>
+        <v>14.0521484846777</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>593</v>
@@ -46234,11 +46234,11 @@
       </c>
       <c r="F61" s="14" t="n">
         <f aca="false">C61*E61</f>
-        <v>410.869616598876</v>
+        <v>408.122164217738</v>
       </c>
       <c r="G61" s="32" t="n">
         <f aca="false">F61/px-1</f>
-        <v>0.33032092147928</v>
+        <v>0.321425171499881</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46250,7 +46250,7 @@
       </c>
       <c r="C62" s="18" t="n">
         <f aca="false">PL!F24</f>
-        <v>14.1467466520876</v>
+        <v>14.0521484846777</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>594</v>
@@ -46261,11 +46261,11 @@
       </c>
       <c r="F62" s="14" t="n">
         <f aca="false">C62*E62</f>
-        <v>533.801066293258</v>
+        <v>530.231581105277</v>
       </c>
       <c r="G62" s="32" t="n">
         <f aca="false">F62/px-1</f>
-        <v>0.728350546521801</v>
+        <v>0.716793204161493</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46277,7 +46277,7 @@
       </c>
       <c r="C63" s="28" t="n">
         <f aca="false">PL!E35</f>
-        <v>13.6756209766078</v>
+        <v>13.5819687908721</v>
       </c>
       <c r="D63" s="27" t="str">
         <f aca="false">"規則值："&amp;D45</f>
@@ -46289,11 +46289,11 @@
       </c>
       <c r="F63" s="30" t="n">
         <f aca="false">C63*E63</f>
-        <v>349.425265587883</v>
+        <v>347.032362192157</v>
       </c>
       <c r="G63" s="31" t="n">
         <f aca="false">F63/px-1</f>
-        <v>0.131375313543413</v>
+        <v>0.123627528548347</v>
       </c>
       <c r="H63" s="27"/>
     </row>
@@ -46306,7 +46306,7 @@
       </c>
       <c r="C64" s="18" t="n">
         <f aca="false">PL!E35</f>
-        <v>13.6756209766078</v>
+        <v>13.5819687908721</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>592</v>
@@ -46317,11 +46317,11 @@
       </c>
       <c r="F64" s="14" t="n">
         <f aca="false">C64*E64</f>
-        <v>349.425265587883</v>
+        <v>347.032362192157</v>
       </c>
       <c r="G64" s="32" t="n">
         <f aca="false">F64/px-1</f>
-        <v>0.131375313543413</v>
+        <v>0.123627528548347</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46333,7 +46333,7 @@
       </c>
       <c r="C65" s="18" t="n">
         <f aca="false">PL!E35</f>
-        <v>13.6756209766078</v>
+        <v>13.5819687908721</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>593</v>
@@ -46344,11 +46344,11 @@
       </c>
       <c r="F65" s="14" t="n">
         <f aca="false">C65*E65</f>
-        <v>397.186525326035</v>
+        <v>394.466547468709</v>
       </c>
       <c r="G65" s="32" t="n">
         <f aca="false">F65/px-1</f>
-        <v>0.286017566216725</v>
+        <v>0.277210773737119</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46360,7 +46360,7 @@
       </c>
       <c r="C66" s="18" t="n">
         <f aca="false">PL!E35</f>
-        <v>13.6756209766078</v>
+        <v>13.5819687908721</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>594</v>
@@ -46371,11 +46371,11 @@
       </c>
       <c r="F66" s="14" t="n">
         <f aca="false">C66*E66</f>
-        <v>516.024018742037</v>
+        <v>512.490228405936</v>
       </c>
       <c r="G66" s="32" t="n">
         <f aca="false">F66/px-1</f>
-        <v>0.670791707113606</v>
+        <v>0.6593499381769</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46387,7 +46387,7 @@
       </c>
       <c r="C67" s="18" t="n">
         <f aca="false">PL!F35</f>
-        <v>12.3127499632354</v>
+        <v>12.2386393886303</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>592</v>
@@ -46398,11 +46398,11 @@
       </c>
       <c r="F67" s="14" t="n">
         <f aca="false">C67*E67</f>
-        <v>314.602600743321</v>
+        <v>312.709004301994</v>
       </c>
       <c r="G67" s="32" t="n">
         <f aca="false">F67/px-1</f>
-        <v>0.0186258725702471</v>
+        <v>0.0124947524752921</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46414,7 +46414,7 @@
       </c>
       <c r="C68" s="18" t="n">
         <f aca="false">PL!F35</f>
-        <v>12.3127499632354</v>
+        <v>12.2386393886303</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>593</v>
@@ -46425,11 +46425,11 @@
       </c>
       <c r="F68" s="14" t="n">
         <f aca="false">C68*E68</f>
-        <v>357.604117829156</v>
+        <v>355.451694793475</v>
       </c>
       <c r="G68" s="32" t="n">
         <f aca="false">F68/px-1</f>
-        <v>0.157856946184737</v>
+        <v>0.15088779275854</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46441,7 +46441,7 @@
       </c>
       <c r="C69" s="18" t="n">
         <f aca="false">PL!F35</f>
-        <v>12.3127499632354</v>
+        <v>12.2386393886303</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>594</v>
@@ -46452,11 +46452,11 @@
       </c>
       <c r="F69" s="14" t="n">
         <f aca="false">C69*E69</f>
-        <v>464.598626172997</v>
+        <v>461.802202039541</v>
       </c>
       <c r="G69" s="32" t="n">
         <f aca="false">F69/px-1</f>
-        <v>0.50428566026549</v>
+        <v>0.495231348679103</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46523,15 +46523,15 @@
       </c>
       <c r="B76" s="25" t="n">
         <f aca="false">px/PL!E13</f>
-        <v>22.4808307636753</v>
+        <v>22.635130674261</v>
       </c>
       <c r="C76" s="25" t="n">
         <f aca="false">px/PL!E24</f>
-        <v>22.5322891292739</v>
+        <v>22.6872986651017</v>
       </c>
       <c r="D76" s="25" t="n">
         <f aca="false">px/PL!E35</f>
-        <v>22.5839836105643</v>
+        <v>22.7397076782835</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46540,15 +46540,15 @@
       </c>
       <c r="B77" s="25" t="n">
         <f aca="false">px/PL!F13</f>
-        <v>18.5939170206604</v>
+        <v>18.713102189636</v>
       </c>
       <c r="C77" s="25" t="n">
         <f aca="false">px/PL!F24</f>
-        <v>21.8318746773079</v>
+        <v>21.9788454652871</v>
       </c>
       <c r="D77" s="25" t="n">
         <f aca="false">px/PL!F35</f>
-        <v>25.0837547194733</v>
+        <v>25.2356483586665</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46587,7 +46587,7 @@
       </c>
       <c r="B82" s="14" t="n">
         <f aca="false">tp_wA*B84+tp_wB*B85+tp_wC*B86</f>
-        <v>388.636638757835</v>
+        <v>385.982075792829</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>612</v>
@@ -46599,7 +46599,7 @@
       </c>
       <c r="B83" s="11" t="n">
         <f aca="false">B82/px-1</f>
-        <v>0.258334592060337</v>
+        <v>0.249739601077639</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>614</v>
@@ -46611,7 +46611,7 @@
       </c>
       <c r="B84" s="14" t="n">
         <f aca="false">F49</f>
-        <v>399.00900783409</v>
+        <v>396.289029976764</v>
       </c>
       <c r="E84" s="0" t="str">
         <f aca="false">"FY2027 EPS × "&amp;D49&amp;" "&amp;TEXT(E49,"0.0")&amp;"x（第 5 節 F49）"</f>
@@ -46624,7 +46624,7 @@
       </c>
       <c r="B85" s="14" t="n">
         <f aca="false">F56</f>
-        <v>398.097766580063</v>
+        <v>395.377788722736</v>
       </c>
       <c r="E85" s="0" t="str">
         <f aca="false">"FY2027 EPS × "&amp;D56&amp;" "&amp;TEXT(E56,"0.0")&amp;"x（第 5 節 F56）"</f>
@@ -46637,7 +46637,7 @@
       </c>
       <c r="B86" s="14" t="n">
         <f aca="false">F63</f>
-        <v>349.425265587883</v>
+        <v>347.032362192157</v>
       </c>
       <c r="E86" s="0" t="str">
         <f aca="false">"FY2027 EPS × "&amp;D63&amp;" "&amp;TEXT(E63,"0.0")&amp;"x（第 5 節 F63）"</f>
@@ -46714,15 +46714,15 @@
       </c>
       <c r="B95" s="14" t="n">
         <f aca="false">PL!E142</f>
-        <v>13.7383712927123</v>
+        <v>13.6447191069765</v>
       </c>
       <c r="C95" s="14" t="n">
         <f aca="false">PL!E149</f>
-        <v>13.70699613466</v>
+        <v>13.6133439489243</v>
       </c>
       <c r="D95" s="14" t="n">
         <f aca="false">PL!E156</f>
-        <v>13.6756209766078</v>
+        <v>13.5819687908721</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46731,15 +46731,15 @@
       </c>
       <c r="B96" s="14" t="n">
         <f aca="false">PL!F142</f>
-        <v>16.6102709642527</v>
+        <v>16.5044788870469</v>
       </c>
       <c r="C96" s="14" t="n">
         <f aca="false">PL!F149</f>
-        <v>14.1467466520876</v>
+        <v>14.0521484846777</v>
       </c>
       <c r="D96" s="14" t="n">
         <f aca="false">PL!F156</f>
-        <v>12.3127499632354</v>
+        <v>12.2386393886303</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46748,15 +46748,15 @@
       </c>
       <c r="B97" s="14" t="n">
         <f aca="false">PL!G142</f>
-        <v>19.5561364528184</v>
+        <v>19.4452023619426</v>
       </c>
       <c r="C97" s="14" t="n">
         <f aca="false">PL!G149</f>
-        <v>17.2424039863611</v>
+        <v>17.1516279671294</v>
       </c>
       <c r="D97" s="14" t="n">
         <f aca="false">PL!G156</f>
-        <v>15.6274246237865</v>
+        <v>15.5541492548145</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46765,15 +46765,15 @@
       </c>
       <c r="B98" s="14" t="n">
         <f aca="false">PL!H142</f>
-        <v>21.6740055169761</v>
+        <v>21.5571203253372</v>
       </c>
       <c r="C98" s="14" t="n">
         <f aca="false">PL!H149</f>
-        <v>17.8817919674033</v>
+        <v>17.8008527410729</v>
       </c>
       <c r="D98" s="14" t="n">
         <f aca="false">PL!H156</f>
-        <v>15.5376089344013</v>
+        <v>15.4770872570043</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46782,15 +46782,15 @@
       </c>
       <c r="B99" s="14" t="n">
         <f aca="false">PL!I142</f>
-        <v>23.4978395476661</v>
+        <v>23.3744792389293</v>
       </c>
       <c r="C99" s="14" t="n">
         <f aca="false">PL!I149</f>
-        <v>17.7769308129153</v>
+        <v>17.7046543607947</v>
       </c>
       <c r="D99" s="14" t="n">
         <f aca="false">PL!I156</f>
-        <v>14.2277057910891</v>
+        <v>14.1813478973092</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46799,15 +46799,15 @@
       </c>
       <c r="B100" s="14" t="n">
         <f aca="false">PL!J142</f>
-        <v>24.9077099205261</v>
+        <v>24.7769479932651</v>
       </c>
       <c r="C100" s="14" t="n">
         <f aca="false">PL!J149</f>
-        <v>16.8989494635231</v>
+        <v>16.8330375713478</v>
       </c>
       <c r="D100" s="14" t="n">
         <f aca="false">PL!J156</f>
-        <v>11.8368328826838</v>
+        <v>11.8043262353975</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46836,15 +46836,15 @@
       </c>
       <c r="B103" s="14" t="n">
         <f aca="false">B95*(1-$B$102)</f>
-        <v>10.8989646590558</v>
+        <v>10.8246682347687</v>
       </c>
       <c r="C103" s="14" t="n">
         <f aca="false">C95*(1-$B$102)</f>
-        <v>10.8740740274447</v>
+        <v>10.7997776031576</v>
       </c>
       <c r="D103" s="14" t="n">
         <f aca="false">D95*(1-$B$102)</f>
-        <v>10.8491833958336</v>
+        <v>10.7748869715465</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46853,15 +46853,15 @@
       </c>
       <c r="B104" s="14" t="n">
         <f aca="false">B96*(1-$B$102)</f>
-        <v>13.1773084566993</v>
+        <v>13.0933811784137</v>
       </c>
       <c r="C104" s="14" t="n">
         <f aca="false">C96*(1-$B$102)</f>
-        <v>11.2229381865308</v>
+        <v>11.1478912933115</v>
       </c>
       <c r="D104" s="14" t="n">
         <f aca="false">D96*(1-$B$102)</f>
-        <v>9.76798660087748</v>
+        <v>9.70919298435096</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46870,15 +46870,15 @@
       </c>
       <c r="B105" s="14" t="n">
         <f aca="false">B97*(1-$B$102)</f>
-        <v>15.5143310313651</v>
+        <v>15.4263244758441</v>
       </c>
       <c r="C105" s="14" t="n">
         <f aca="false">C97*(1-$B$102)</f>
-        <v>13.6787940637621</v>
+        <v>13.6067793682487</v>
       </c>
       <c r="D105" s="14" t="n">
         <f aca="false">D97*(1-$B$102)</f>
-        <v>12.3975939401971</v>
+        <v>12.3394629114318</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46887,15 +46887,15 @@
       </c>
       <c r="B106" s="14" t="n">
         <f aca="false">B98*(1-$B$102)</f>
-        <v>17.1944850751714</v>
+        <v>17.1017573750898</v>
       </c>
       <c r="C106" s="14" t="n">
         <f aca="false">C98*(1-$B$102)</f>
-        <v>14.1860351959406</v>
+        <v>14.1218242535727</v>
       </c>
       <c r="D106" s="14" t="n">
         <f aca="false">D98*(1-$B$102)</f>
-        <v>12.3263410963497</v>
+        <v>12.2783278632667</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46904,15 +46904,15 @@
       </c>
       <c r="B107" s="14" t="n">
         <f aca="false">B99*(1-$B$102)</f>
-        <v>18.6413743913029</v>
+        <v>18.5435098324985</v>
       </c>
       <c r="C107" s="14" t="n">
         <f aca="false">C99*(1-$B$102)</f>
-        <v>14.1028464399723</v>
+        <v>14.045507874828</v>
       </c>
       <c r="D107" s="14" t="n">
         <f aca="false">D99*(1-$B$102)</f>
-        <v>11.2871649260769</v>
+        <v>11.2503881469952</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46921,15 +46921,15 @@
       </c>
       <c r="B108" s="14" t="n">
         <f aca="false">B100*(1-$B$102)</f>
-        <v>19.7598568547811</v>
+        <v>19.6561204224484</v>
       </c>
       <c r="C108" s="14" t="n">
         <f aca="false">C100*(1-$B$102)</f>
-        <v>13.4063237230901</v>
+        <v>13.3540343091469</v>
       </c>
       <c r="D108" s="14" t="n">
         <f aca="false">D100*(1-$B$102)</f>
-        <v>9.39043067877745</v>
+        <v>9.36464241083732</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46938,15 +46938,15 @@
       </c>
       <c r="B109" s="14" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(B103:B108,1/(1+tp_r)^{1;2;3;4;5;6})+B108*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>260.26213299813</v>
+        <v>258.861472274415</v>
       </c>
       <c r="C109" s="14" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(C103:C108,1/(1+tp_r)^{1;2;3;4;5;6})+C108*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>186.621639853638</v>
+        <v>185.81738317384</v>
       </c>
       <c r="D109" s="14" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(D103:D108,1/(1+tp_r)^{1;2;3;4;5;6})+D108*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>139.856248241198</v>
+        <v>139.373937641237</v>
       </c>
       <c r="E109" s="8" t="s">
         <v>636</v>
@@ -46958,15 +46958,15 @@
       </c>
       <c r="B110" s="14" t="n">
         <f aca="false">B109*(1+tp_r)</f>
-        <v>286.288346297943</v>
+        <v>284.747619501857</v>
       </c>
       <c r="C110" s="14" t="n">
         <f aca="false">C109*(1+tp_r)</f>
-        <v>205.283803839002</v>
+        <v>204.399121491224</v>
       </c>
       <c r="D110" s="14" t="n">
         <f aca="false">D109*(1+tp_r)</f>
-        <v>153.841873065318</v>
+        <v>153.311331405361</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46975,7 +46975,7 @@
       </c>
       <c r="B111" s="30" t="n">
         <f aca="false">tp_wA*B110+tp_wB*C110+tp_wC*D110</f>
-        <v>219.296780421947</v>
+        <v>218.286112877241</v>
       </c>
       <c r="E111" s="8" t="s">
         <v>639</v>
@@ -47124,7 +47124,7 @@
       </c>
       <c r="B121" s="14" t="n">
         <f aca="false">tp_wA*(2/12*B95+10/12*B96)+tp_wB*(2/12*C95+10/12*C96)+tp_wC*(2/12*D95+10/12*D96)</f>
-        <v>14.3841927817164</v>
+        <v>14.2903683992708</v>
       </c>
       <c r="E121" s="4" t="s">
         <v>663</v>
@@ -47136,7 +47136,7 @@
       </c>
       <c r="B122" s="30" t="n">
         <f aca="false">B120*B121</f>
-        <v>405.202710660952</v>
+        <v>402.559677807458</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>665</v>
@@ -47166,7 +47166,7 @@
       </c>
       <c r="B126" s="30" t="n">
         <f aca="false">tp_w_dcf*B111+(1-tp_w_dcf)*tp_comp_adj</f>
-        <v>356.366566588699</v>
+        <v>354.251953735619</v>
       </c>
       <c r="E126" s="8" t="s">
         <v>668</v>
@@ -47178,7 +47178,7 @@
       </c>
       <c r="B127" s="14" t="n">
         <f aca="false">B122</f>
-        <v>405.202710660952</v>
+        <v>402.559677807458</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>670</v>
@@ -47202,7 +47202,7 @@
       </c>
       <c r="B129" s="11" t="n">
         <f aca="false">B126/px-1</f>
-        <v>0.153849980860286</v>
+        <v>0.147003249912964</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>614</v>
@@ -47214,7 +47214,7 @@
       </c>
       <c r="B130" s="11" t="n">
         <f aca="false">B127/px-1</f>
-        <v>0.311972513067677</v>
+        <v>0.30341485448424</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47223,7 +47223,7 @@
       </c>
       <c r="B131" s="11" t="n">
         <f aca="false">B121/cons_feps-1</f>
-        <v>0.272937414311189</v>
+        <v>0.264634371616882</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>675</v>
@@ -47248,7 +47248,7 @@
       </c>
       <c r="B133" s="33" t="str">
         <f aca="false">TEXT(D110,"#,##0.00")&amp;"～"&amp;TEXT(B110,"#,##0.00")</f>
-        <v>153.84～286.29</v>
+        <v>153.31～284.75</v>
       </c>
       <c r="E133" s="8" t="s">
         <v>678</v>
@@ -47260,15 +47260,15 @@
       </c>
       <c r="B134" s="32" t="n">
         <f aca="false">IF(px/B96&lt;MIN(E20:E29),0,IF(px/B96&gt;MAX(E20:E29),1,PERCENTRANK(E20:E29,px/B96)))</f>
-        <v>0.0946</v>
+        <v>0.0966</v>
       </c>
       <c r="C134" s="32" t="n">
         <f aca="false">IF(px/C96&lt;MIN(E20:E29),0,IF(px/C96&gt;MAX(E20:E29),1,PERCENTRANK(E20:E29,px/C96)))</f>
-        <v>0.159</v>
+        <v>0.163</v>
       </c>
       <c r="D134" s="32" t="n">
         <f aca="false">IF(px/D96&lt;MIN(E20:E29),0,IF(px/D96&gt;MAX(E20:E29),1,PERCENTRANK(E20:E29,px/D96)))</f>
-        <v>0.239</v>
+        <v>0.242</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>680</v>
@@ -47787,7 +47787,7 @@
       </c>
       <c r="B158" s="30" t="n">
         <f aca="false">Val!$B$122*B157</f>
-        <v>493.436352755451</v>
+        <v>490.217794593997</v>
       </c>
       <c r="E158" s="4" t="s">
         <v>727</v>
@@ -47989,27 +47989,27 @@
       </c>
       <c r="C9" s="18" t="n">
         <f aca="false">PL!E13</f>
-        <v>13.7383712927123</v>
+        <v>13.6447191069765</v>
       </c>
       <c r="D9" s="11" t="n">
         <f aca="false">C9/B9-1</f>
-        <v>0.215785070151528</v>
+        <v>0.207497266104119</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">PL!E24</f>
-        <v>13.70699613466</v>
+        <v>13.6133439489243</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">E9/B9-1</f>
-        <v>0.213008507492038</v>
+        <v>0.204720703444629</v>
       </c>
       <c r="G9" s="18" t="n">
         <f aca="false">PL!E35</f>
-        <v>13.6756209766078</v>
+        <v>13.5819687908721</v>
       </c>
       <c r="H9" s="11" t="n">
         <f aca="false">G9/B9-1</f>
-        <v>0.210231944832547</v>
+        <v>0.201944140785138</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>746</v>
@@ -48033,27 +48033,27 @@
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">PL!E5</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="D11" s="11" t="n">
         <f aca="false">C11/B11-1</f>
-        <v>0.159828190873112</v>
+        <v>0.153945370778632</v>
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">PL!E16</f>
-        <v>6947.14404523867</v>
+        <v>6911.84712467179</v>
       </c>
       <c r="F11" s="11" t="n">
         <f aca="false">E11/B11-1</f>
-        <v>0.157857340873112</v>
+        <v>0.151974520778632</v>
       </c>
       <c r="G11" s="9" t="n">
         <f aca="false">PL!E27</f>
-        <v>6935.31894523867</v>
+        <v>6900.02202467179</v>
       </c>
       <c r="H11" s="11" t="n">
         <f aca="false">G11/B11-1</f>
-        <v>0.155886490873112</v>
+        <v>0.150003670778632</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>750</v>
@@ -48072,27 +48072,27 @@
       </c>
       <c r="C12" s="18" t="n">
         <f aca="false">PL!E13</f>
-        <v>13.7383712927123</v>
+        <v>13.6447191069765</v>
       </c>
       <c r="D12" s="11" t="n">
         <f aca="false">C12/B12-1</f>
-        <v>0.248942844792025</v>
+        <v>0.240429009725141</v>
       </c>
       <c r="E12" s="18" t="n">
         <f aca="false">PL!E24</f>
-        <v>13.70699613466</v>
+        <v>13.6133439489243</v>
       </c>
       <c r="F12" s="11" t="n">
         <f aca="false">E12/B12-1</f>
-        <v>0.246090557696366</v>
+        <v>0.237576722629482</v>
       </c>
       <c r="G12" s="18" t="n">
         <f aca="false">PL!E35</f>
-        <v>13.6756209766078</v>
+        <v>13.5819687908721</v>
       </c>
       <c r="H12" s="11" t="n">
         <f aca="false">G12/B12-1</f>
-        <v>0.243238270600707</v>
+        <v>0.234724435533824</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>38</v>
@@ -48191,27 +48191,27 @@
       </c>
       <c r="C16" s="11" t="n">
         <f aca="false">Units!D10</f>
-        <v>0.0880523802786935</v>
+        <v>0.0859133291658267</v>
       </c>
       <c r="D16" s="11" t="n">
         <f aca="false">C16-B16</f>
-        <v>-0.00194761972130647</v>
+        <v>-0.00408667083417331</v>
       </c>
       <c r="E16" s="11" t="n">
         <f aca="false">Units!D18</f>
-        <v>0.0880523802786935</v>
+        <v>0.0859133291658267</v>
       </c>
       <c r="F16" s="11" t="n">
         <f aca="false">E16-B16</f>
-        <v>-0.00194761972130647</v>
+        <v>-0.00408667083417331</v>
       </c>
       <c r="G16" s="11" t="n">
         <f aca="false">Units!D26</f>
-        <v>0.0880523802786935</v>
+        <v>0.0859133291658267</v>
       </c>
       <c r="H16" s="11" t="n">
         <f aca="false">G16-B16</f>
-        <v>-0.00194761972130647</v>
+        <v>-0.00408667083417331</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>761</v>
@@ -48227,27 +48227,27 @@
       </c>
       <c r="C17" s="11" t="n">
         <f aca="false">Units!E10</f>
-        <v>0.100655189777327</v>
+        <v>0.100077207336046</v>
       </c>
       <c r="D17" s="11" t="n">
         <f aca="false">C17-B17</f>
-        <v>0.0106551897773269</v>
+        <v>0.0100772073360455</v>
       </c>
       <c r="E17" s="11" t="n">
         <f aca="false">Units!E18</f>
-        <v>0.100655189777327</v>
+        <v>0.100077207336046</v>
       </c>
       <c r="F17" s="11" t="n">
         <f aca="false">E17-B17</f>
-        <v>0.0106551897773269</v>
+        <v>0.0100772073360455</v>
       </c>
       <c r="G17" s="11" t="n">
         <f aca="false">Units!E26</f>
-        <v>0.100655189777327</v>
+        <v>0.100077207336046</v>
       </c>
       <c r="H17" s="11" t="n">
         <f aca="false">G17-B17</f>
-        <v>0.0106551897773269</v>
+        <v>0.0100772073360455</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>761</v>
@@ -48266,27 +48266,27 @@
       </c>
       <c r="C18" s="11" t="n">
         <f aca="false">Units!F10</f>
-        <v>0.103725344659339</v>
+        <v>0.103150082185545</v>
       </c>
       <c r="D18" s="11" t="n">
         <f aca="false">C18-B18</f>
-        <v>0.013725344659339</v>
+        <v>0.0131500821855454</v>
       </c>
       <c r="E18" s="11" t="n">
         <f aca="false">Units!F18</f>
-        <v>0.10175967564377</v>
+        <v>0.101181693202489</v>
       </c>
       <c r="F18" s="11" t="n">
         <f aca="false">E18-B18</f>
-        <v>0.01175967564377</v>
+        <v>0.0111816932024887</v>
       </c>
       <c r="G18" s="11" t="n">
         <f aca="false">Units!F26</f>
-        <v>0.103541308553797</v>
+        <v>0.102963326112516</v>
       </c>
       <c r="H18" s="11" t="n">
         <f aca="false">G18-B18</f>
-        <v>0.0135413085537974</v>
+        <v>0.0129633261125161</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>761</v>
@@ -48385,11 +48385,11 @@
       </c>
       <c r="C4" s="20" t="n">
         <f aca="false">PL!E61</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="D4" s="18" t="n">
         <f aca="false">PL!E69</f>
-        <v>13.7383712927123</v>
+        <v>13.6447191069765</v>
       </c>
       <c r="E4" s="11" t="n">
         <f aca="false">D4/D$4-1</f>
@@ -48397,11 +48397,11 @@
       </c>
       <c r="F4" s="20" t="n">
         <f aca="false">PL!F61</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G4" s="18" t="n">
         <f aca="false">PL!F69</f>
-        <v>16.6102709642527</v>
+        <v>16.5044788870469</v>
       </c>
       <c r="H4" s="11" t="n">
         <f aca="false">G4/G$4-1</f>
@@ -48417,27 +48417,27 @@
       </c>
       <c r="C5" s="20" t="n">
         <f aca="false">E57</f>
-        <v>6188.25124130855</v>
+        <v>6152.95432074166</v>
       </c>
       <c r="D5" s="18" t="n">
         <f aca="false">E65</f>
-        <v>11.6934502307759</v>
+        <v>11.5997980450402</v>
       </c>
       <c r="E5" s="11" t="n">
         <f aca="false">D5/D$4-1</f>
-        <v>-0.148847415633693</v>
+        <v>-0.149869047937438</v>
       </c>
       <c r="F5" s="20" t="n">
         <f aca="false">F57</f>
-        <v>7136.01297584357</v>
+        <v>7096.53933012736</v>
       </c>
       <c r="G5" s="18" t="n">
         <f aca="false">F65</f>
-        <v>14.2921210438455</v>
+        <v>14.1863289666397</v>
       </c>
       <c r="H5" s="11" t="n">
         <f aca="false">G5/G$4-1</f>
-        <v>-0.139561234455244</v>
+        <v>-0.140455808164082</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48446,27 +48446,27 @@
       </c>
       <c r="C6" s="20" t="n">
         <f aca="false">E89</f>
-        <v>7729.6870491688</v>
+        <v>7694.39012860192</v>
       </c>
       <c r="D6" s="18" t="n">
         <f aca="false">E97</f>
-        <v>15.7832923546486</v>
+        <v>15.6896401689129</v>
       </c>
       <c r="E6" s="11" t="n">
         <f aca="false">D6/D$4-1</f>
-        <v>0.148847415633693</v>
+        <v>0.149869047937438</v>
       </c>
       <c r="F6" s="20" t="n">
         <f aca="false">F89</f>
-        <v>8865.93134198398</v>
+        <v>8826.45769626777</v>
       </c>
       <c r="G6" s="18" t="n">
         <f aca="false">F97</f>
-        <v>18.9284208846599</v>
+        <v>18.8226288074541</v>
       </c>
       <c r="H6" s="11" t="n">
         <f aca="false">G6/G$4-1</f>
-        <v>0.139561234455244</v>
+        <v>0.140455808164081</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48478,27 +48478,27 @@
       </c>
       <c r="C7" s="20" t="n">
         <f aca="false">E121</f>
-        <v>6234.88037514896</v>
+        <v>6199.58345458208</v>
       </c>
       <c r="D7" s="18" t="n">
         <f aca="false">E129</f>
-        <v>11.8171698140422</v>
+        <v>11.7235176283065</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false">D7/D$4-1</f>
-        <v>-0.139842011672023</v>
+        <v>-0.140801834292634</v>
       </c>
       <c r="F7" s="20" t="n">
         <f aca="false">F121</f>
-        <v>7188.34379274585</v>
+        <v>7148.87014702964</v>
       </c>
       <c r="G7" s="18" t="n">
         <f aca="false">F129</f>
-        <v>14.4323712214392</v>
+        <v>14.3265791442334</v>
       </c>
       <c r="H7" s="11" t="n">
         <f aca="false">G7/G$4-1</f>
-        <v>-0.131117652896852</v>
+        <v>-0.131958104083057</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48507,27 +48507,27 @@
       </c>
       <c r="C8" s="20" t="n">
         <f aca="false">E153</f>
-        <v>6759.39382124844</v>
+        <v>6729.6685204845</v>
       </c>
       <c r="D8" s="18" t="n">
         <f aca="false">E161</f>
-        <v>13.2088444951781</v>
+        <v>13.129975309326</v>
       </c>
       <c r="E8" s="11" t="n">
         <f aca="false">D8/D$4-1</f>
-        <v>-0.0385436371060298</v>
+        <v>-0.0377247632299992</v>
       </c>
       <c r="F8" s="20" t="n">
         <f aca="false">F153</f>
-        <v>7742.43739563519</v>
+        <v>7709.19466589223</v>
       </c>
       <c r="G8" s="18" t="n">
         <f aca="false">F161</f>
-        <v>15.9173800710785</v>
+        <v>15.8282872759315</v>
       </c>
       <c r="H8" s="11" t="n">
         <f aca="false">G8/G$4-1</f>
-        <v>-0.0417146050576411</v>
+        <v>-0.0409701885011399</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48536,27 +48536,27 @@
       </c>
       <c r="C9" s="20" t="n">
         <f aca="false">E185</f>
-        <v>7158.54446922891</v>
+        <v>7117.67592885908</v>
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">E193</f>
-        <v>14.2678980902465</v>
+        <v>14.1594629046271</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">D9/D$4-1</f>
-        <v>0.0385436371060297</v>
+        <v>0.0377247632299993</v>
       </c>
       <c r="F9" s="20" t="n">
         <f aca="false">F185</f>
-        <v>8259.50692219236</v>
+        <v>8213.8023605029</v>
       </c>
       <c r="G9" s="18" t="n">
         <f aca="false">F193</f>
-        <v>17.3031618574269</v>
+        <v>17.1806704981623</v>
       </c>
       <c r="H9" s="11" t="n">
         <f aca="false">G9/G$4-1</f>
-        <v>0.0417146050576411</v>
+        <v>0.0409701885011393</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48568,27 +48568,27 @@
       </c>
       <c r="C10" s="20" t="n">
         <f aca="false">E217</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">E225</f>
-        <v>12.9172087603935</v>
+        <v>12.8395947739147</v>
       </c>
       <c r="E10" s="11" t="n">
         <f aca="false">D10/D$4-1</f>
-        <v>-0.0597714616109085</v>
+        <v>-0.0590062958973072</v>
       </c>
       <c r="F10" s="20" t="n">
         <f aca="false">F217</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G10" s="18" t="n">
         <f aca="false">F225</f>
-        <v>15.3228379027746</v>
+        <v>15.2351630152606</v>
       </c>
       <c r="H10" s="11" t="n">
         <f aca="false">G10/G$4-1</f>
-        <v>-0.0775082516262874</v>
+        <v>-0.0769073583282005</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48600,27 +48600,27 @@
       </c>
       <c r="C11" s="20" t="n">
         <f aca="false">E249</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="D11" s="18" t="n">
         <f aca="false">E257</f>
-        <v>14.5067562316426</v>
+        <v>14.3980966505722</v>
       </c>
       <c r="E11" s="11" t="n">
         <f aca="false">D11/D$4-1</f>
-        <v>0.0559298422323138</v>
+        <v>0.0552138550958123</v>
       </c>
       <c r="F11" s="20" t="n">
         <f aca="false">F249</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G11" s="18" t="n">
         <f aca="false">F257</f>
-        <v>17.8149583865191</v>
+        <v>17.6922135439994</v>
       </c>
       <c r="H11" s="11" t="n">
         <f aca="false">G11/G$4-1</f>
-        <v>0.0725266568413574</v>
+        <v>0.0719643840366664</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48632,27 +48632,27 @@
       </c>
       <c r="C12" s="20" t="n">
         <f aca="false">E281</f>
-        <v>6943.20234523868</v>
+        <v>6907.90542467179</v>
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">E289</f>
-        <v>13.6965377486426</v>
+        <v>13.6028855629069</v>
       </c>
       <c r="E12" s="11" t="n">
         <f aca="false">D12/D$4-1</f>
-        <v>-0.00304501481131569</v>
+        <v>-0.00306591464006523</v>
       </c>
       <c r="F12" s="20" t="n">
         <f aca="false">F281</f>
-        <v>7967.54654291378</v>
+        <v>7928.07289719757</v>
       </c>
       <c r="G12" s="18" t="n">
         <f aca="false">F289</f>
-        <v>16.5206880213965</v>
+        <v>16.4148959441907</v>
       </c>
       <c r="H12" s="11" t="n">
         <f aca="false">G12/G$4-1</f>
-        <v>-0.00539322585700375</v>
+        <v>-0.00542779590130249</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48664,27 +48664,27 @@
       </c>
       <c r="C13" s="20" t="n">
         <f aca="false">E313</f>
-        <v>6974.73594523868</v>
+        <v>6939.43902467179</v>
       </c>
       <c r="D13" s="18" t="n">
         <f aca="false">E321</f>
-        <v>13.7802048367819</v>
+        <v>13.6865526510462</v>
       </c>
       <c r="E13" s="11" t="n">
         <f aca="false">D13/D$4-1</f>
-        <v>0.00304501481131547</v>
+        <v>0.00306591464006556</v>
       </c>
       <c r="F13" s="20" t="n">
         <f aca="false">F313</f>
-        <v>8035.65911891378</v>
+        <v>7996.18547319757</v>
       </c>
       <c r="G13" s="18" t="n">
         <f aca="false">F321</f>
-        <v>16.7032343955186</v>
+        <v>16.5974423183129</v>
       </c>
       <c r="H13" s="11" t="n">
         <f aca="false">G13/G$4-1</f>
-        <v>0.00559674381387154</v>
+        <v>0.00563261838814344</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48696,27 +48696,27 @@
       </c>
       <c r="C14" s="20" t="n">
         <f aca="false">E345</f>
-        <v>6918.81714523867</v>
+        <v>6883.52022467179</v>
       </c>
       <c r="D14" s="18" t="n">
         <f aca="false">E353</f>
-        <v>13.7339568045147</v>
+        <v>13.6403046187789</v>
       </c>
       <c r="E14" s="11" t="n">
         <f aca="false">D14/D$4-1</f>
-        <v>-0.000321325439789466</v>
+        <v>-0.000323530895946611</v>
       </c>
       <c r="F14" s="20" t="n">
         <f aca="false">F345</f>
-        <v>7916.65295891378</v>
+        <v>7877.17931319757</v>
       </c>
       <c r="G14" s="18" t="n">
         <f aca="false">F353</f>
-        <v>16.5915428325052</v>
+        <v>16.4857507552995</v>
       </c>
       <c r="H14" s="11" t="n">
         <f aca="false">G14/G$4-1</f>
-        <v>-0.00112750308455511</v>
+        <v>-0.00113473026780586</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48725,27 +48725,27 @@
       </c>
       <c r="C15" s="20" t="n">
         <f aca="false">E377</f>
-        <v>6999.12114523867</v>
+        <v>6963.82422467179</v>
       </c>
       <c r="D15" s="18" t="n">
         <f aca="false">E385</f>
-        <v>13.7427857809099</v>
+        <v>13.6491335951742</v>
       </c>
       <c r="E15" s="11" t="n">
         <f aca="false">D15/D$4-1</f>
-        <v>0.000321325439789577</v>
+        <v>0.000323530895947055</v>
       </c>
       <c r="F15" s="20" t="n">
         <f aca="false">F377</f>
-        <v>8093.32175891378</v>
+        <v>8053.84811319757</v>
       </c>
       <c r="G15" s="18" t="n">
         <f aca="false">F385</f>
-        <v>16.6307827275952</v>
+        <v>16.5249906503894</v>
       </c>
       <c r="H15" s="11" t="n">
         <f aca="false">G15/G$4-1</f>
-        <v>0.00123488433070351</v>
+        <v>0.00124279981712072</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48757,27 +48757,27 @@
       </c>
       <c r="C16" s="20" t="n">
         <f aca="false">E409</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="D16" s="18" t="n">
         <f aca="false">E417</f>
-        <v>13.5684134971038</v>
+        <v>13.474761311368</v>
       </c>
       <c r="E16" s="11" t="n">
         <f aca="false">D16/D$4-1</f>
-        <v>-0.0123710294318998</v>
+        <v>-0.0124559394939548</v>
       </c>
       <c r="F16" s="20" t="n">
         <f aca="false">F409</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G16" s="18" t="n">
         <f aca="false">F417</f>
-        <v>16.4214289691322</v>
+        <v>16.3156368919264</v>
       </c>
       <c r="H16" s="11" t="n">
         <f aca="false">G16/G$4-1</f>
-        <v>-0.0113689894359325</v>
+        <v>-0.0114418635337086</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48789,27 +48789,27 @@
       </c>
       <c r="C17" s="20" t="n">
         <f aca="false">E441</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="D17" s="18" t="n">
         <f aca="false">E449</f>
-        <v>13.8597697181469</v>
+        <v>13.7661175324112</v>
       </c>
       <c r="E17" s="11" t="n">
         <f aca="false">D17/D$4-1</f>
-        <v>0.00883644959421415</v>
+        <v>0.00889709963853935</v>
       </c>
       <c r="F17" s="20" t="n">
         <f aca="false">F441</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G17" s="18" t="n">
         <f aca="false">F449</f>
-        <v>16.7451581036246</v>
+        <v>16.6393660264188</v>
       </c>
       <c r="H17" s="11" t="n">
         <f aca="false">G17/G$4-1</f>
-        <v>0.0081207067399518</v>
+        <v>0.00817275966693476</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48818,27 +48818,27 @@
       </c>
       <c r="C18" s="20" t="n">
         <f aca="false">E473</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="D18" s="18" t="n">
         <f aca="false">E481</f>
-        <v>14.0887975479087</v>
+        <v>13.9927711760599</v>
       </c>
       <c r="E18" s="11" t="n">
         <f aca="false">D18/D$4-1</f>
-        <v>0.0255071178184174</v>
+        <v>0.0255081886519311</v>
       </c>
       <c r="F18" s="20" t="n">
         <f aca="false">F473</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G18" s="18" t="n">
         <f aca="false">F481</f>
-        <v>17.0335246914911</v>
+        <v>16.9250506685454</v>
       </c>
       <c r="H18" s="11" t="n">
         <f aca="false">G18/G$4-1</f>
-        <v>0.0254814462779833</v>
+        <v>0.0254822817719194</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48847,27 +48847,27 @@
       </c>
       <c r="C19" s="20" t="n">
         <f aca="false">E505</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="D19" s="18" t="n">
         <f aca="false">E513</f>
-        <v>13.2834937826184</v>
+        <v>13.1929234546247</v>
       </c>
       <c r="E19" s="11" t="n">
         <f aca="false">D19/D$4-1</f>
-        <v>-0.0331100026635048</v>
+        <v>-0.0331113926794496</v>
       </c>
       <c r="F19" s="20" t="n">
         <f aca="false">F505</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G19" s="18" t="n">
         <f aca="false">F513</f>
-        <v>16.0608583596628</v>
+        <v>15.9585476334753</v>
       </c>
       <c r="H19" s="11" t="n">
         <f aca="false">G19/G$4-1</f>
-        <v>-0.0330766792289166</v>
+        <v>-0.0330777637578176</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48876,27 +48876,27 @@
       </c>
       <c r="C20" s="20" t="n">
         <f aca="false">E537</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="D20" s="18" t="n">
         <f aca="false">E545</f>
-        <v>13.6009875797852</v>
+        <v>13.5082719159068</v>
       </c>
       <c r="E20" s="11" t="n">
         <f aca="false">D20/D$4-1</f>
-        <v>-0.0099999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="F20" s="20" t="n">
         <f aca="false">F537</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G20" s="18" t="n">
         <f aca="false">F545</f>
-        <v>16.2797265720641</v>
+        <v>16.1760397571947</v>
       </c>
       <c r="H20" s="11" t="n">
         <f aca="false">G20/G$4-1</f>
-        <v>-0.0198999999999999</v>
+        <v>-0.0199</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48905,23 +48905,23 @@
       </c>
       <c r="C21" s="20" t="n">
         <f aca="false">E569</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="D21" s="18" t="n">
         <f aca="false">E577</f>
-        <v>13.8785587548828</v>
+        <v>13.7839509345988</v>
       </c>
       <c r="E21" s="11" t="n">
         <f aca="false">D21/D$4-1</f>
-        <v>0.0102040816326532</v>
+        <v>0.010204081632653</v>
       </c>
       <c r="F21" s="20" t="n">
         <f aca="false">F569</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G21" s="18" t="n">
         <f aca="false">F577</f>
-        <v>16.9509856018993</v>
+        <v>16.8430234872915</v>
       </c>
       <c r="H21" s="11" t="n">
         <f aca="false">G21/G$4-1</f>
@@ -48937,27 +48937,27 @@
       </c>
       <c r="C22" s="20" t="n">
         <f aca="false">PL!E91</f>
-        <v>6947.14404523867</v>
+        <v>6911.84712467179</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">PL!E99</f>
-        <v>13.70699613466</v>
+        <v>13.6133439489243</v>
       </c>
       <c r="E22" s="11" t="n">
         <f aca="false">D22/D$4-1</f>
-        <v>-0.00228376110848683</v>
+        <v>-0.00229943598004911</v>
       </c>
       <c r="F22" s="20" t="n">
         <f aca="false">PL!F91</f>
-        <v>7081.7701876497</v>
+        <v>7046.47326708282</v>
       </c>
       <c r="G22" s="18" t="n">
         <f aca="false">PL!F99</f>
-        <v>14.1467466520876</v>
+        <v>14.0521484846777</v>
       </c>
       <c r="H22" s="11" t="n">
         <f aca="false">G22/G$4-1</f>
-        <v>-0.148313312736858</v>
+        <v>-0.14858575173154</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48969,27 +48969,27 @@
       </c>
       <c r="C23" s="20" t="n">
         <f aca="false">PL!E121</f>
-        <v>6935.31894523867</v>
+        <v>6900.02202467179</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">PL!E129</f>
-        <v>13.6756209766078</v>
+        <v>13.5819687908721</v>
       </c>
       <c r="E23" s="11" t="n">
         <f aca="false">D23/D$4-1</f>
-        <v>-0.00456752221697332</v>
+        <v>-0.00459887196009812</v>
       </c>
       <c r="F23" s="20" t="n">
         <f aca="false">PL!F121</f>
-        <v>6522.53289805538</v>
+        <v>6494.29536160187</v>
       </c>
       <c r="G23" s="18" t="n">
         <f aca="false">PL!F129</f>
-        <v>12.3127499632354</v>
+        <v>12.2386393886303</v>
       </c>
       <c r="H23" s="11" t="n">
         <f aca="false">G23/G$4-1</f>
-        <v>-0.258726724583008</v>
+        <v>-0.258465567293042</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49073,15 +49073,15 @@
       </c>
       <c r="E43" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F43" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G43" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49191,15 +49191,15 @@
       </c>
       <c r="E47" s="9" t="n">
         <f aca="false">E43*1000*E46</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F47" s="9" t="n">
         <f aca="false">F43*1000*F46</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G47" s="9" t="n">
         <f aca="false">G43*1000*G46</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49250,15 +49250,15 @@
       </c>
       <c r="E49" s="9" t="n">
         <f aca="false">E45+E47+E48</f>
-        <v>5320.87564130855</v>
+        <v>5285.57872074166</v>
       </c>
       <c r="F49" s="9" t="n">
         <f aca="false">F45+F47+F48</f>
-        <v>6190.41388784357</v>
+        <v>6150.94024212736</v>
       </c>
       <c r="G49" s="9" t="n">
         <f aca="false">G45+G47+G48</f>
-        <v>7067.89117546612</v>
+        <v>7026.91283960606</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49306,15 +49306,15 @@
       </c>
       <c r="E51" s="9" t="n">
         <f aca="false">E49+E50</f>
-        <v>5746.57924130855</v>
+        <v>5711.28232074166</v>
       </c>
       <c r="F51" s="9" t="n">
         <f aca="false">F49+F50</f>
-        <v>6650.17377584357</v>
+        <v>6610.70013012736</v>
       </c>
       <c r="G51" s="9" t="n">
         <f aca="false">G49+G50</f>
-        <v>7564.43185450612</v>
+        <v>7523.45351864606</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49334,15 +49334,15 @@
       </c>
       <c r="E52" s="9" t="n">
         <f aca="false">t_inc*E51-t_fix+0*E51</f>
-        <v>2144.10355522555</v>
+        <v>2127.06727652993</v>
       </c>
       <c r="F52" s="9" t="n">
         <f aca="false">t_inc*F51-t_fix+0*F51</f>
-        <v>2580.22908886815</v>
+        <v>2561.17688774826</v>
       </c>
       <c r="G52" s="9" t="n">
         <f aca="false">t_inc*G51-t_fix+0*G51</f>
-        <v>3021.50144854323</v>
+        <v>3001.72299934759</v>
       </c>
       <c r="H52" s="4" t="s">
         <v>500</v>
@@ -49365,15 +49365,15 @@
       </c>
       <c r="E53" s="11" t="n">
         <f aca="false">E52/E51</f>
-        <v>0.373109543119659</v>
+        <v>0.37243252164318</v>
       </c>
       <c r="F53" s="11" t="n">
         <f aca="false">F52/F51</f>
-        <v>0.387994235314678</v>
+        <v>0.387428991987708</v>
       </c>
       <c r="G53" s="11" t="n">
         <f aca="false">G52/G51</f>
-        <v>0.399435345133465</v>
+        <v>0.398982062148473</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49477,15 +49477,15 @@
       </c>
       <c r="E57" s="9" t="n">
         <f aca="false">E51+E54</f>
-        <v>6188.25124130855</v>
+        <v>6152.95432074166</v>
       </c>
       <c r="F57" s="9" t="n">
         <f aca="false">F51+F54</f>
-        <v>7136.01297584357</v>
+        <v>7096.53933012736</v>
       </c>
       <c r="G57" s="9" t="n">
         <f aca="false">G51+G54</f>
-        <v>8098.85497450612</v>
+        <v>8057.87663864606</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49524,15 +49524,15 @@
       </c>
       <c r="E59" s="9" t="n">
         <f aca="false">E52+E55+E56</f>
-        <v>2142.53699522555</v>
+        <v>2125.50071652993</v>
       </c>
       <c r="F59" s="9" t="n">
         <f aca="false">F52+F55+F56</f>
-        <v>2589.26265686815</v>
+        <v>2570.21045574826</v>
       </c>
       <c r="G59" s="9" t="n">
         <f aca="false">G52+G55+G56</f>
-        <v>3037.82260454323</v>
+        <v>3018.04415534759</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49552,15 +49552,15 @@
       </c>
       <c r="E60" s="11" t="n">
         <f aca="false">E59/E57</f>
-        <v>0.346226568973708</v>
+        <v>0.345443929165027</v>
       </c>
       <c r="F60" s="11" t="n">
         <f aca="false">F59/F57</f>
-        <v>0.362844443477496</v>
+        <v>0.362178004825083</v>
       </c>
       <c r="G60" s="11" t="n">
         <f aca="false">G59/G57</f>
-        <v>0.375092851286484</v>
+        <v>0.374545837655651</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49580,15 +49580,15 @@
       </c>
       <c r="E61" s="9" t="n">
         <f aca="false">E59*etr</f>
-        <v>303.720464846116</v>
+        <v>301.30544634412</v>
       </c>
       <c r="F61" s="9" t="n">
         <f aca="false">F59*etr</f>
-        <v>367.047131277142</v>
+        <v>364.346340862147</v>
       </c>
       <c r="G61" s="9" t="n">
         <f aca="false">G59*etr</f>
-        <v>430.633821319281</v>
+        <v>427.830079868365</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49636,15 +49636,15 @@
       </c>
       <c r="E63" s="9" t="n">
         <f aca="false">E59-E61+E62</f>
-        <v>1825.61653037943</v>
+        <v>1810.99527018581</v>
       </c>
       <c r="F63" s="9" t="n">
         <f aca="false">F59-F61+F62</f>
-        <v>2209.01552559101</v>
+        <v>2192.66411488611</v>
       </c>
       <c r="G63" s="9" t="n">
         <f aca="false">G59-G61+G62</f>
-        <v>2593.98878322394</v>
+        <v>2577.01407547922</v>
       </c>
       <c r="H63" s="8" t="s">
         <v>505</v>
@@ -49695,15 +49695,15 @@
       </c>
       <c r="E65" s="18" t="n">
         <f aca="false">E63/E64</f>
-        <v>11.6934502307759</v>
+        <v>11.5997980450402</v>
       </c>
       <c r="F65" s="18" t="n">
         <f aca="false">F63/F64</f>
-        <v>14.2921210438455</v>
+        <v>14.1863289666397</v>
       </c>
       <c r="G65" s="18" t="n">
         <f aca="false">G63/G64</f>
-        <v>16.9523853804547</v>
+        <v>16.8414512895788</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49723,15 +49723,15 @@
       </c>
       <c r="E66" s="11" t="n">
         <f aca="false">E45/E57</f>
-        <v>0.611250451955929</v>
+        <v>0.614756939656712</v>
       </c>
       <c r="F66" s="11" t="n">
         <f aca="false">F45/F57</f>
-        <v>0.594883147302844</v>
+        <v>0.598192113195485</v>
       </c>
       <c r="G66" s="11" t="n">
         <f aca="false">G45/G57</f>
-        <v>0.582850014616031</v>
+        <v>0.585814098670189</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49751,15 +49751,15 @@
       </c>
       <c r="E67" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E66-D66)</f>
-        <v>0.586793584924919</v>
+        <v>0.587880628944498</v>
       </c>
       <c r="F67" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F66-D66)</f>
-        <v>0.581719567230289</v>
+        <v>0.582745377639887</v>
       </c>
       <c r="G67" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G66-D66)</f>
-        <v>0.577989183427407</v>
+        <v>0.578908077237838</v>
       </c>
       <c r="H67" s="8" t="s">
         <v>509</v>
@@ -49841,15 +49841,15 @@
       </c>
       <c r="E75" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F75" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G75" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49959,15 +49959,15 @@
       </c>
       <c r="E79" s="9" t="n">
         <f aca="false">E75*1000*E78</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F79" s="9" t="n">
         <f aca="false">F75*1000*F78</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G79" s="9" t="n">
         <f aca="false">G75*1000*G78</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50018,15 +50018,15 @@
       </c>
       <c r="E81" s="9" t="n">
         <f aca="false">E77+E79+E80</f>
-        <v>6862.31144916881</v>
+        <v>6827.01452860192</v>
       </c>
       <c r="F81" s="9" t="n">
         <f aca="false">F77+F79+F80</f>
-        <v>7920.33225398398</v>
+        <v>7880.85860826777</v>
       </c>
       <c r="G81" s="9" t="n">
         <f aca="false">G77+G79+G80</f>
-        <v>8991.50879556689</v>
+        <v>8950.53045970683</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50074,15 +50074,15 @@
       </c>
       <c r="E83" s="9" t="n">
         <f aca="false">E81+E82</f>
-        <v>7288.01504916881</v>
+        <v>7252.71812860192</v>
       </c>
       <c r="F83" s="9" t="n">
         <f aca="false">F81+F82</f>
-        <v>8380.09214198398</v>
+        <v>8340.61849626777</v>
       </c>
       <c r="G83" s="9" t="n">
         <f aca="false">G81+G82</f>
-        <v>9488.04947460689</v>
+        <v>9447.07113874683</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50102,15 +50102,15 @@
       </c>
       <c r="E84" s="9" t="n">
         <f aca="false">t_inc*E83-t_fix+0*E83</f>
-        <v>2888.08715471114</v>
+        <v>2871.05087601553</v>
       </c>
       <c r="F84" s="9" t="n">
         <f aca="false">t_inc*F83-t_fix+0*F83</f>
-        <v>3415.18496980358</v>
+        <v>3396.13276868369</v>
       </c>
       <c r="G84" s="9" t="n">
         <f aca="false">t_inc*G83-t_fix+0*G83</f>
-        <v>3949.947481611</v>
+        <v>3930.16903241537</v>
       </c>
       <c r="H84" s="4" t="s">
         <v>500</v>
@@ -50133,15 +50133,15 @@
       </c>
       <c r="E85" s="11" t="n">
         <f aca="false">E84/E83</f>
-        <v>0.396278977914642</v>
+        <v>0.395858604333899</v>
       </c>
       <c r="F85" s="11" t="n">
         <f aca="false">F84/F83</f>
-        <v>0.407535491488646</v>
+        <v>0.407179967553171</v>
       </c>
       <c r="G85" s="11" t="n">
         <f aca="false">G84/G83</f>
-        <v>0.416307639645256</v>
+        <v>0.416019840932066</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50245,15 +50245,15 @@
       </c>
       <c r="E89" s="9" t="n">
         <f aca="false">E83+E86</f>
-        <v>7729.6870491688</v>
+        <v>7694.39012860192</v>
       </c>
       <c r="F89" s="9" t="n">
         <f aca="false">F83+F86</f>
-        <v>8865.93134198398</v>
+        <v>8826.45769626777</v>
       </c>
       <c r="G89" s="9" t="n">
         <f aca="false">G83+G86</f>
-        <v>10022.4725946069</v>
+        <v>9981.49425874683</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50292,15 +50292,15 @@
       </c>
       <c r="E91" s="9" t="n">
         <f aca="false">E84+E87+E88</f>
-        <v>2886.52059471114</v>
+        <v>2869.48431601553</v>
       </c>
       <c r="F91" s="9" t="n">
         <f aca="false">F84+F87+F88</f>
-        <v>3424.21853780358</v>
+        <v>3405.16633668369</v>
       </c>
       <c r="G91" s="9" t="n">
         <f aca="false">G84+G87+G88</f>
-        <v>3966.268637611</v>
+        <v>3946.49018841537</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50320,15 +50320,15 @@
       </c>
       <c r="E92" s="11" t="n">
         <f aca="false">E91/E89</f>
-        <v>0.3734330479811</v>
+        <v>0.372932002154265</v>
       </c>
       <c r="F92" s="11" t="n">
         <f aca="false">F91/F89</f>
-        <v>0.386222090575915</v>
+        <v>0.385790818226382</v>
       </c>
       <c r="G92" s="11" t="n">
         <f aca="false">G91/G89</f>
-        <v>0.395737538833008</v>
+        <v>0.395380700134856</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50348,15 +50348,15 @@
       </c>
       <c r="E93" s="9" t="n">
         <f aca="false">E91*etr</f>
-        <v>409.185642426335</v>
+        <v>406.770623924339</v>
       </c>
       <c r="F93" s="9" t="n">
         <f aca="false">F91*etr</f>
-        <v>485.40830256558</v>
+        <v>482.707512150585</v>
       </c>
       <c r="G93" s="9" t="n">
         <f aca="false">G91*etr</f>
-        <v>562.24791310685</v>
+        <v>559.444171655934</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50404,15 +50404,15 @@
       </c>
       <c r="E95" s="9" t="n">
         <f aca="false">E91-E93+E94</f>
-        <v>2464.13495228481</v>
+        <v>2449.51369209119</v>
       </c>
       <c r="F95" s="9" t="n">
         <f aca="false">F91-F93+F94</f>
-        <v>2925.610235238</v>
+        <v>2909.2588245331</v>
       </c>
       <c r="G95" s="9" t="n">
         <f aca="false">G91-G93+G94</f>
-        <v>3390.82072450415</v>
+        <v>3373.84601675943</v>
       </c>
       <c r="H95" s="8" t="s">
         <v>505</v>
@@ -50463,15 +50463,15 @@
       </c>
       <c r="E97" s="18" t="n">
         <f aca="false">E95/E96</f>
-        <v>15.7832923546486</v>
+        <v>15.6896401689129</v>
       </c>
       <c r="F97" s="18" t="n">
         <f aca="false">F95/F96</f>
-        <v>18.9284208846599</v>
+        <v>18.8226288074541</v>
       </c>
       <c r="G97" s="18" t="n">
         <f aca="false">G95/G96</f>
-        <v>22.1598875251822</v>
+        <v>22.0489534343064</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50491,15 +50491,15 @@
       </c>
       <c r="E98" s="11" t="n">
         <f aca="false">E77/E89</f>
-        <v>0.688773962265323</v>
+        <v>0.691933614873038</v>
       </c>
       <c r="F98" s="11" t="n">
         <f aca="false">F77/F89</f>
-        <v>0.673929449025837</v>
+        <v>0.676943393376334</v>
       </c>
       <c r="G98" s="11" t="n">
         <f aca="false">G77/G89</f>
-        <v>0.662913796735144</v>
+        <v>0.665635343580204</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50519,15 +50519,15 @@
       </c>
       <c r="E99" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E98-D98)</f>
-        <v>0.610826598997611</v>
+        <v>0.611806120890815</v>
       </c>
       <c r="F99" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F98-D98)</f>
-        <v>0.606224660899568</v>
+        <v>0.607159011868722</v>
       </c>
       <c r="G99" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G98-D98)</f>
-        <v>0.602809705546469</v>
+        <v>0.603653410551129</v>
       </c>
       <c r="H99" s="8" t="s">
         <v>509</v>
@@ -50609,15 +50609,15 @@
       </c>
       <c r="E107" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F107" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G107" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50727,15 +50727,15 @@
       </c>
       <c r="E111" s="9" t="n">
         <f aca="false">E107*1000*E110</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F111" s="9" t="n">
         <f aca="false">F107*1000*F110</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G111" s="9" t="n">
         <f aca="false">G107*1000*G110</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50786,15 +50786,15 @@
       </c>
       <c r="E113" s="9" t="n">
         <f aca="false">E109+E111+E112</f>
-        <v>5367.50477514896</v>
+        <v>5332.20785458208</v>
       </c>
       <c r="F113" s="9" t="n">
         <f aca="false">F109+F111+F112</f>
-        <v>6242.74470474585</v>
+        <v>6203.27105902964</v>
       </c>
       <c r="G113" s="9" t="n">
         <f aca="false">G109+G111+G112</f>
-        <v>7126.08148284581</v>
+        <v>7085.10314698575</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50842,15 +50842,15 @@
       </c>
       <c r="E115" s="9" t="n">
         <f aca="false">E113+E114</f>
-        <v>5793.20837514896</v>
+        <v>5757.91145458208</v>
       </c>
       <c r="F115" s="9" t="n">
         <f aca="false">F113+F114</f>
-        <v>6702.50459274585</v>
+        <v>6663.03094702964</v>
       </c>
       <c r="G115" s="9" t="n">
         <f aca="false">G113+G114</f>
-        <v>7622.62216188581</v>
+        <v>7581.64382602575</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50870,15 +50870,15 @@
       </c>
       <c r="E116" s="9" t="n">
         <f aca="false">t_inc*E115-t_fix+0*E115</f>
-        <v>2166.60939728435</v>
+        <v>2149.57311858874</v>
       </c>
       <c r="F116" s="9" t="n">
         <f aca="false">t_inc*F115-t_fix+0*F115</f>
-        <v>2605.48688379185</v>
+        <v>2586.43468267195</v>
       </c>
       <c r="G116" s="9" t="n">
         <f aca="false">t_inc*G115-t_fix+0*G115</f>
-        <v>3049.58736306445</v>
+        <v>3029.80891386881</v>
       </c>
       <c r="H116" s="4" t="s">
         <v>500</v>
@@ -50901,15 +50901,15 @@
       </c>
       <c r="E117" s="11" t="n">
         <f aca="false">E116/E115</f>
-        <v>0.373991276850738</v>
+        <v>0.37332514324758</v>
       </c>
       <c r="F117" s="11" t="n">
         <f aca="false">F116/F115</f>
-        <v>0.388733323153822</v>
+        <v>0.388176897756265</v>
       </c>
       <c r="G117" s="11" t="n">
         <f aca="false">G116/G115</f>
-        <v>0.400070644759597</v>
+        <v>0.399624274549576</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51013,15 +51013,15 @@
       </c>
       <c r="E121" s="9" t="n">
         <f aca="false">E115+E118</f>
-        <v>6234.88037514896</v>
+        <v>6199.58345458208</v>
       </c>
       <c r="F121" s="9" t="n">
         <f aca="false">F115+F118</f>
-        <v>7188.34379274585</v>
+        <v>7148.87014702964</v>
       </c>
       <c r="G121" s="9" t="n">
         <f aca="false">G115+G118</f>
-        <v>8157.04528188582</v>
+        <v>8116.06694602575</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51060,15 +51060,15 @@
       </c>
       <c r="E123" s="9" t="n">
         <f aca="false">E116+E119+E120</f>
-        <v>2165.04283728435</v>
+        <v>2148.00655858873</v>
       </c>
       <c r="F123" s="9" t="n">
         <f aca="false">F116+F119+F120</f>
-        <v>2614.52045179185</v>
+        <v>2595.46825067195</v>
       </c>
       <c r="G123" s="9" t="n">
         <f aca="false">G116+G119+G120</f>
-        <v>3065.90851906445</v>
+        <v>3046.13006986881</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51088,15 +51088,15 @@
       </c>
       <c r="E124" s="11" t="n">
         <f aca="false">E123/E121</f>
-        <v>0.347246892805481</v>
+        <v>0.346475948638316</v>
       </c>
       <c r="F124" s="11" t="n">
         <f aca="false">F123/F121</f>
-        <v>0.363716667868655</v>
+        <v>0.363059923776958</v>
       </c>
       <c r="G124" s="11" t="n">
         <f aca="false">G123/G121</f>
-        <v>0.375860181366512</v>
+        <v>0.375320963975098</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51116,15 +51116,15 @@
       </c>
       <c r="E125" s="9" t="n">
         <f aca="false">E123*etr</f>
-        <v>306.910834406634</v>
+        <v>304.495815904639</v>
       </c>
       <c r="F125" s="9" t="n">
         <f aca="false">F123*etr</f>
-        <v>370.627610509149</v>
+        <v>367.926820094154</v>
       </c>
       <c r="G125" s="9" t="n">
         <f aca="false">G123*etr</f>
-        <v>434.615207420442</v>
+        <v>431.811465969526</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51172,15 +51172,15 @@
       </c>
       <c r="E127" s="9" t="n">
         <f aca="false">E123-E125+E126</f>
-        <v>1844.93200287771</v>
+        <v>1830.3107426841</v>
       </c>
       <c r="F127" s="9" t="n">
         <f aca="false">F123-F125+F126</f>
-        <v>2230.6928412827</v>
+        <v>2214.3414305778</v>
       </c>
       <c r="G127" s="9" t="n">
         <f aca="false">G123-G125+G126</f>
-        <v>2618.09331164401</v>
+        <v>2601.11860389929</v>
       </c>
       <c r="H127" s="8" t="s">
         <v>505</v>
@@ -51231,15 +51231,15 @@
       </c>
       <c r="E129" s="18" t="n">
         <f aca="false">E127/E128</f>
-        <v>11.8171698140422</v>
+        <v>11.7235176283065</v>
       </c>
       <c r="F129" s="18" t="n">
         <f aca="false">F127/F128</f>
-        <v>14.4323712214392</v>
+        <v>14.3265791442334</v>
       </c>
       <c r="G129" s="18" t="n">
         <f aca="false">G127/G128</f>
-        <v>17.1099146873791</v>
+        <v>16.9989805965033</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51259,15 +51259,15 @@
       </c>
       <c r="E130" s="11" t="n">
         <f aca="false">E109/E121</f>
-        <v>0.620749019760436</v>
+        <v>0.62428321346925</v>
       </c>
       <c r="F130" s="11" t="n">
         <f aca="false">F109/F121</f>
-        <v>0.604248379093551</v>
+        <v>0.607584834498444</v>
       </c>
       <c r="G130" s="11" t="n">
         <f aca="false">G109/G121</f>
-        <v>0.592113001811193</v>
+        <v>0.59510260325444</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51287,15 +51287,15 @@
       </c>
       <c r="E131" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E130-D130)</f>
-        <v>0.589738229882366</v>
+        <v>0.590833863023855</v>
       </c>
       <c r="F131" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F130-D130)</f>
-        <v>0.584622876774992</v>
+        <v>0.58565720919078</v>
       </c>
       <c r="G131" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G130-D130)</f>
-        <v>0.580860796190142</v>
+        <v>0.581787600630119</v>
       </c>
       <c r="H131" s="8" t="s">
         <v>509</v>
@@ -51377,15 +51377,15 @@
       </c>
       <c r="E139" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F139" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G139" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51495,15 +51495,15 @@
       </c>
       <c r="E143" s="9" t="n">
         <f aca="false">E139*1000*E142</f>
-        <v>1064.75975398366</v>
+        <v>1035.03445321972</v>
       </c>
       <c r="F143" s="9" t="n">
         <f aca="false">F139*1000*F142</f>
-        <v>1379.31586651567</v>
+        <v>1346.07313677271</v>
       </c>
       <c r="G143" s="9" t="n">
         <f aca="false">G139*1000*G142</f>
-        <v>1688.99631198906</v>
+        <v>1654.48640747945</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51554,15 +51554,15 @@
       </c>
       <c r="E145" s="9" t="n">
         <f aca="false">E141+E143+E144</f>
-        <v>5892.01822124844</v>
+        <v>5862.2929204845</v>
       </c>
       <c r="F145" s="9" t="n">
         <f aca="false">F141+F143+F144</f>
-        <v>6796.83830763519</v>
+        <v>6763.59557789223</v>
       </c>
       <c r="G145" s="9" t="n">
         <f aca="false">G141+G143+G144</f>
-        <v>7713.119663127</v>
+        <v>7678.6097586174</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51610,15 +51610,15 @@
       </c>
       <c r="E147" s="9" t="n">
         <f aca="false">E145+E146</f>
-        <v>6317.72182124844</v>
+        <v>6287.9965204845</v>
       </c>
       <c r="F147" s="9" t="n">
         <f aca="false">F145+F146</f>
-        <v>7256.59819563519</v>
+        <v>7223.35546589223</v>
       </c>
       <c r="G147" s="9" t="n">
         <f aca="false">G145+G146</f>
-        <v>8209.660342167</v>
+        <v>8175.1504376574</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51638,15 +51638,15 @@
       </c>
       <c r="E148" s="9" t="n">
         <f aca="false">t_inc*E147-t_fix+0*E147</f>
-        <v>2419.76908101415</v>
+        <v>2405.4219793409</v>
       </c>
       <c r="F148" s="9" t="n">
         <f aca="false">t_inc*F147-t_fix+0*F147</f>
-        <v>2872.92361455121</v>
+        <v>2856.87880385927</v>
       </c>
       <c r="G148" s="9" t="n">
         <f aca="false">t_inc*G147-t_fix+0*G147</f>
-        <v>3332.92499942528</v>
+        <v>3316.2685789347</v>
       </c>
       <c r="H148" s="4" t="s">
         <v>500</v>
@@ -51669,15 +51669,15 @@
       </c>
       <c r="E149" s="11" t="n">
         <f aca="false">E148/E147</f>
-        <v>0.383012919764165</v>
+        <v>0.382541875063818</v>
       </c>
       <c r="F149" s="11" t="n">
         <f aca="false">F148/F147</f>
-        <v>0.395905014594753</v>
+        <v>0.395505775307485</v>
       </c>
       <c r="G149" s="11" t="n">
         <f aca="false">G148/G147</f>
-        <v>0.405975991760157</v>
+        <v>0.405652300128801</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51781,15 +51781,15 @@
       </c>
       <c r="E153" s="9" t="n">
         <f aca="false">E147+E150</f>
-        <v>6759.39382124844</v>
+        <v>6729.6685204845</v>
       </c>
       <c r="F153" s="9" t="n">
         <f aca="false">F147+F150</f>
-        <v>7742.43739563519</v>
+        <v>7709.19466589223</v>
       </c>
       <c r="G153" s="9" t="n">
         <f aca="false">G147+G150</f>
-        <v>8744.083462167</v>
+        <v>8709.5735576574</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51828,15 +51828,15 @@
       </c>
       <c r="E155" s="9" t="n">
         <f aca="false">E148+E151+E152</f>
-        <v>2418.20252101415</v>
+        <v>2403.8554193409</v>
       </c>
       <c r="F155" s="9" t="n">
         <f aca="false">F148+F151+F152</f>
-        <v>2881.95718255121</v>
+        <v>2865.91237185927</v>
       </c>
       <c r="G155" s="9" t="n">
         <f aca="false">G148+G151+G152</f>
-        <v>3349.24615542528</v>
+        <v>3332.5897349347</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51856,15 +51856,15 @@
       </c>
       <c r="E156" s="11" t="n">
         <f aca="false">E155/E153</f>
-        <v>0.357754346759975</v>
+        <v>0.357202648544098</v>
       </c>
       <c r="F156" s="11" t="n">
         <f aca="false">F155/F153</f>
-        <v>0.37222867106112</v>
+        <v>0.371752497642706</v>
       </c>
       <c r="G156" s="11" t="n">
         <f aca="false">G155/G153</f>
-        <v>0.383029984779589</v>
+        <v>0.382635236142498</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51884,15 +51884,15 @@
       </c>
       <c r="E157" s="9" t="n">
         <f aca="false">E155*etr</f>
-        <v>342.79809189346</v>
+        <v>340.764284122998</v>
       </c>
       <c r="F157" s="9" t="n">
         <f aca="false">F155*etr</f>
-        <v>408.538745002585</v>
+        <v>406.264274422808</v>
       </c>
       <c r="G157" s="9" t="n">
         <f aca="false">G155*etr</f>
-        <v>474.780412882787</v>
+        <v>472.41924209071</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51940,15 +51940,15 @@
       </c>
       <c r="E159" s="9" t="n">
         <f aca="false">E155-E157+E158</f>
-        <v>2062.20442912069</v>
+        <v>2049.89113521791</v>
       </c>
       <c r="F159" s="9" t="n">
         <f aca="false">F155-F157+F158</f>
-        <v>2460.21843754862</v>
+        <v>2446.44809743646</v>
       </c>
       <c r="G159" s="9" t="n">
         <f aca="false">G155-G157+G158</f>
-        <v>2861.26574254249</v>
+        <v>2846.97049284399</v>
       </c>
       <c r="H159" s="8" t="s">
         <v>505</v>
@@ -51999,15 +51999,15 @@
       </c>
       <c r="E161" s="18" t="n">
         <f aca="false">E159/E160</f>
-        <v>13.2088444951781</v>
+        <v>13.129975309326</v>
       </c>
       <c r="F161" s="18" t="n">
         <f aca="false">F159/F160</f>
-        <v>15.9173800710785</v>
+        <v>15.8282872759315</v>
       </c>
       <c r="G161" s="18" t="n">
         <f aca="false">G159/G160</f>
-        <v>18.6991092086328</v>
+        <v>18.6056860668035</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52027,15 +52027,15 @@
       </c>
       <c r="E162" s="11" t="n">
         <f aca="false">E141/E153</f>
-        <v>0.673623906582179</v>
+        <v>0.6765993389031</v>
       </c>
       <c r="F162" s="11" t="n">
         <f aca="false">F141/F153</f>
-        <v>0.660005729489626</v>
+        <v>0.662851732612533</v>
       </c>
       <c r="G162" s="11" t="n">
         <f aca="false">G141/G153</f>
-        <v>0.649836723871595</v>
+        <v>0.652411569027811</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52055,15 +52055,15 @@
       </c>
       <c r="E163" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E162-D162)</f>
-        <v>0.606129939881145</v>
+        <v>0.607052351760531</v>
       </c>
       <c r="F163" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F162-D162)</f>
-        <v>0.601908177471219</v>
+        <v>0.602790465087334</v>
       </c>
       <c r="G163" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G162-D162)</f>
-        <v>0.598755690514061</v>
+        <v>0.599553916621566</v>
       </c>
       <c r="H163" s="8" t="s">
         <v>509</v>
@@ -52145,15 +52145,15 @@
       </c>
       <c r="E171" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F171" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G171" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52263,15 +52263,15 @@
       </c>
       <c r="E175" s="9" t="n">
         <f aca="false">E171*1000*E174</f>
-        <v>1463.91040196413</v>
+        <v>1423.0418615943</v>
       </c>
       <c r="F175" s="9" t="n">
         <f aca="false">F171*1000*F174</f>
-        <v>1896.38539307285</v>
+        <v>1850.68083138338</v>
       </c>
       <c r="G175" s="9" t="n">
         <f aca="false">G171*1000*G174</f>
-        <v>2322.15695676807</v>
+        <v>2274.71018955755</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52322,15 +52322,15 @@
       </c>
       <c r="E177" s="9" t="n">
         <f aca="false">E173+E175+E176</f>
-        <v>6291.16886922891</v>
+        <v>6250.30032885908</v>
       </c>
       <c r="F177" s="9" t="n">
         <f aca="false">F173+F175+F176</f>
-        <v>7313.90783419236</v>
+        <v>7268.2032725029</v>
       </c>
       <c r="G177" s="9" t="n">
         <f aca="false">G173+G175+G176</f>
-        <v>8346.28030790601</v>
+        <v>8298.83354069549</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52378,15 +52378,15 @@
       </c>
       <c r="E179" s="9" t="n">
         <f aca="false">E177+E178</f>
-        <v>6716.87246922891</v>
+        <v>6676.00392885908</v>
       </c>
       <c r="F179" s="9" t="n">
         <f aca="false">F177+F178</f>
-        <v>7773.66772219236</v>
+        <v>7727.9631605029</v>
       </c>
       <c r="G179" s="9" t="n">
         <f aca="false">G177+G178</f>
-        <v>8842.82098694601</v>
+        <v>8795.37421973549</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52406,15 +52406,15 @@
       </c>
       <c r="E180" s="9" t="n">
         <f aca="false">t_inc*E179-t_fix+0*E179</f>
-        <v>2612.42162892254</v>
+        <v>2592.69617320455</v>
       </c>
       <c r="F180" s="9" t="n">
         <f aca="false">t_inc*F179-t_fix+0*F179</f>
-        <v>3122.49044412053</v>
+        <v>3100.43085257268</v>
       </c>
       <c r="G180" s="9" t="n">
         <f aca="false">t_inc*G179-t_fix+0*G179</f>
-        <v>3638.52393072895</v>
+        <v>3615.62345282826</v>
       </c>
       <c r="H180" s="4" t="s">
         <v>500</v>
@@ -52437,15 +52437,15 @@
       </c>
       <c r="E181" s="11" t="n">
         <f aca="false">E180/E179</f>
-        <v>0.388934231056265</v>
+        <v>0.388360492419249</v>
       </c>
       <c r="F181" s="11" t="n">
         <f aca="false">F180/F179</f>
-        <v>0.401675316685637</v>
+        <v>0.40119638101004</v>
       </c>
       <c r="G181" s="11" t="n">
         <f aca="false">G180/G179</f>
-        <v>0.411466424130968</v>
+        <v>0.41108238973111</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52549,15 +52549,15 @@
       </c>
       <c r="E185" s="9" t="n">
         <f aca="false">E179+E182</f>
-        <v>7158.54446922891</v>
+        <v>7117.67592885908</v>
       </c>
       <c r="F185" s="9" t="n">
         <f aca="false">F179+F182</f>
-        <v>8259.50692219236</v>
+        <v>8213.8023605029</v>
       </c>
       <c r="G185" s="9" t="n">
         <f aca="false">G179+G182</f>
-        <v>9377.24410694601</v>
+        <v>9329.79733973549</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52596,15 +52596,15 @@
       </c>
       <c r="E187" s="9" t="n">
         <f aca="false">E180+E183+E184</f>
-        <v>2610.85506892254</v>
+        <v>2591.12961320455</v>
       </c>
       <c r="F187" s="9" t="n">
         <f aca="false">F180+F183+F184</f>
-        <v>3131.52401212053</v>
+        <v>3109.46442057268</v>
       </c>
       <c r="G187" s="9" t="n">
         <f aca="false">G180+G183+G184</f>
-        <v>3654.84508672895</v>
+        <v>3631.94460882826</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52624,15 +52624,15 @@
       </c>
       <c r="E188" s="11" t="n">
         <f aca="false">E187/E185</f>
-        <v>0.364718705058736</v>
+        <v>0.364041526911706</v>
       </c>
       <c r="F188" s="11" t="n">
         <f aca="false">F187/F185</f>
-        <v>0.379141762531427</v>
+        <v>0.378565770650256</v>
       </c>
       <c r="G188" s="11" t="n">
         <f aca="false">G187/G185</f>
-        <v>0.389756845939597</v>
+        <v>0.389284405284974</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52652,15 +52652,15 @@
       </c>
       <c r="E189" s="9" t="n">
         <f aca="false">E187*etr</f>
-        <v>370.10801537899</v>
+        <v>367.31178614546</v>
       </c>
       <c r="F189" s="9" t="n">
         <f aca="false">F187*etr</f>
-        <v>443.916688840137</v>
+        <v>440.789578589924</v>
       </c>
       <c r="G189" s="9" t="n">
         <f aca="false">G187*etr</f>
-        <v>518.101321543343</v>
+        <v>514.855009433589</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52708,15 +52708,15 @@
       </c>
       <c r="E191" s="9" t="n">
         <f aca="false">E187-E189+E190</f>
-        <v>2227.54705354355</v>
+        <v>2210.61782705909</v>
       </c>
       <c r="F191" s="9" t="n">
         <f aca="false">F187-F189+F190</f>
-        <v>2674.40732328039</v>
+        <v>2655.47484198275</v>
       </c>
       <c r="G191" s="9" t="n">
         <f aca="false">G187-G189+G190</f>
-        <v>3123.54376518561</v>
+        <v>3103.88959939467</v>
       </c>
       <c r="H191" s="8" t="s">
         <v>505</v>
@@ -52767,15 +52767,15 @@
       </c>
       <c r="E193" s="18" t="n">
         <f aca="false">E191/E192</f>
-        <v>14.2678980902465</v>
+        <v>14.1594629046271</v>
       </c>
       <c r="F193" s="18" t="n">
         <f aca="false">F191/F192</f>
-        <v>17.3031618574269</v>
+        <v>17.1806704981623</v>
       </c>
       <c r="G193" s="18" t="n">
         <f aca="false">G191/G192</f>
-        <v>20.4131636970041</v>
+        <v>20.2847186570817</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52795,15 +52795,15 @@
       </c>
       <c r="E194" s="11" t="n">
         <f aca="false">E173/E185</f>
-        <v>0.636063558949615</v>
+        <v>0.639715732706403</v>
       </c>
       <c r="F194" s="11" t="n">
         <f aca="false">F173/F185</f>
-        <v>0.618687421594602</v>
+        <v>0.622130021767542</v>
       </c>
       <c r="G194" s="11" t="n">
         <f aca="false">G173/G185</f>
-        <v>0.60595911608032</v>
+        <v>0.609040726545459</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52823,15 +52823,15 @@
       </c>
       <c r="E195" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E194-D194)</f>
-        <v>0.594485880425813</v>
+        <v>0.595618088486858</v>
       </c>
       <c r="F195" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F194-D194)</f>
-        <v>0.589099115147571</v>
+        <v>0.590166353435321</v>
       </c>
       <c r="G195" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G194-D194)</f>
-        <v>0.585153221259053</v>
+        <v>0.586108549357326</v>
       </c>
       <c r="H195" s="8" t="s">
         <v>509</v>
@@ -52913,15 +52913,15 @@
       </c>
       <c r="E203" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F203" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G203" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53031,15 +53031,15 @@
       </c>
       <c r="E207" s="9" t="n">
         <f aca="false">E203*1000*E206</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F207" s="9" t="n">
         <f aca="false">F203*1000*F206</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G207" s="9" t="n">
         <f aca="false">G203*1000*G206</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53090,15 +53090,15 @@
       </c>
       <c r="E209" s="9" t="n">
         <f aca="false">E205+E207+E208</f>
-        <v>6091.59354523868</v>
+        <v>6056.29662467179</v>
       </c>
       <c r="F209" s="9" t="n">
         <f aca="false">F205+F207+F208</f>
-        <v>7055.37307091378</v>
+        <v>7015.89942519757</v>
       </c>
       <c r="G209" s="9" t="n">
         <f aca="false">G205+G207+G208</f>
-        <v>8029.69998551651</v>
+        <v>7988.72164965644</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53146,15 +53146,15 @@
       </c>
       <c r="E211" s="9" t="n">
         <f aca="false">E209+E210</f>
-        <v>6517.29714523868</v>
+        <v>6482.00022467179</v>
       </c>
       <c r="F211" s="9" t="n">
         <f aca="false">F209+F210</f>
-        <v>7515.13295891378</v>
+        <v>7475.65931319757</v>
       </c>
       <c r="G211" s="9" t="n">
         <f aca="false">G209+G210</f>
-        <v>8526.24066455651</v>
+        <v>8485.26232869644</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53174,15 +53174,15 @@
       </c>
       <c r="E212" s="9" t="n">
         <f aca="false">t_inc_lo*E211-t_fix_lo+0*E211</f>
-        <v>2366.71759464083</v>
+        <v>2352.59882641408</v>
       </c>
       <c r="F212" s="9" t="n">
         <f aca="false">t_inc_lo*F211-t_fix_lo+0*F211</f>
-        <v>2765.85192011087</v>
+        <v>2750.06246182439</v>
       </c>
       <c r="G212" s="9" t="n">
         <f aca="false">t_inc_lo*G211-t_fix_lo+0*G211</f>
-        <v>3170.29500236796</v>
+        <v>3153.90366802394</v>
       </c>
       <c r="H212" s="4" t="s">
         <v>500</v>
@@ -53205,15 +53205,15 @@
       </c>
       <c r="E213" s="11" t="n">
         <f aca="false">E212/E211</f>
-        <v>0.363144036845071</v>
+        <v>0.362943342312704</v>
       </c>
       <c r="F213" s="11" t="n">
         <f aca="false">F212/F211</f>
-        <v>0.368037656184149</v>
+        <v>0.367868885754252</v>
       </c>
       <c r="G213" s="11" t="n">
         <f aca="false">G212/G211</f>
-        <v>0.371827998656764</v>
+        <v>0.37169194608842</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53317,15 +53317,15 @@
       </c>
       <c r="E217" s="9" t="n">
         <f aca="false">E211+E214</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="F217" s="9" t="n">
         <f aca="false">F211+F214</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G217" s="9" t="n">
         <f aca="false">G211+G214</f>
-        <v>9060.66378455651</v>
+        <v>9019.68544869644</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53364,15 +53364,15 @@
       </c>
       <c r="E219" s="9" t="n">
         <f aca="false">E212+E215+E216</f>
-        <v>2365.15103464083</v>
+        <v>2351.03226641408</v>
       </c>
       <c r="F219" s="9" t="n">
         <f aca="false">F212+F215+F216</f>
-        <v>2774.88548811087</v>
+        <v>2759.09602982439</v>
       </c>
       <c r="G219" s="9" t="n">
         <f aca="false">G212+G215+G216</f>
-        <v>3186.61615836796</v>
+        <v>3170.22482402394</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53392,15 +53392,15 @@
       </c>
       <c r="E220" s="11" t="n">
         <f aca="false">E219/E217</f>
-        <v>0.339870889678979</v>
+        <v>0.339564351130953</v>
       </c>
       <c r="F220" s="11" t="n">
         <f aca="false">F219/F217</f>
-        <v>0.346818540671887</v>
+        <v>0.346554863415563</v>
       </c>
       <c r="G220" s="11" t="n">
         <f aca="false">G219/G217</f>
-        <v>0.351697870502535</v>
+        <v>0.351478423727305</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53420,15 +53420,15 @@
       </c>
       <c r="E221" s="9" t="n">
         <f aca="false">E219*etr</f>
-        <v>335.277651341915</v>
+        <v>333.276211526201</v>
       </c>
       <c r="F221" s="9" t="n">
         <f aca="false">F219*etr</f>
-        <v>393.360540434941</v>
+        <v>391.122267947172</v>
       </c>
       <c r="G221" s="9" t="n">
         <f aca="false">G219*etr</f>
-        <v>451.726408021149</v>
+        <v>449.40281515087</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53476,15 +53476,15 @@
       </c>
       <c r="E223" s="9" t="n">
         <f aca="false">E219-E221+E222</f>
-        <v>2016.67338329892</v>
+        <v>2004.55605488788</v>
       </c>
       <c r="F223" s="9" t="n">
         <f aca="false">F219-F221+F222</f>
-        <v>2368.32494767593</v>
+        <v>2354.77376187722</v>
       </c>
       <c r="G223" s="9" t="n">
         <f aca="false">G219-G221+G222</f>
-        <v>2721.68975034682</v>
+        <v>2707.62200887307</v>
       </c>
       <c r="H223" s="8" t="s">
         <v>505</v>
@@ -53535,15 +53535,15 @@
       </c>
       <c r="E225" s="18" t="n">
         <f aca="false">E223/E224</f>
-        <v>12.9172087603935</v>
+        <v>12.8395947739147</v>
       </c>
       <c r="F225" s="18" t="n">
         <f aca="false">F223/F224</f>
-        <v>15.3228379027746</v>
+        <v>15.2351630152606</v>
       </c>
       <c r="G225" s="18" t="n">
         <f aca="false">G223/G224</f>
-        <v>17.786944119538</v>
+        <v>17.6950078026048</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53563,15 +53563,15 @@
       </c>
       <c r="E226" s="11" t="n">
         <f aca="false">E205/E217</f>
-        <v>0.654305138730523</v>
+        <v>0.657640790066815</v>
       </c>
       <c r="F226" s="11" t="n">
         <f aca="false">F205/F217</f>
-        <v>0.638679017979199</v>
+        <v>0.641845631555813</v>
       </c>
       <c r="G226" s="11" t="n">
         <f aca="false">G205/G217</f>
-        <v>0.627131376400865</v>
+        <v>0.629980566687679</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53591,15 +53591,15 @@
       </c>
       <c r="E227" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E226-D226)</f>
-        <v>0.600140940959489</v>
+        <v>0.601175024106483</v>
       </c>
       <c r="F227" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F226-D226)</f>
-        <v>0.595296697214342</v>
+        <v>0.596278377073082</v>
       </c>
       <c r="G227" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G226-D226)</f>
-        <v>0.591716820200892</v>
+        <v>0.592600095867661</v>
       </c>
       <c r="H227" s="8" t="s">
         <v>509</v>
@@ -53681,15 +53681,15 @@
       </c>
       <c r="E235" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F235" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G235" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53799,15 +53799,15 @@
       </c>
       <c r="E239" s="9" t="n">
         <f aca="false">E235*1000*E238</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F239" s="9" t="n">
         <f aca="false">F235*1000*F238</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G239" s="9" t="n">
         <f aca="false">G235*1000*G238</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53858,15 +53858,15 @@
       </c>
       <c r="E241" s="9" t="n">
         <f aca="false">E237+E239+E240</f>
-        <v>6091.59354523868</v>
+        <v>6056.29662467179</v>
       </c>
       <c r="F241" s="9" t="n">
         <f aca="false">F237+F239+F240</f>
-        <v>7055.37307091378</v>
+        <v>7015.89942519757</v>
       </c>
       <c r="G241" s="9" t="n">
         <f aca="false">G237+G239+G240</f>
-        <v>8029.69998551651</v>
+        <v>7988.72164965644</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53914,15 +53914,15 @@
       </c>
       <c r="E243" s="9" t="n">
         <f aca="false">E241+E242</f>
-        <v>6517.29714523868</v>
+        <v>6482.00022467179</v>
       </c>
       <c r="F243" s="9" t="n">
         <f aca="false">F241+F242</f>
-        <v>7515.13295891378</v>
+        <v>7475.65931319757</v>
       </c>
       <c r="G243" s="9" t="n">
         <f aca="false">G241+G242</f>
-        <v>8526.24066455651</v>
+        <v>8485.26232869644</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53942,15 +53942,15 @@
       </c>
       <c r="E244" s="9" t="n">
         <f aca="false">t_inc_hi*E243-t_fix_hi+0*E243</f>
-        <v>2655.87233787902</v>
+        <v>2636.10606236157</v>
       </c>
       <c r="F244" s="9" t="n">
         <f aca="false">t_inc_hi*F243-t_fix_hi+0*F243</f>
-        <v>3214.66039353708</v>
+        <v>3192.555151936</v>
       </c>
       <c r="G244" s="9" t="n">
         <f aca="false">t_inc_hi*G243-t_fix_hi+0*G243</f>
-        <v>3780.88070869701</v>
+        <v>3757.93284061537</v>
       </c>
       <c r="H244" s="4" t="s">
         <v>500</v>
@@ -53973,15 +53973,15 @@
       </c>
       <c r="E245" s="11" t="n">
         <f aca="false">E244/E243</f>
-        <v>0.407511316223983</v>
+        <v>0.406680958190655</v>
       </c>
       <c r="F245" s="11" t="n">
         <f aca="false">F244/F243</f>
-        <v>0.42775828599601</v>
+        <v>0.427060011456093</v>
       </c>
       <c r="G245" s="11" t="n">
         <f aca="false">G244/G243</f>
-        <v>0.443440533459733</v>
+        <v>0.442877626529749</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54085,15 +54085,15 @@
       </c>
       <c r="E249" s="9" t="n">
         <f aca="false">E243+E246</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="F249" s="9" t="n">
         <f aca="false">F243+F246</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G249" s="9" t="n">
         <f aca="false">G243+G246</f>
-        <v>9060.66378455651</v>
+        <v>9019.68544869644</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54132,15 +54132,15 @@
       </c>
       <c r="E251" s="9" t="n">
         <f aca="false">E244+E247+E248</f>
-        <v>2654.30577787902</v>
+        <v>2634.53950236157</v>
       </c>
       <c r="F251" s="9" t="n">
         <f aca="false">F244+F247+F248</f>
-        <v>3223.69396153708</v>
+        <v>3201.588719936</v>
       </c>
       <c r="G251" s="9" t="n">
         <f aca="false">G244+G247+G248</f>
-        <v>3797.20186469701</v>
+        <v>3774.25399661537</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54160,15 +54160,15 @@
       </c>
       <c r="E252" s="11" t="n">
         <f aca="false">E251/E249</f>
-        <v>0.38142226563759</v>
+        <v>0.380511875327323</v>
       </c>
       <c r="F252" s="11" t="n">
         <f aca="false">F251/F249</f>
-        <v>0.402912783285416</v>
+        <v>0.402133934287472</v>
       </c>
       <c r="G252" s="11" t="n">
         <f aca="false">G251/G249</f>
-        <v>0.419086499067449</v>
+        <v>0.418446299273201</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54188,15 +54188,15 @@
       </c>
       <c r="E253" s="9" t="n">
         <f aca="false">E251*etr</f>
-        <v>376.267474726279</v>
+        <v>373.46545898428</v>
       </c>
       <c r="F253" s="9" t="n">
         <f aca="false">F251*etr</f>
-        <v>456.982460840349</v>
+        <v>453.848879357473</v>
       </c>
       <c r="G253" s="9" t="n">
         <f aca="false">G251*etr</f>
-        <v>538.281447662426</v>
+        <v>535.028417644035</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54244,15 +54244,15 @@
       </c>
       <c r="E255" s="9" t="n">
         <f aca="false">E251-E253+E254</f>
-        <v>2264.83830315274</v>
+        <v>2247.87404337729</v>
       </c>
       <c r="F255" s="9" t="n">
         <f aca="false">F251-F253+F254</f>
-        <v>2753.51150069673</v>
+        <v>2734.53984057853</v>
       </c>
       <c r="G255" s="9" t="n">
         <f aca="false">G251-G253+G254</f>
-        <v>3245.72041703458</v>
+        <v>3226.02557897133</v>
       </c>
       <c r="H255" s="8" t="s">
         <v>505</v>
@@ -54303,15 +54303,15 @@
       </c>
       <c r="E257" s="18" t="n">
         <f aca="false">E255/E256</f>
-        <v>14.5067562316426</v>
+        <v>14.3980966505722</v>
       </c>
       <c r="F257" s="18" t="n">
         <f aca="false">F255/F256</f>
-        <v>17.8149583865191</v>
+        <v>17.6922135439994</v>
       </c>
       <c r="G257" s="18" t="n">
         <f aca="false">G255/G256</f>
-        <v>21.2116196117067</v>
+        <v>21.0829087680003</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54331,15 +54331,15 @@
       </c>
       <c r="E258" s="11" t="n">
         <f aca="false">E237/E249</f>
-        <v>0.654305138730523</v>
+        <v>0.657640790066815</v>
       </c>
       <c r="F258" s="11" t="n">
         <f aca="false">F237/F249</f>
-        <v>0.638679017979199</v>
+        <v>0.641845631555813</v>
       </c>
       <c r="G258" s="11" t="n">
         <f aca="false">G237/G249</f>
-        <v>0.627131376400865</v>
+        <v>0.629980566687679</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54359,15 +54359,15 @@
       </c>
       <c r="E259" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E258-D258)</f>
-        <v>0.600140940959489</v>
+        <v>0.601175024106483</v>
       </c>
       <c r="F259" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F258-D258)</f>
-        <v>0.595296697214342</v>
+        <v>0.596278377073082</v>
       </c>
       <c r="G259" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G258-D258)</f>
-        <v>0.591716820200892</v>
+        <v>0.592600095867661</v>
       </c>
       <c r="H259" s="8" t="s">
         <v>509</v>
@@ -54449,15 +54449,15 @@
       </c>
       <c r="E267" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F267" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G267" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54567,15 +54567,15 @@
       </c>
       <c r="E271" s="9" t="n">
         <f aca="false">E267*1000*E270</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F271" s="9" t="n">
         <f aca="false">F267*1000*F270</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G271" s="9" t="n">
         <f aca="false">G267*1000*G270</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54626,15 +54626,15 @@
       </c>
       <c r="E273" s="9" t="n">
         <f aca="false">E269+E271+E272</f>
-        <v>6091.59354523868</v>
+        <v>6056.29662467179</v>
       </c>
       <c r="F273" s="9" t="n">
         <f aca="false">F269+F271+F272</f>
-        <v>7055.37307091378</v>
+        <v>7015.89942519757</v>
       </c>
       <c r="G273" s="9" t="n">
         <f aca="false">G269+G271+G272</f>
-        <v>8029.69998551651</v>
+        <v>7988.72164965644</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54682,15 +54682,15 @@
       </c>
       <c r="E275" s="9" t="n">
         <f aca="false">E273+E274</f>
-        <v>6501.53034523867</v>
+        <v>6466.23342467179</v>
       </c>
       <c r="F275" s="9" t="n">
         <f aca="false">F273+F274</f>
-        <v>7481.70734291378</v>
+        <v>7442.23369719757</v>
       </c>
       <c r="G275" s="9" t="n">
         <f aca="false">G273+G274</f>
-        <v>8473.08762839651</v>
+        <v>8432.10929253644</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54710,15 +54710,15 @@
       </c>
       <c r="E276" s="9" t="n">
         <f aca="false">t_inc*E275-t_fix+0*E275</f>
-        <v>2508.48541068357</v>
+        <v>2491.44913198796</v>
       </c>
       <c r="F276" s="9" t="n">
         <f aca="false">t_inc*F275-t_fix+0*F275</f>
-        <v>2981.57394745215</v>
+        <v>2962.52174633225</v>
       </c>
       <c r="G276" s="9" t="n">
         <f aca="false">t_inc*G275-t_fix+0*G275</f>
-        <v>3460.06982090429</v>
+        <v>3440.29137170865</v>
       </c>
       <c r="H276" s="4" t="s">
         <v>500</v>
@@ -54741,15 +54741,15 @@
       </c>
       <c r="E277" s="11" t="n">
         <f aca="false">E276/E275</f>
-        <v>0.385829993475403</v>
+        <v>0.385301452694528</v>
       </c>
       <c r="F277" s="11" t="n">
         <f aca="false">F276/F275</f>
-        <v>0.398515179864142</v>
+        <v>0.39806889528984</v>
       </c>
       <c r="G277" s="11" t="n">
         <f aca="false">G276/G275</f>
-        <v>0.408359971317692</v>
+        <v>0.407998906602619</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54853,15 +54853,15 @@
       </c>
       <c r="E281" s="9" t="n">
         <f aca="false">E275+E278</f>
-        <v>6943.20234523868</v>
+        <v>6907.90542467179</v>
       </c>
       <c r="F281" s="9" t="n">
         <f aca="false">F275+F278</f>
-        <v>7967.54654291378</v>
+        <v>7928.07289719757</v>
       </c>
       <c r="G281" s="9" t="n">
         <f aca="false">G275+G278</f>
-        <v>9007.51074839651</v>
+        <v>8966.53241253644</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54900,15 +54900,15 @@
       </c>
       <c r="E283" s="9" t="n">
         <f aca="false">E276+E279+E280</f>
-        <v>2506.91885068357</v>
+        <v>2489.88257198796</v>
       </c>
       <c r="F283" s="9" t="n">
         <f aca="false">F276+F279+F280</f>
-        <v>2990.60751545215</v>
+        <v>2971.55531433225</v>
       </c>
       <c r="G283" s="9" t="n">
         <f aca="false">G276+G279+G280</f>
-        <v>3476.39097690429</v>
+        <v>3456.61252770865</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54928,15 +54928,15 @@
       </c>
       <c r="E284" s="11" t="n">
         <f aca="false">E283/E281</f>
-        <v>0.361060894675308</v>
+        <v>0.360439586085714</v>
       </c>
       <c r="F284" s="11" t="n">
         <f aca="false">F283/F281</f>
-        <v>0.375348609430083</v>
+        <v>0.374814327878172</v>
       </c>
       <c r="G284" s="11" t="n">
         <f aca="false">G283/G281</f>
-        <v>0.385943583528129</v>
+        <v>0.385501592887328</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54956,15 +54956,15 @@
       </c>
       <c r="E285" s="9" t="n">
         <f aca="false">E283*etr</f>
-        <v>355.374287752241</v>
+        <v>352.959269250245</v>
       </c>
       <c r="F285" s="9" t="n">
         <f aca="false">F283*etr</f>
-        <v>423.940733247314</v>
+        <v>421.239942832319</v>
       </c>
       <c r="G285" s="9" t="n">
         <f aca="false">G283*etr</f>
-        <v>492.804131664976</v>
+        <v>490.000390214061</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55012,15 +55012,15 @@
       </c>
       <c r="E287" s="9" t="n">
         <f aca="false">E283-E285+E286</f>
-        <v>2138.34456293133</v>
+        <v>2123.72330273771</v>
       </c>
       <c r="F287" s="9" t="n">
         <f aca="false">F283-F285+F286</f>
-        <v>2553.46678220484</v>
+        <v>2537.11537149994</v>
       </c>
       <c r="G287" s="9" t="n">
         <f aca="false">G283-G285+G286</f>
-        <v>2970.38684523931</v>
+        <v>2953.41213749459</v>
       </c>
       <c r="H287" s="8" t="s">
         <v>505</v>
@@ -55071,15 +55071,15 @@
       </c>
       <c r="E289" s="18" t="n">
         <f aca="false">E287/E288</f>
-        <v>13.6965377486426</v>
+        <v>13.6028855629069</v>
       </c>
       <c r="F289" s="18" t="n">
         <f aca="false">F287/F288</f>
-        <v>16.5206880213965</v>
+        <v>16.4148959441907</v>
       </c>
       <c r="G289" s="18" t="n">
         <f aca="false">G287/G288</f>
-        <v>19.4122437441483</v>
+        <v>19.3013096532724</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55099,15 +55099,15 @@
       </c>
       <c r="E290" s="11" t="n">
         <f aca="false">E269/E281</f>
-        <v>0.655790951436012</v>
+        <v>0.659141808128207</v>
       </c>
       <c r="F290" s="11" t="n">
         <f aca="false">F269/F281</f>
-        <v>0.641358417401248</v>
+        <v>0.644551722416714</v>
       </c>
       <c r="G290" s="11" t="n">
         <f aca="false">G269/G281</f>
-        <v>0.630832058826678</v>
+        <v>0.633715051581129</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55127,15 +55127,15 @@
       </c>
       <c r="E291" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E290-D290)</f>
-        <v>0.600601556810318</v>
+        <v>0.601640353760014</v>
       </c>
       <c r="F291" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F290-D290)</f>
-        <v>0.596127336123228</v>
+        <v>0.597117290577933</v>
       </c>
       <c r="G291" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G290-D290)</f>
-        <v>0.592864066403537</v>
+        <v>0.593757821151776</v>
       </c>
       <c r="H291" s="8" t="s">
         <v>509</v>
@@ -55217,15 +55217,15 @@
       </c>
       <c r="E299" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F299" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G299" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55335,15 +55335,15 @@
       </c>
       <c r="E303" s="9" t="n">
         <f aca="false">E299*1000*E302</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F303" s="9" t="n">
         <f aca="false">F299*1000*F302</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G303" s="9" t="n">
         <f aca="false">G299*1000*G302</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55394,15 +55394,15 @@
       </c>
       <c r="E305" s="9" t="n">
         <f aca="false">E301+E303+E304</f>
-        <v>6091.59354523868</v>
+        <v>6056.29662467179</v>
       </c>
       <c r="F305" s="9" t="n">
         <f aca="false">F301+F303+F304</f>
-        <v>7055.37307091378</v>
+        <v>7015.89942519757</v>
       </c>
       <c r="G305" s="9" t="n">
         <f aca="false">G301+G303+G304</f>
-        <v>8029.69998551651</v>
+        <v>7988.72164965644</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55450,15 +55450,15 @@
       </c>
       <c r="E307" s="9" t="n">
         <f aca="false">E305+E306</f>
-        <v>6533.06394523868</v>
+        <v>6497.76702467179</v>
       </c>
       <c r="F307" s="9" t="n">
         <f aca="false">F305+F306</f>
-        <v>7549.81991891378</v>
+        <v>7510.34627319757</v>
       </c>
       <c r="G307" s="9" t="n">
         <f aca="false">G305+G306</f>
-        <v>8583.48045527651</v>
+        <v>8542.50211941644</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55478,15 +55478,15 @@
       </c>
       <c r="E308" s="9" t="n">
         <f aca="false">t_inc*E307-t_fix+0*E307</f>
-        <v>2523.70529925312</v>
+        <v>2506.6690205575</v>
       </c>
       <c r="F308" s="9" t="n">
         <f aca="false">t_inc*F307-t_fix+0*F307</f>
-        <v>3014.44890676237</v>
+        <v>2995.39670564247</v>
       </c>
       <c r="G308" s="9" t="n">
         <f aca="false">t_inc*G307-t_fix+0*G307</f>
-        <v>3513.35160680855</v>
+        <v>3493.57315761291</v>
       </c>
       <c r="H308" s="4" t="s">
         <v>500</v>
@@ -55509,15 +55509,15 @@
       </c>
       <c r="E309" s="11" t="n">
         <f aca="false">E308/E307</f>
-        <v>0.386297351504175</v>
+        <v>0.385773914490896</v>
       </c>
       <c r="F309" s="11" t="n">
         <f aca="false">F308/F307</f>
-        <v>0.39927427927262</v>
+        <v>0.398836031879415</v>
       </c>
       <c r="G309" s="11" t="n">
         <f aca="false">G308/G307</f>
-        <v>0.409315501458245</v>
+        <v>0.408963686373843</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55621,15 +55621,15 @@
       </c>
       <c r="E313" s="9" t="n">
         <f aca="false">E307+E310</f>
-        <v>6974.73594523868</v>
+        <v>6939.43902467179</v>
       </c>
       <c r="F313" s="9" t="n">
         <f aca="false">F307+F310</f>
-        <v>8035.65911891378</v>
+        <v>7996.18547319757</v>
       </c>
       <c r="G313" s="9" t="n">
         <f aca="false">G307+G310</f>
-        <v>9117.90357527651</v>
+        <v>9076.92523941644</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55668,15 +55668,15 @@
       </c>
       <c r="E315" s="9" t="n">
         <f aca="false">E308+E311+E312</f>
-        <v>2522.13873925312</v>
+        <v>2505.1024605575</v>
       </c>
       <c r="F315" s="9" t="n">
         <f aca="false">F308+F311+F312</f>
-        <v>3023.48247476237</v>
+        <v>3004.43027364247</v>
       </c>
       <c r="G315" s="9" t="n">
         <f aca="false">G308+G311+G312</f>
-        <v>3529.67276280855</v>
+        <v>3509.89431361291</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55696,15 +55696,15 @@
       </c>
       <c r="E316" s="11" t="n">
         <f aca="false">E315/E313</f>
-        <v>0.361610641471648</v>
+        <v>0.360994952423547</v>
       </c>
       <c r="F316" s="11" t="n">
         <f aca="false">F315/F313</f>
-        <v>0.376258179947667</v>
+        <v>0.375732939626404</v>
       </c>
       <c r="G316" s="11" t="n">
         <f aca="false">G315/G313</f>
-        <v>0.387114508688091</v>
+        <v>0.386683179715003</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55724,15 +55724,15 @@
       </c>
       <c r="E317" s="9" t="n">
         <f aca="false">E315*etr</f>
-        <v>357.53181952021</v>
+        <v>355.116801018214</v>
       </c>
       <c r="F317" s="9" t="n">
         <f aca="false">F315*etr</f>
-        <v>428.601001866127</v>
+        <v>425.900211451132</v>
       </c>
       <c r="G317" s="9" t="n">
         <f aca="false">G315*etr</f>
-        <v>500.357218878283</v>
+        <v>497.553477427367</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55780,15 +55780,15 @@
       </c>
       <c r="E319" s="9" t="n">
         <f aca="false">E315-E317+E318</f>
-        <v>2151.40691973291</v>
+        <v>2136.78565953929</v>
       </c>
       <c r="F319" s="9" t="n">
         <f aca="false">F315-F317+F318</f>
-        <v>2581.68147289624</v>
+        <v>2565.33006219134</v>
       </c>
       <c r="G319" s="9" t="n">
         <f aca="false">G315-G317+G318</f>
-        <v>3016.11554393027</v>
+        <v>2999.14083618555</v>
       </c>
       <c r="H319" s="8" t="s">
         <v>505</v>
@@ -55839,15 +55839,15 @@
       </c>
       <c r="E321" s="18" t="n">
         <f aca="false">E319/E320</f>
-        <v>13.7802048367819</v>
+        <v>13.6865526510462</v>
       </c>
       <c r="F321" s="18" t="n">
         <f aca="false">F319/F320</f>
-        <v>16.7032343955186</v>
+        <v>16.5974423183129</v>
       </c>
       <c r="G321" s="18" t="n">
         <f aca="false">G319/G320</f>
-        <v>19.7110925781021</v>
+        <v>19.6001584872262</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55867,15 +55867,15 @@
       </c>
       <c r="E322" s="11" t="n">
         <f aca="false">E301/E313</f>
-        <v>0.652826043558701</v>
+        <v>0.656146592802171</v>
       </c>
       <c r="F322" s="11" t="n">
         <f aca="false">F301/F313</f>
-        <v>0.635922077543866</v>
+        <v>0.639061344745237</v>
       </c>
       <c r="G322" s="11" t="n">
         <f aca="false">G301/G313</f>
-        <v>0.623194411237462</v>
+        <v>0.626007860639789</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55895,15 +55895,15 @@
       </c>
       <c r="E323" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E322-D322)</f>
-        <v>0.599682407606995</v>
+        <v>0.600711808963809</v>
       </c>
       <c r="F323" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F322-D322)</f>
-        <v>0.594442019865296</v>
+        <v>0.595415222091658</v>
       </c>
       <c r="G323" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G322-D322)</f>
-        <v>0.590496324137206</v>
+        <v>0.591368519795131</v>
       </c>
       <c r="H323" s="8" t="s">
         <v>509</v>
@@ -55985,15 +55985,15 @@
       </c>
       <c r="E331" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F331" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G331" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56103,15 +56103,15 @@
       </c>
       <c r="E335" s="9" t="n">
         <f aca="false">E331*1000*E334</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F335" s="9" t="n">
         <f aca="false">F331*1000*F334</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G335" s="9" t="n">
         <f aca="false">G331*1000*G334</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56162,15 +56162,15 @@
       </c>
       <c r="E337" s="9" t="n">
         <f aca="false">E333+E335+E336</f>
-        <v>6091.59354523868</v>
+        <v>6056.29662467179</v>
       </c>
       <c r="F337" s="9" t="n">
         <f aca="false">F333+F335+F336</f>
-        <v>7055.37307091378</v>
+        <v>7015.89942519757</v>
       </c>
       <c r="G337" s="9" t="n">
         <f aca="false">G333+G335+G336</f>
-        <v>8029.69998551651</v>
+        <v>7988.72164965644</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56218,15 +56218,15 @@
       </c>
       <c r="E339" s="9" t="n">
         <f aca="false">E337+E338</f>
-        <v>6517.29714523868</v>
+        <v>6482.00022467179</v>
       </c>
       <c r="F339" s="9" t="n">
         <f aca="false">F337+F338</f>
-        <v>7515.13295891378</v>
+        <v>7475.65931319757</v>
       </c>
       <c r="G339" s="9" t="n">
         <f aca="false">G337+G338</f>
-        <v>8526.24066455651</v>
+        <v>8485.26232869644</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56246,15 +56246,15 @@
       </c>
       <c r="E340" s="9" t="n">
         <f aca="false">t_inc*E339-t_fix+0*E339</f>
-        <v>2516.09535496834</v>
+        <v>2499.05907627273</v>
       </c>
       <c r="F340" s="9" t="n">
         <f aca="false">t_inc*F339-t_fix+0*F339</f>
-        <v>2997.70702933587</v>
+        <v>2978.65482821597</v>
       </c>
       <c r="G340" s="9" t="n">
         <f aca="false">t_inc*G339-t_fix+0*G339</f>
-        <v>3485.72446507711</v>
+        <v>3465.94601588148</v>
       </c>
       <c r="H340" s="4" t="s">
         <v>500</v>
@@ -56277,15 +56277,15 @@
       </c>
       <c r="E341" s="11" t="n">
         <f aca="false">E340/E339</f>
-        <v>0.386064237811609</v>
+        <v>0.385538258200117</v>
       </c>
       <c r="F341" s="11" t="n">
         <f aca="false">F340/F339</f>
-        <v>0.398889420283677</v>
+        <v>0.398447107261488</v>
       </c>
       <c r="G341" s="11" t="n">
         <f aca="false">G340/G339</f>
-        <v>0.408823138146597</v>
+        <v>0.408466571995063</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56389,15 +56389,15 @@
       </c>
       <c r="E345" s="9" t="n">
         <f aca="false">E339+E342</f>
-        <v>6918.81714523867</v>
+        <v>6883.52022467179</v>
       </c>
       <c r="F345" s="9" t="n">
         <f aca="false">F339+F342</f>
-        <v>7916.65295891378</v>
+        <v>7877.17931319757</v>
       </c>
       <c r="G345" s="9" t="n">
         <f aca="false">G339+G342</f>
-        <v>8927.76066455651</v>
+        <v>8886.78232869644</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56436,15 +56436,15 @@
       </c>
       <c r="E347" s="9" t="n">
         <f aca="false">E340+E343+E344</f>
-        <v>2513.72575496834</v>
+        <v>2496.68947627273</v>
       </c>
       <c r="F347" s="9" t="n">
         <f aca="false">F340+F343+F344</f>
-        <v>3003.36782933587</v>
+        <v>2984.31562821597</v>
       </c>
       <c r="G347" s="9" t="n">
         <f aca="false">G340+G343+G344</f>
-        <v>3495.40046507711</v>
+        <v>3475.62201588148</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56464,15 +56464,15 @@
       </c>
       <c r="E348" s="11" t="n">
         <f aca="false">E347/E345</f>
-        <v>0.363317269729872</v>
+        <v>0.362705330235559</v>
       </c>
       <c r="F348" s="11" t="n">
         <f aca="false">F347/F345</f>
-        <v>0.379373435329664</v>
+        <v>0.378855870808475</v>
       </c>
       <c r="G348" s="11" t="n">
         <f aca="false">G347/G345</f>
-        <v>0.391520404321989</v>
+        <v>0.391100162840525</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56492,15 +56492,15 @@
       </c>
       <c r="E349" s="9" t="n">
         <f aca="false">E347*etr</f>
-        <v>356.339216777103</v>
+        <v>353.924198275107</v>
       </c>
       <c r="F349" s="9" t="n">
         <f aca="false">F347*etr</f>
-        <v>425.749602113047</v>
+        <v>423.048811698052</v>
       </c>
       <c r="G349" s="9" t="n">
         <f aca="false">G347*etr</f>
-        <v>495.498867203827</v>
+        <v>492.695125752912</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56548,15 +56548,15 @@
       </c>
       <c r="E351" s="9" t="n">
         <f aca="false">E347-E349+E350</f>
-        <v>2144.18653819124</v>
+        <v>2129.56527799762</v>
       </c>
       <c r="F351" s="9" t="n">
         <f aca="false">F347-F349+F350</f>
-        <v>2564.41822722282</v>
+        <v>2548.06681651792</v>
       </c>
       <c r="G351" s="9" t="n">
         <f aca="false">G347-G349+G350</f>
-        <v>2986.70159787329</v>
+        <v>2969.72689012857</v>
       </c>
       <c r="H351" s="8" t="s">
         <v>505</v>
@@ -56607,15 +56607,15 @@
       </c>
       <c r="E353" s="18" t="n">
         <f aca="false">E351/E352</f>
-        <v>13.7339568045147</v>
+        <v>13.6403046187789</v>
       </c>
       <c r="F353" s="18" t="n">
         <f aca="false">F351/F352</f>
-        <v>16.5915428325052</v>
+        <v>16.4857507552995</v>
       </c>
       <c r="G353" s="18" t="n">
         <f aca="false">G351/G352</f>
-        <v>19.5188648582512</v>
+        <v>19.4079307673754</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56635,15 +56635,15 @@
       </c>
       <c r="E354" s="11" t="n">
         <f aca="false">E333/E345</f>
-        <v>0.658102270433647</v>
+        <v>0.661476849545237</v>
       </c>
       <c r="F354" s="11" t="n">
         <f aca="false">F333/F345</f>
-        <v>0.645481501823354</v>
+        <v>0.648716099781109</v>
       </c>
       <c r="G354" s="11" t="n">
         <f aca="false">G333/G345</f>
-        <v>0.636467168399016</v>
+        <v>0.639402017529543</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56663,15 +56663,15 @@
       </c>
       <c r="E355" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E354-D354)</f>
-        <v>0.601318087341185</v>
+        <v>0.602364238463014</v>
       </c>
       <c r="F355" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F354-D354)</f>
-        <v>0.597405530899805</v>
+        <v>0.598408286553258</v>
       </c>
       <c r="G355" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G354-D354)</f>
-        <v>0.594611003134248</v>
+        <v>0.595520833844618</v>
       </c>
       <c r="H355" s="8" t="s">
         <v>509</v>
@@ -56753,15 +56753,15 @@
       </c>
       <c r="E363" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F363" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G363" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56871,15 +56871,15 @@
       </c>
       <c r="E367" s="9" t="n">
         <f aca="false">E363*1000*E366</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F367" s="9" t="n">
         <f aca="false">F363*1000*F366</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G367" s="9" t="n">
         <f aca="false">G363*1000*G366</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56930,15 +56930,15 @@
       </c>
       <c r="E369" s="9" t="n">
         <f aca="false">E365+E367+E368</f>
-        <v>6091.59354523868</v>
+        <v>6056.29662467179</v>
       </c>
       <c r="F369" s="9" t="n">
         <f aca="false">F365+F367+F368</f>
-        <v>7055.37307091378</v>
+        <v>7015.89942519757</v>
       </c>
       <c r="G369" s="9" t="n">
         <f aca="false">G365+G367+G368</f>
-        <v>8029.69998551651</v>
+        <v>7988.72164965644</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56986,15 +56986,15 @@
       </c>
       <c r="E371" s="9" t="n">
         <f aca="false">E369+E370</f>
-        <v>6517.29714523868</v>
+        <v>6482.00022467179</v>
       </c>
       <c r="F371" s="9" t="n">
         <f aca="false">F369+F370</f>
-        <v>7515.13295891378</v>
+        <v>7475.65931319757</v>
       </c>
       <c r="G371" s="9" t="n">
         <f aca="false">G369+G370</f>
-        <v>8526.24066455651</v>
+        <v>8485.26232869644</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57014,15 +57014,15 @@
       </c>
       <c r="E372" s="9" t="n">
         <f aca="false">t_inc*E371-t_fix+0*E371</f>
-        <v>2516.09535496834</v>
+        <v>2499.05907627273</v>
       </c>
       <c r="F372" s="9" t="n">
         <f aca="false">t_inc*F371-t_fix+0*F371</f>
-        <v>2997.70702933587</v>
+        <v>2978.65482821597</v>
       </c>
       <c r="G372" s="9" t="n">
         <f aca="false">t_inc*G371-t_fix+0*G371</f>
-        <v>3485.72446507711</v>
+        <v>3465.94601588148</v>
       </c>
       <c r="H372" s="4" t="s">
         <v>500</v>
@@ -57045,15 +57045,15 @@
       </c>
       <c r="E373" s="11" t="n">
         <f aca="false">E372/E371</f>
-        <v>0.386064237811609</v>
+        <v>0.385538258200117</v>
       </c>
       <c r="F373" s="11" t="n">
         <f aca="false">F372/F371</f>
-        <v>0.398889420283677</v>
+        <v>0.398447107261488</v>
       </c>
       <c r="G373" s="11" t="n">
         <f aca="false">G372/G371</f>
-        <v>0.408823138146597</v>
+        <v>0.408466571995063</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57157,15 +57157,15 @@
       </c>
       <c r="E377" s="9" t="n">
         <f aca="false">E371+E374</f>
-        <v>6999.12114523867</v>
+        <v>6963.82422467179</v>
       </c>
       <c r="F377" s="9" t="n">
         <f aca="false">F371+F374</f>
-        <v>8093.32175891378</v>
+        <v>8053.84811319757</v>
       </c>
       <c r="G377" s="9" t="n">
         <f aca="false">G371+G374</f>
-        <v>9220.06722455651</v>
+        <v>9179.08888869644</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57204,15 +57204,15 @@
       </c>
       <c r="E379" s="9" t="n">
         <f aca="false">E372+E375+E376</f>
-        <v>2515.33183496834</v>
+        <v>2498.29555627273</v>
       </c>
       <c r="F379" s="9" t="n">
         <f aca="false">F372+F375+F376</f>
-        <v>3010.43458133587</v>
+        <v>2991.38238021597</v>
       </c>
       <c r="G379" s="9" t="n">
         <f aca="false">G372+G375+G376</f>
-        <v>3510.01579307711</v>
+        <v>3490.23734388148</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57232,15 +57232,15 @@
       </c>
       <c r="E380" s="11" t="n">
         <f aca="false">E379/E377</f>
-        <v>0.359378239463602</v>
+        <v>0.358753391192966</v>
       </c>
       <c r="F380" s="11" t="n">
         <f aca="false">F379/F377</f>
-        <v>0.37196526605658</v>
+        <v>0.371422745769702</v>
       </c>
       <c r="G380" s="11" t="n">
         <f aca="false">G379/G377</f>
-        <v>0.380693080385425</v>
+        <v>0.380237884849282</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57260,15 +57260,15 @@
       </c>
       <c r="E381" s="9" t="n">
         <f aca="false">E379*etr</f>
-        <v>356.566890495348</v>
+        <v>354.151871993352</v>
       </c>
       <c r="F381" s="9" t="n">
         <f aca="false">F379*etr</f>
-        <v>426.751366473324</v>
+        <v>424.050576058329</v>
       </c>
       <c r="G381" s="9" t="n">
         <f aca="false">G379*etr</f>
-        <v>497.570698039855</v>
+        <v>494.766956588939</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57316,15 +57316,15 @@
       </c>
       <c r="E383" s="9" t="n">
         <f aca="false">E379-E381+E382</f>
-        <v>2145.564944473</v>
+        <v>2130.94368427938</v>
       </c>
       <c r="F383" s="9" t="n">
         <f aca="false">F379-F381+F382</f>
-        <v>2570.48321486255</v>
+        <v>2554.13180415764</v>
       </c>
       <c r="G383" s="9" t="n">
         <f aca="false">G379-G381+G382</f>
-        <v>2999.24509503726</v>
+        <v>2982.27038729254</v>
       </c>
       <c r="H383" s="8" t="s">
         <v>505</v>
@@ -57375,15 +57375,15 @@
       </c>
       <c r="E385" s="18" t="n">
         <f aca="false">E383/E384</f>
-        <v>13.7427857809099</v>
+        <v>13.6491335951742</v>
       </c>
       <c r="F385" s="18" t="n">
         <f aca="false">F383/F384</f>
-        <v>16.6307827275952</v>
+        <v>16.5249906503894</v>
       </c>
       <c r="G385" s="18" t="n">
         <f aca="false">G383/G384</f>
-        <v>19.6008398456982</v>
+        <v>19.4899057548223</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57403,15 +57403,15 @@
       </c>
       <c r="E386" s="11" t="n">
         <f aca="false">E365/E377</f>
-        <v>0.650551573192058</v>
+        <v>0.653848966472358</v>
       </c>
       <c r="F386" s="11" t="n">
         <f aca="false">F365/F377</f>
-        <v>0.631391311695458</v>
+        <v>0.634485896618822</v>
       </c>
       <c r="G386" s="11" t="n">
         <f aca="false">G365/G377</f>
-        <v>0.616289058628606</v>
+        <v>0.619040366556615</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57431,15 +57431,15 @@
       </c>
       <c r="E387" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E386-D386)</f>
-        <v>0.598977300496762</v>
+        <v>0.599999523288175</v>
       </c>
       <c r="F387" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F386-D386)</f>
-        <v>0.593037440029318</v>
+        <v>0.593996790331123</v>
       </c>
       <c r="G387" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G386-D386)</f>
-        <v>0.588355600171493</v>
+        <v>0.589208531390529</v>
       </c>
       <c r="H387" s="8" t="s">
         <v>509</v>
@@ -57521,15 +57521,15 @@
       </c>
       <c r="E395" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F395" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G395" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57639,15 +57639,15 @@
       </c>
       <c r="E399" s="9" t="n">
         <f aca="false">E395*1000*E398</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F399" s="9" t="n">
         <f aca="false">F395*1000*F398</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G399" s="9" t="n">
         <f aca="false">G395*1000*G398</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57698,15 +57698,15 @@
       </c>
       <c r="E401" s="9" t="n">
         <f aca="false">E397+E399+E400</f>
-        <v>6091.59354523868</v>
+        <v>6056.29662467179</v>
       </c>
       <c r="F401" s="9" t="n">
         <f aca="false">F397+F399+F400</f>
-        <v>7055.37307091378</v>
+        <v>7015.89942519757</v>
       </c>
       <c r="G401" s="9" t="n">
         <f aca="false">G397+G399+G400</f>
-        <v>8029.69998551651</v>
+        <v>7988.72164965644</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57754,15 +57754,15 @@
       </c>
       <c r="E403" s="9" t="n">
         <f aca="false">E401+E402</f>
-        <v>6517.29714523868</v>
+        <v>6482.00022467179</v>
       </c>
       <c r="F403" s="9" t="n">
         <f aca="false">F401+F402</f>
-        <v>7515.13295891378</v>
+        <v>7475.65931319757</v>
       </c>
       <c r="G403" s="9" t="n">
         <f aca="false">G401+G402</f>
-        <v>8526.24066455651</v>
+        <v>8485.26232869644</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57782,15 +57782,15 @@
       </c>
       <c r="E404" s="9" t="n">
         <f aca="false">t_inc*E403-t_fix+0*E403</f>
-        <v>2516.09535496834</v>
+        <v>2499.05907627273</v>
       </c>
       <c r="F404" s="9" t="n">
         <f aca="false">t_inc*F403-t_fix+0*F403</f>
-        <v>2997.70702933587</v>
+        <v>2978.65482821597</v>
       </c>
       <c r="G404" s="9" t="n">
         <f aca="false">t_inc*G403-t_fix+0*G403</f>
-        <v>3485.72446507711</v>
+        <v>3465.94601588148</v>
       </c>
       <c r="H404" s="4" t="s">
         <v>500</v>
@@ -57813,15 +57813,15 @@
       </c>
       <c r="E405" s="11" t="n">
         <f aca="false">E404/E403</f>
-        <v>0.386064237811609</v>
+        <v>0.385538258200117</v>
       </c>
       <c r="F405" s="11" t="n">
         <f aca="false">F404/F403</f>
-        <v>0.398889420283677</v>
+        <v>0.398447107261488</v>
       </c>
       <c r="G405" s="11" t="n">
         <f aca="false">G404/G403</f>
-        <v>0.408823138146597</v>
+        <v>0.408466571995063</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57925,15 +57925,15 @@
       </c>
       <c r="E409" s="9" t="n">
         <f aca="false">E403+E406</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="F409" s="9" t="n">
         <f aca="false">F403+F406</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G409" s="9" t="n">
         <f aca="false">G403+G406</f>
-        <v>9060.66378455651</v>
+        <v>9019.68544869644</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57972,15 +57972,15 @@
       </c>
       <c r="E411" s="9" t="n">
         <f aca="false">E404+E407+E408</f>
-        <v>2483.61175496834</v>
+        <v>2466.57547627273</v>
       </c>
       <c r="F411" s="9" t="n">
         <f aca="false">F404+F407+F408</f>
-        <v>2972.73185333587</v>
+        <v>2953.67965221597</v>
       </c>
       <c r="G411" s="9" t="n">
         <f aca="false">G404+G407+G408</f>
-        <v>3464.63600267711</v>
+        <v>3444.85755348148</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58000,15 +58000,15 @@
       </c>
       <c r="E412" s="11" t="n">
         <f aca="false">E411/E409</f>
-        <v>0.356893629377223</v>
+        <v>0.356252490908414</v>
       </c>
       <c r="F412" s="11" t="n">
         <f aca="false">F411/F409</f>
-        <v>0.371546331407239</v>
+        <v>0.370995441036601</v>
       </c>
       <c r="G412" s="11" t="n">
         <f aca="false">G411/G409</f>
-        <v>0.382382139439103</v>
+        <v>0.381926573057971</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58028,15 +58028,15 @@
       </c>
       <c r="E413" s="9" t="n">
         <f aca="false">E411*etr</f>
-        <v>352.070334560013</v>
+        <v>349.655316058017</v>
       </c>
       <c r="F413" s="9" t="n">
         <f aca="false">F411*etr</f>
-        <v>421.406725937527</v>
+        <v>418.705935522533</v>
       </c>
       <c r="G413" s="9" t="n">
         <f aca="false">G411*etr</f>
-        <v>491.137777130848</v>
+        <v>488.334035679932</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58084,15 +58084,15 @@
       </c>
       <c r="E415" s="9" t="n">
         <f aca="false">E411-E413+E414</f>
-        <v>2118.34142040833</v>
+        <v>2103.72016021471</v>
       </c>
       <c r="F415" s="9" t="n">
         <f aca="false">F411-F413+F414</f>
-        <v>2538.12512739834</v>
+        <v>2521.77371669344</v>
       </c>
       <c r="G415" s="9" t="n">
         <f aca="false">G411-G413+G414</f>
-        <v>2960.29822554627</v>
+        <v>2943.32351780155</v>
       </c>
       <c r="H415" s="8" t="s">
         <v>505</v>
@@ -58143,15 +58143,15 @@
       </c>
       <c r="E417" s="18" t="n">
         <f aca="false">E415/E416</f>
-        <v>13.5684134971038</v>
+        <v>13.474761311368</v>
       </c>
       <c r="F417" s="18" t="n">
         <f aca="false">F415/F416</f>
-        <v>16.4214289691322</v>
+        <v>16.3156368919264</v>
       </c>
       <c r="G417" s="18" t="n">
         <f aca="false">G415/G416</f>
-        <v>19.3463120137956</v>
+        <v>19.2353779229198</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58171,15 +58171,15 @@
       </c>
       <c r="E418" s="11" t="n">
         <f aca="false">E397/E409</f>
-        <v>0.654305138730523</v>
+        <v>0.657640790066815</v>
       </c>
       <c r="F418" s="11" t="n">
         <f aca="false">F397/F409</f>
-        <v>0.638679017979199</v>
+        <v>0.641845631555813</v>
       </c>
       <c r="G418" s="11" t="n">
         <f aca="false">G397/G409</f>
-        <v>0.627131376400865</v>
+        <v>0.629980566687679</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58199,15 +58199,15 @@
       </c>
       <c r="E419" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E418-D418)</f>
-        <v>0.600140940959489</v>
+        <v>0.601175024106483</v>
       </c>
       <c r="F419" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F418-D418)</f>
-        <v>0.595296697214342</v>
+        <v>0.596278377073082</v>
       </c>
       <c r="G419" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G418-D418)</f>
-        <v>0.591716820200892</v>
+        <v>0.592600095867661</v>
       </c>
       <c r="H419" s="8" t="s">
         <v>509</v>
@@ -58289,15 +58289,15 @@
       </c>
       <c r="E427" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F427" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G427" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="428" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58407,15 +58407,15 @@
       </c>
       <c r="E431" s="9" t="n">
         <f aca="false">E427*1000*E430</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F431" s="9" t="n">
         <f aca="false">F427*1000*F430</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G431" s="9" t="n">
         <f aca="false">G427*1000*G430</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="432" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58466,15 +58466,15 @@
       </c>
       <c r="E433" s="9" t="n">
         <f aca="false">E429+E431+E432</f>
-        <v>6091.59354523868</v>
+        <v>6056.29662467179</v>
       </c>
       <c r="F433" s="9" t="n">
         <f aca="false">F429+F431+F432</f>
-        <v>7055.37307091378</v>
+        <v>7015.89942519757</v>
       </c>
       <c r="G433" s="9" t="n">
         <f aca="false">G429+G431+G432</f>
-        <v>8029.69998551651</v>
+        <v>7988.72164965644</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58522,15 +58522,15 @@
       </c>
       <c r="E435" s="9" t="n">
         <f aca="false">E433+E434</f>
-        <v>6517.29714523868</v>
+        <v>6482.00022467179</v>
       </c>
       <c r="F435" s="9" t="n">
         <f aca="false">F433+F434</f>
-        <v>7515.13295891378</v>
+        <v>7475.65931319757</v>
       </c>
       <c r="G435" s="9" t="n">
         <f aca="false">G433+G434</f>
-        <v>8526.24066455651</v>
+        <v>8485.26232869644</v>
       </c>
     </row>
     <row r="436" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58550,15 +58550,15 @@
       </c>
       <c r="E436" s="9" t="n">
         <f aca="false">t_inc*E435-t_fix+0*E435</f>
-        <v>2516.09535496834</v>
+        <v>2499.05907627273</v>
       </c>
       <c r="F436" s="9" t="n">
         <f aca="false">t_inc*F435-t_fix+0*F435</f>
-        <v>2997.70702933587</v>
+        <v>2978.65482821597</v>
       </c>
       <c r="G436" s="9" t="n">
         <f aca="false">t_inc*G435-t_fix+0*G435</f>
-        <v>3485.72446507711</v>
+        <v>3465.94601588148</v>
       </c>
       <c r="H436" s="4" t="s">
         <v>500</v>
@@ -58581,15 +58581,15 @@
       </c>
       <c r="E437" s="11" t="n">
         <f aca="false">E436/E435</f>
-        <v>0.386064237811609</v>
+        <v>0.385538258200117</v>
       </c>
       <c r="F437" s="11" t="n">
         <f aca="false">F436/F435</f>
-        <v>0.398889420283677</v>
+        <v>0.398447107261488</v>
       </c>
       <c r="G437" s="11" t="n">
         <f aca="false">G436/G435</f>
-        <v>0.408823138146597</v>
+        <v>0.408466571995063</v>
       </c>
     </row>
     <row r="438" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58693,15 +58693,15 @@
       </c>
       <c r="E441" s="9" t="n">
         <f aca="false">E435+E438</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="F441" s="9" t="n">
         <f aca="false">F435+F438</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G441" s="9" t="n">
         <f aca="false">G435+G438</f>
-        <v>9060.66378455651</v>
+        <v>9019.68544869644</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58740,15 +58740,15 @@
       </c>
       <c r="E443" s="9" t="n">
         <f aca="false">E436+E439+E440</f>
-        <v>2536.61239496834</v>
+        <v>2519.57611627273</v>
       </c>
       <c r="F443" s="9" t="n">
         <f aca="false">F436+F439+F440</f>
-        <v>3031.03255733587</v>
+        <v>3011.98035621597</v>
       </c>
       <c r="G443" s="9" t="n">
         <f aca="false">G436+G439+G440</f>
-        <v>3528.76677707711</v>
+        <v>3508.98832788148</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58768,15 +58768,15 @@
       </c>
       <c r="E444" s="11" t="n">
         <f aca="false">E443/E441</f>
-        <v>0.364509791899838</v>
+        <v>0.363907480671092</v>
       </c>
       <c r="F444" s="11" t="n">
         <f aca="false">F443/F441</f>
-        <v>0.378833033928138</v>
+        <v>0.378318271519249</v>
       </c>
       <c r="G444" s="11" t="n">
         <f aca="false">G443/G441</f>
-        <v>0.389460072791989</v>
+        <v>0.389036662956867</v>
       </c>
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58796,15 +58796,15 @@
       </c>
       <c r="E445" s="9" t="n">
         <f aca="false">E443*etr</f>
-        <v>359.583567262091</v>
+        <v>357.168548760095</v>
       </c>
       <c r="F445" s="9" t="n">
         <f aca="false">F443*etr</f>
-        <v>429.671281909814</v>
+        <v>426.970491494819</v>
       </c>
       <c r="G445" s="9" t="n">
         <f aca="false">G443*etr</f>
-        <v>500.228788700363</v>
+        <v>497.425047249447</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58852,15 +58852,15 @@
       </c>
       <c r="E447" s="9" t="n">
         <f aca="false">E443-E445+E446</f>
-        <v>2163.82882770625</v>
+        <v>2149.20756751263</v>
       </c>
       <c r="F447" s="9" t="n">
         <f aca="false">F443-F445+F446</f>
-        <v>2588.16127542606</v>
+        <v>2571.80986472115</v>
       </c>
       <c r="G447" s="9" t="n">
         <f aca="false">G443-G445+G446</f>
-        <v>3015.33798837675</v>
+        <v>2998.36328063203</v>
       </c>
       <c r="H447" s="8" t="s">
         <v>505</v>
@@ -58911,15 +58911,15 @@
       </c>
       <c r="E449" s="18" t="n">
         <f aca="false">E447/E448</f>
-        <v>13.8597697181469</v>
+        <v>13.7661175324112</v>
       </c>
       <c r="F449" s="18" t="n">
         <f aca="false">F447/F448</f>
-        <v>16.7451581036246</v>
+        <v>16.6393660264188</v>
       </c>
       <c r="G449" s="18" t="n">
         <f aca="false">G447/G448</f>
-        <v>19.7060110521205</v>
+        <v>19.5950769612446</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58939,15 +58939,15 @@
       </c>
       <c r="E450" s="11" t="n">
         <f aca="false">E429/E441</f>
-        <v>0.654305138730523</v>
+        <v>0.657640790066815</v>
       </c>
       <c r="F450" s="11" t="n">
         <f aca="false">F429/F441</f>
-        <v>0.638679017979199</v>
+        <v>0.641845631555813</v>
       </c>
       <c r="G450" s="11" t="n">
         <f aca="false">G429/G441</f>
-        <v>0.627131376400865</v>
+        <v>0.629980566687679</v>
       </c>
     </row>
     <row r="451" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58967,15 +58967,15 @@
       </c>
       <c r="E451" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E450-D450)</f>
-        <v>0.600140940959489</v>
+        <v>0.601175024106483</v>
       </c>
       <c r="F451" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F450-D450)</f>
-        <v>0.595296697214342</v>
+        <v>0.596278377073082</v>
       </c>
       <c r="G451" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G450-D450)</f>
-        <v>0.591716820200892</v>
+        <v>0.592600095867661</v>
       </c>
       <c r="H451" s="8" t="s">
         <v>509</v>
@@ -59057,15 +59057,15 @@
       </c>
       <c r="E459" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F459" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G459" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59175,15 +59175,15 @@
       </c>
       <c r="E463" s="9" t="n">
         <f aca="false">E459*1000*E462</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F463" s="9" t="n">
         <f aca="false">F459*1000*F462</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G463" s="9" t="n">
         <f aca="false">G459*1000*G462</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="464" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59234,15 +59234,15 @@
       </c>
       <c r="E465" s="9" t="n">
         <f aca="false">E461+E463+E464</f>
-        <v>6091.59354523868</v>
+        <v>6056.29662467179</v>
       </c>
       <c r="F465" s="9" t="n">
         <f aca="false">F461+F463+F464</f>
-        <v>7055.37307091378</v>
+        <v>7015.89942519757</v>
       </c>
       <c r="G465" s="9" t="n">
         <f aca="false">G461+G463+G464</f>
-        <v>8029.69998551651</v>
+        <v>7988.72164965644</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59290,15 +59290,15 @@
       </c>
       <c r="E467" s="9" t="n">
         <f aca="false">E465+E466</f>
-        <v>6517.29714523868</v>
+        <v>6482.00022467179</v>
       </c>
       <c r="F467" s="9" t="n">
         <f aca="false">F465+F466</f>
-        <v>7515.13295891378</v>
+        <v>7475.65931319757</v>
       </c>
       <c r="G467" s="9" t="n">
         <f aca="false">G465+G466</f>
-        <v>8526.24066455651</v>
+        <v>8485.26232869644</v>
       </c>
     </row>
     <row r="468" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59318,15 +59318,15 @@
       </c>
       <c r="E468" s="9" t="n">
         <f aca="false">t_inc*E467-t_fix+0*E467</f>
-        <v>2516.09535496834</v>
+        <v>2499.05907627273</v>
       </c>
       <c r="F468" s="9" t="n">
         <f aca="false">t_inc*F467-t_fix+0*F467</f>
-        <v>2997.70702933587</v>
+        <v>2978.65482821597</v>
       </c>
       <c r="G468" s="9" t="n">
         <f aca="false">t_inc*G467-t_fix+0*G467</f>
-        <v>3485.72446507711</v>
+        <v>3465.94601588148</v>
       </c>
       <c r="H468" s="4" t="s">
         <v>500</v>
@@ -59349,15 +59349,15 @@
       </c>
       <c r="E469" s="11" t="n">
         <f aca="false">E468/E467</f>
-        <v>0.386064237811609</v>
+        <v>0.385538258200117</v>
       </c>
       <c r="F469" s="11" t="n">
         <f aca="false">F468/F467</f>
-        <v>0.398889420283677</v>
+        <v>0.398447107261488</v>
       </c>
       <c r="G469" s="11" t="n">
         <f aca="false">G468/G467</f>
-        <v>0.408823138146597</v>
+        <v>0.408466571995063</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59461,15 +59461,15 @@
       </c>
       <c r="E473" s="9" t="n">
         <f aca="false">E467+E470</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="F473" s="9" t="n">
         <f aca="false">F467+F470</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G473" s="9" t="n">
         <f aca="false">G467+G470</f>
-        <v>9060.66378455651</v>
+        <v>9019.68544869644</v>
       </c>
     </row>
     <row r="474" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59508,15 +59508,15 @@
       </c>
       <c r="E475" s="9" t="n">
         <f aca="false">E468+E471+E472</f>
-        <v>2514.52879496834</v>
+        <v>2497.49251627273</v>
       </c>
       <c r="F475" s="9" t="n">
         <f aca="false">F468+F471+F472</f>
-        <v>3006.74059733587</v>
+        <v>2987.68839621597</v>
       </c>
       <c r="G475" s="9" t="n">
         <f aca="false">G468+G471+G472</f>
-        <v>3502.04562107711</v>
+        <v>3482.26717188148</v>
       </c>
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59536,15 +59536,15 @@
       </c>
       <c r="E476" s="11" t="n">
         <f aca="false">E475/E473</f>
-        <v>0.361336390848749</v>
+        <v>0.36071790160331</v>
       </c>
       <c r="F476" s="11" t="n">
         <f aca="false">F475/F473</f>
-        <v>0.375796907877763</v>
+        <v>0.375267092151479</v>
       </c>
       <c r="G476" s="11" t="n">
         <f aca="false">G475/G473</f>
-        <v>0.386510933894953</v>
+        <v>0.386074125498994</v>
       </c>
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59564,15 +59564,15 @@
       </c>
       <c r="E477" s="9" t="n">
         <f aca="false">E475*etr_lo</f>
-        <v>301.743455396201</v>
+        <v>299.699101952727</v>
       </c>
       <c r="F477" s="9" t="n">
         <f aca="false">F475*etr_lo</f>
-        <v>360.808871680304</v>
+        <v>358.522607545917</v>
       </c>
       <c r="G477" s="9" t="n">
         <f aca="false">G475*etr_lo</f>
-        <v>420.245474529254</v>
+        <v>417.872060625777</v>
       </c>
     </row>
     <row r="478" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59620,15 +59620,15 @@
       </c>
       <c r="E479" s="9" t="n">
         <f aca="false">E475-E477+E478</f>
-        <v>2199.58533957214</v>
+        <v>2184.59341432</v>
       </c>
       <c r="F479" s="9" t="n">
         <f aca="false">F475-F477+F478</f>
-        <v>2632.73172565557</v>
+        <v>2615.96578867006</v>
       </c>
       <c r="G479" s="9" t="n">
         <f aca="false">G475-G477+G478</f>
-        <v>3068.60014654786</v>
+        <v>3051.1951112557</v>
       </c>
       <c r="H479" s="8" t="s">
         <v>505</v>
@@ -59679,15 +59679,15 @@
       </c>
       <c r="E481" s="18" t="n">
         <f aca="false">E479/E480</f>
-        <v>14.0887975479087</v>
+        <v>13.9927711760599</v>
       </c>
       <c r="F481" s="18" t="n">
         <f aca="false">F479/F480</f>
-        <v>17.0335246914911</v>
+        <v>16.9250506685454</v>
       </c>
       <c r="G481" s="18" t="n">
         <f aca="false">G479/G480</f>
-        <v>20.0540929857629</v>
+        <v>19.9403465934341</v>
       </c>
     </row>
     <row r="482" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59707,15 +59707,15 @@
       </c>
       <c r="E482" s="11" t="n">
         <f aca="false">E461/E473</f>
-        <v>0.654305138730523</v>
+        <v>0.657640790066815</v>
       </c>
       <c r="F482" s="11" t="n">
         <f aca="false">F461/F473</f>
-        <v>0.638679017979199</v>
+        <v>0.641845631555813</v>
       </c>
       <c r="G482" s="11" t="n">
         <f aca="false">G461/G473</f>
-        <v>0.627131376400865</v>
+        <v>0.629980566687679</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59735,15 +59735,15 @@
       </c>
       <c r="E483" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E482-D482)</f>
-        <v>0.600140940959489</v>
+        <v>0.601175024106483</v>
       </c>
       <c r="F483" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F482-D482)</f>
-        <v>0.595296697214342</v>
+        <v>0.596278377073082</v>
       </c>
       <c r="G483" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G482-D482)</f>
-        <v>0.591716820200892</v>
+        <v>0.592600095867661</v>
       </c>
       <c r="H483" s="8" t="s">
         <v>509</v>
@@ -59825,15 +59825,15 @@
       </c>
       <c r="E491" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F491" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G491" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59943,15 +59943,15 @@
       </c>
       <c r="E495" s="9" t="n">
         <f aca="false">E491*1000*E494</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F495" s="9" t="n">
         <f aca="false">F491*1000*F494</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G495" s="9" t="n">
         <f aca="false">G491*1000*G494</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60002,15 +60002,15 @@
       </c>
       <c r="E497" s="9" t="n">
         <f aca="false">E493+E495+E496</f>
-        <v>6091.59354523868</v>
+        <v>6056.29662467179</v>
       </c>
       <c r="F497" s="9" t="n">
         <f aca="false">F493+F495+F496</f>
-        <v>7055.37307091378</v>
+        <v>7015.89942519757</v>
       </c>
       <c r="G497" s="9" t="n">
         <f aca="false">G493+G495+G496</f>
-        <v>8029.69998551651</v>
+        <v>7988.72164965644</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60058,15 +60058,15 @@
       </c>
       <c r="E499" s="9" t="n">
         <f aca="false">E497+E498</f>
-        <v>6517.29714523868</v>
+        <v>6482.00022467179</v>
       </c>
       <c r="F499" s="9" t="n">
         <f aca="false">F497+F498</f>
-        <v>7515.13295891378</v>
+        <v>7475.65931319757</v>
       </c>
       <c r="G499" s="9" t="n">
         <f aca="false">G497+G498</f>
-        <v>8526.24066455651</v>
+        <v>8485.26232869644</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60086,15 +60086,15 @@
       </c>
       <c r="E500" s="9" t="n">
         <f aca="false">t_inc*E499-t_fix+0*E499</f>
-        <v>2516.09535496834</v>
+        <v>2499.05907627273</v>
       </c>
       <c r="F500" s="9" t="n">
         <f aca="false">t_inc*F499-t_fix+0*F499</f>
-        <v>2997.70702933587</v>
+        <v>2978.65482821597</v>
       </c>
       <c r="G500" s="9" t="n">
         <f aca="false">t_inc*G499-t_fix+0*G499</f>
-        <v>3485.72446507711</v>
+        <v>3465.94601588148</v>
       </c>
       <c r="H500" s="4" t="s">
         <v>500</v>
@@ -60117,15 +60117,15 @@
       </c>
       <c r="E501" s="11" t="n">
         <f aca="false">E500/E499</f>
-        <v>0.386064237811609</v>
+        <v>0.385538258200117</v>
       </c>
       <c r="F501" s="11" t="n">
         <f aca="false">F500/F499</f>
-        <v>0.398889420283677</v>
+        <v>0.398447107261488</v>
       </c>
       <c r="G501" s="11" t="n">
         <f aca="false">G500/G499</f>
-        <v>0.408823138146597</v>
+        <v>0.408466571995063</v>
       </c>
     </row>
     <row r="502" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60229,15 +60229,15 @@
       </c>
       <c r="E505" s="9" t="n">
         <f aca="false">E499+E502</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="F505" s="9" t="n">
         <f aca="false">F499+F502</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G505" s="9" t="n">
         <f aca="false">G499+G502</f>
-        <v>9060.66378455651</v>
+        <v>9019.68544869644</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60276,15 +60276,15 @@
       </c>
       <c r="E507" s="9" t="n">
         <f aca="false">E500+E503+E504</f>
-        <v>2514.52879496834</v>
+        <v>2497.49251627273</v>
       </c>
       <c r="F507" s="9" t="n">
         <f aca="false">F500+F503+F504</f>
-        <v>3006.74059733587</v>
+        <v>2987.68839621597</v>
       </c>
       <c r="G507" s="9" t="n">
         <f aca="false">G500+G503+G504</f>
-        <v>3502.04562107711</v>
+        <v>3482.26717188148</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60304,15 +60304,15 @@
       </c>
       <c r="E508" s="11" t="n">
         <f aca="false">E507/E505</f>
-        <v>0.361336390848749</v>
+        <v>0.36071790160331</v>
       </c>
       <c r="F508" s="11" t="n">
         <f aca="false">F507/F505</f>
-        <v>0.375796907877763</v>
+        <v>0.375267092151479</v>
       </c>
       <c r="G508" s="11" t="n">
         <f aca="false">G507/G505</f>
-        <v>0.386510933894953</v>
+        <v>0.386074125498994</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60332,15 +60332,15 @@
       </c>
       <c r="E509" s="9" t="n">
         <f aca="false">E507*etr_hi</f>
-        <v>427.469895144618</v>
+        <v>424.573727766364</v>
       </c>
       <c r="F509" s="9" t="n">
         <f aca="false">F507*etr_hi</f>
-        <v>511.145901547098</v>
+        <v>507.907027356715</v>
       </c>
       <c r="G509" s="9" t="n">
         <f aca="false">G507*etr_hi</f>
-        <v>595.34775558311</v>
+        <v>591.985419219851</v>
       </c>
     </row>
     <row r="510" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60388,15 +60388,15 @@
       </c>
       <c r="E511" s="9" t="n">
         <f aca="false">E507-E509+E510</f>
-        <v>2073.85889982372</v>
+        <v>2059.71878850637</v>
       </c>
       <c r="F511" s="9" t="n">
         <f aca="false">F507-F509+F510</f>
-        <v>2482.39469578877</v>
+        <v>2466.58136885926</v>
       </c>
       <c r="G511" s="9" t="n">
         <f aca="false">G507-G509+G510</f>
-        <v>2893.497865494</v>
+        <v>2877.08175266163</v>
       </c>
       <c r="H511" s="8" t="s">
         <v>505</v>
@@ -60447,15 +60447,15 @@
       </c>
       <c r="E513" s="18" t="n">
         <f aca="false">E511/E512</f>
-        <v>13.2834937826184</v>
+        <v>13.1929234546247</v>
       </c>
       <c r="F513" s="18" t="n">
         <f aca="false">F511/F512</f>
-        <v>16.0608583596628</v>
+        <v>15.9585476334753</v>
       </c>
       <c r="G513" s="18" t="n">
         <f aca="false">G511/G512</f>
-        <v>18.9097544409631</v>
+        <v>18.8024709118348</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60475,15 +60475,15 @@
       </c>
       <c r="E514" s="11" t="n">
         <f aca="false">E493/E505</f>
-        <v>0.654305138730523</v>
+        <v>0.657640790066815</v>
       </c>
       <c r="F514" s="11" t="n">
         <f aca="false">F493/F505</f>
-        <v>0.638679017979199</v>
+        <v>0.641845631555813</v>
       </c>
       <c r="G514" s="11" t="n">
         <f aca="false">G493/G505</f>
-        <v>0.627131376400865</v>
+        <v>0.629980566687679</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60503,15 +60503,15 @@
       </c>
       <c r="E515" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E514-D514)</f>
-        <v>0.600140940959489</v>
+        <v>0.601175024106483</v>
       </c>
       <c r="F515" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F514-D514)</f>
-        <v>0.595296697214342</v>
+        <v>0.596278377073082</v>
       </c>
       <c r="G515" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G514-D514)</f>
-        <v>0.591716820200892</v>
+        <v>0.592600095867661</v>
       </c>
       <c r="H515" s="8" t="s">
         <v>509</v>
@@ -60593,15 +60593,15 @@
       </c>
       <c r="E523" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F523" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G523" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60711,15 +60711,15 @@
       </c>
       <c r="E527" s="9" t="n">
         <f aca="false">E523*1000*E526</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F527" s="9" t="n">
         <f aca="false">F523*1000*F526</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G527" s="9" t="n">
         <f aca="false">G523*1000*G526</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60770,15 +60770,15 @@
       </c>
       <c r="E529" s="9" t="n">
         <f aca="false">E525+E527+E528</f>
-        <v>6091.59354523868</v>
+        <v>6056.29662467179</v>
       </c>
       <c r="F529" s="9" t="n">
         <f aca="false">F525+F527+F528</f>
-        <v>7055.37307091378</v>
+        <v>7015.89942519757</v>
       </c>
       <c r="G529" s="9" t="n">
         <f aca="false">G525+G527+G528</f>
-        <v>8029.69998551651</v>
+        <v>7988.72164965644</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60826,15 +60826,15 @@
       </c>
       <c r="E531" s="9" t="n">
         <f aca="false">E529+E530</f>
-        <v>6517.29714523868</v>
+        <v>6482.00022467179</v>
       </c>
       <c r="F531" s="9" t="n">
         <f aca="false">F529+F530</f>
-        <v>7515.13295891378</v>
+        <v>7475.65931319757</v>
       </c>
       <c r="G531" s="9" t="n">
         <f aca="false">G529+G530</f>
-        <v>8526.24066455651</v>
+        <v>8485.26232869644</v>
       </c>
     </row>
     <row r="532" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60854,15 +60854,15 @@
       </c>
       <c r="E532" s="9" t="n">
         <f aca="false">t_inc*E531-t_fix+0*E531</f>
-        <v>2516.09535496834</v>
+        <v>2499.05907627273</v>
       </c>
       <c r="F532" s="9" t="n">
         <f aca="false">t_inc*F531-t_fix+0*F531</f>
-        <v>2997.70702933587</v>
+        <v>2978.65482821597</v>
       </c>
       <c r="G532" s="9" t="n">
         <f aca="false">t_inc*G531-t_fix+0*G531</f>
-        <v>3485.72446507711</v>
+        <v>3465.94601588148</v>
       </c>
       <c r="H532" s="4" t="s">
         <v>500</v>
@@ -60885,15 +60885,15 @@
       </c>
       <c r="E533" s="11" t="n">
         <f aca="false">E532/E531</f>
-        <v>0.386064237811609</v>
+        <v>0.385538258200117</v>
       </c>
       <c r="F533" s="11" t="n">
         <f aca="false">F532/F531</f>
-        <v>0.398889420283677</v>
+        <v>0.398447107261488</v>
       </c>
       <c r="G533" s="11" t="n">
         <f aca="false">G532/G531</f>
-        <v>0.408823138146597</v>
+        <v>0.408466571995063</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60997,15 +60997,15 @@
       </c>
       <c r="E537" s="9" t="n">
         <f aca="false">E531+E534</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="F537" s="9" t="n">
         <f aca="false">F531+F534</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G537" s="9" t="n">
         <f aca="false">G531+G534</f>
-        <v>9060.66378455651</v>
+        <v>9019.68544869644</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61044,15 +61044,15 @@
       </c>
       <c r="E539" s="9" t="n">
         <f aca="false">E532+E535+E536</f>
-        <v>2514.52879496834</v>
+        <v>2497.49251627273</v>
       </c>
       <c r="F539" s="9" t="n">
         <f aca="false">F532+F535+F536</f>
-        <v>3006.74059733587</v>
+        <v>2987.68839621597</v>
       </c>
       <c r="G539" s="9" t="n">
         <f aca="false">G532+G535+G536</f>
-        <v>3502.04562107711</v>
+        <v>3482.26717188148</v>
       </c>
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61072,15 +61072,15 @@
       </c>
       <c r="E540" s="11" t="n">
         <f aca="false">E539/E537</f>
-        <v>0.361336390848749</v>
+        <v>0.36071790160331</v>
       </c>
       <c r="F540" s="11" t="n">
         <f aca="false">F539/F537</f>
-        <v>0.375796907877763</v>
+        <v>0.375267092151479</v>
       </c>
       <c r="G540" s="11" t="n">
         <f aca="false">G539/G537</f>
-        <v>0.386510933894953</v>
+        <v>0.386074125498994</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61100,15 +61100,15 @@
       </c>
       <c r="E541" s="9" t="n">
         <f aca="false">E539*etr</f>
-        <v>356.453053636225</v>
+        <v>354.038035134229</v>
       </c>
       <c r="F541" s="9" t="n">
         <f aca="false">F539*etr</f>
-        <v>426.227716921361</v>
+        <v>423.526926506366</v>
       </c>
       <c r="G541" s="9" t="n">
         <f aca="false">G539*etr</f>
-        <v>496.440867213065</v>
+        <v>493.63712576215</v>
       </c>
     </row>
     <row r="542" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61156,15 +61156,15 @@
       </c>
       <c r="E543" s="9" t="n">
         <f aca="false">E539-E541+E542</f>
-        <v>2144.87574133212</v>
+        <v>2130.2544811385</v>
       </c>
       <c r="F543" s="9" t="n">
         <f aca="false">F539-F541+F542</f>
-        <v>2567.31288041451</v>
+        <v>2550.96146970961</v>
       </c>
       <c r="G543" s="9" t="n">
         <f aca="false">G539-G541+G542</f>
-        <v>2992.40475386405</v>
+        <v>2975.43004611933</v>
       </c>
       <c r="H543" s="8" t="s">
         <v>505</v>
@@ -61215,15 +61215,15 @@
       </c>
       <c r="E545" s="18" t="n">
         <f aca="false">E543/E544</f>
-        <v>13.6009875797852</v>
+        <v>13.5082719159068</v>
       </c>
       <c r="F545" s="18" t="n">
         <f aca="false">F543/F544</f>
-        <v>16.2797265720641</v>
+        <v>16.1760397571947</v>
       </c>
       <c r="G545" s="18" t="n">
         <f aca="false">G543/G544</f>
-        <v>18.9752996440333</v>
+        <v>18.8676604065905</v>
       </c>
     </row>
     <row r="546" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61243,15 +61243,15 @@
       </c>
       <c r="E546" s="11" t="n">
         <f aca="false">E525/E537</f>
-        <v>0.654305138730523</v>
+        <v>0.657640790066815</v>
       </c>
       <c r="F546" s="11" t="n">
         <f aca="false">F525/F537</f>
-        <v>0.638679017979199</v>
+        <v>0.641845631555813</v>
       </c>
       <c r="G546" s="11" t="n">
         <f aca="false">G525/G537</f>
-        <v>0.627131376400865</v>
+        <v>0.629980566687679</v>
       </c>
     </row>
     <row r="547" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61271,15 +61271,15 @@
       </c>
       <c r="E547" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E546-D546)</f>
-        <v>0.600140940959489</v>
+        <v>0.601175024106483</v>
       </c>
       <c r="F547" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F546-D546)</f>
-        <v>0.595296697214342</v>
+        <v>0.596278377073082</v>
       </c>
       <c r="G547" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G546-D546)</f>
-        <v>0.591716820200892</v>
+        <v>0.592600095867661</v>
       </c>
       <c r="H547" s="8" t="s">
         <v>509</v>
@@ -61361,15 +61361,15 @@
       </c>
       <c r="E555" s="18" t="n">
         <f aca="false">mm_A_2027</f>
-        <v>3.99150647980462</v>
+        <v>3.88007408374579</v>
       </c>
       <c r="F555" s="18" t="n">
         <f aca="false">mm_A_2028</f>
-        <v>5.17069526557172</v>
+        <v>5.04607694610671</v>
       </c>
       <c r="G555" s="18" t="n">
         <f aca="false">mm_A_2029</f>
-        <v>6.33160644779016</v>
+        <v>6.20223782078096</v>
       </c>
     </row>
     <row r="556" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61479,15 +61479,15 @@
       </c>
       <c r="E559" s="9" t="n">
         <f aca="false">E555*1000*E558</f>
-        <v>1264.33507797389</v>
+        <v>1229.03815740701</v>
       </c>
       <c r="F559" s="9" t="n">
         <f aca="false">F555*1000*F558</f>
-        <v>1637.85062979426</v>
+        <v>1598.37698407805</v>
       </c>
       <c r="G559" s="9" t="n">
         <f aca="false">G555*1000*G558</f>
-        <v>2005.57663437856</v>
+        <v>1964.5982985185</v>
       </c>
     </row>
     <row r="560" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61538,15 +61538,15 @@
       </c>
       <c r="E561" s="9" t="n">
         <f aca="false">E557+E559+E560</f>
-        <v>6091.59354523868</v>
+        <v>6056.29662467179</v>
       </c>
       <c r="F561" s="9" t="n">
         <f aca="false">F557+F559+F560</f>
-        <v>7055.37307091378</v>
+        <v>7015.89942519757</v>
       </c>
       <c r="G561" s="9" t="n">
         <f aca="false">G557+G559+G560</f>
-        <v>8029.69998551651</v>
+        <v>7988.72164965644</v>
       </c>
     </row>
     <row r="562" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61594,15 +61594,15 @@
       </c>
       <c r="E563" s="9" t="n">
         <f aca="false">E561+E562</f>
-        <v>6517.29714523868</v>
+        <v>6482.00022467179</v>
       </c>
       <c r="F563" s="9" t="n">
         <f aca="false">F561+F562</f>
-        <v>7515.13295891378</v>
+        <v>7475.65931319757</v>
       </c>
       <c r="G563" s="9" t="n">
         <f aca="false">G561+G562</f>
-        <v>8526.24066455651</v>
+        <v>8485.26232869644</v>
       </c>
     </row>
     <row r="564" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61622,15 +61622,15 @@
       </c>
       <c r="E564" s="9" t="n">
         <f aca="false">t_inc*E563-t_fix+0*E563</f>
-        <v>2516.09535496834</v>
+        <v>2499.05907627273</v>
       </c>
       <c r="F564" s="9" t="n">
         <f aca="false">t_inc*F563-t_fix+0*F563</f>
-        <v>2997.70702933587</v>
+        <v>2978.65482821597</v>
       </c>
       <c r="G564" s="9" t="n">
         <f aca="false">t_inc*G563-t_fix+0*G563</f>
-        <v>3485.72446507711</v>
+        <v>3465.94601588148</v>
       </c>
       <c r="H564" s="4" t="s">
         <v>500</v>
@@ -61653,15 +61653,15 @@
       </c>
       <c r="E565" s="11" t="n">
         <f aca="false">E564/E563</f>
-        <v>0.386064237811609</v>
+        <v>0.385538258200117</v>
       </c>
       <c r="F565" s="11" t="n">
         <f aca="false">F564/F563</f>
-        <v>0.398889420283677</v>
+        <v>0.398447107261488</v>
       </c>
       <c r="G565" s="11" t="n">
         <f aca="false">G564/G563</f>
-        <v>0.408823138146597</v>
+        <v>0.408466571995063</v>
       </c>
     </row>
     <row r="566" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61765,15 +61765,15 @@
       </c>
       <c r="E569" s="9" t="n">
         <f aca="false">E563+E566</f>
-        <v>6958.96914523867</v>
+        <v>6923.67222467179</v>
       </c>
       <c r="F569" s="9" t="n">
         <f aca="false">F563+F566</f>
-        <v>8000.97215891378</v>
+        <v>7961.49851319757</v>
       </c>
       <c r="G569" s="9" t="n">
         <f aca="false">G563+G566</f>
-        <v>9060.66378455651</v>
+        <v>9019.68544869644</v>
       </c>
     </row>
     <row r="570" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61812,15 +61812,15 @@
       </c>
       <c r="E571" s="9" t="n">
         <f aca="false">E564+E567+E568</f>
-        <v>2514.52879496834</v>
+        <v>2497.49251627273</v>
       </c>
       <c r="F571" s="9" t="n">
         <f aca="false">F564+F567+F568</f>
-        <v>3006.74059733587</v>
+        <v>2987.68839621597</v>
       </c>
       <c r="G571" s="9" t="n">
         <f aca="false">G564+G567+G568</f>
-        <v>3502.04562107711</v>
+        <v>3482.26717188148</v>
       </c>
     </row>
     <row r="572" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61840,15 +61840,15 @@
       </c>
       <c r="E572" s="11" t="n">
         <f aca="false">E571/E569</f>
-        <v>0.361336390848749</v>
+        <v>0.36071790160331</v>
       </c>
       <c r="F572" s="11" t="n">
         <f aca="false">F571/F569</f>
-        <v>0.375796907877763</v>
+        <v>0.375267092151479</v>
       </c>
       <c r="G572" s="11" t="n">
         <f aca="false">G571/G569</f>
-        <v>0.386510933894953</v>
+        <v>0.386074125498994</v>
       </c>
     </row>
     <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61868,15 +61868,15 @@
       </c>
       <c r="E573" s="9" t="n">
         <f aca="false">E571*etr</f>
-        <v>356.453053636225</v>
+        <v>354.038035134229</v>
       </c>
       <c r="F573" s="9" t="n">
         <f aca="false">F571*etr</f>
-        <v>426.227716921361</v>
+        <v>423.526926506366</v>
       </c>
       <c r="G573" s="9" t="n">
         <f aca="false">G571*etr</f>
-        <v>496.440867213065</v>
+        <v>493.63712576215</v>
       </c>
     </row>
     <row r="574" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61924,15 +61924,15 @@
       </c>
       <c r="E575" s="9" t="n">
         <f aca="false">E571-E573+E574</f>
-        <v>2144.87574133212</v>
+        <v>2130.2544811385</v>
       </c>
       <c r="F575" s="9" t="n">
         <f aca="false">F571-F573+F574</f>
-        <v>2567.31288041451</v>
+        <v>2550.96146970961</v>
       </c>
       <c r="G575" s="9" t="n">
         <f aca="false">G571-G573+G574</f>
-        <v>2992.40475386405</v>
+        <v>2975.43004611933</v>
       </c>
       <c r="H575" s="8" t="s">
         <v>505</v>
@@ -61983,15 +61983,15 @@
       </c>
       <c r="E577" s="18" t="n">
         <f aca="false">E575/E576</f>
-        <v>13.8785587548828</v>
+        <v>13.7839509345988</v>
       </c>
       <c r="F577" s="18" t="n">
         <f aca="false">F575/F576</f>
-        <v>16.9509856018993</v>
+        <v>16.8430234872915</v>
       </c>
       <c r="G577" s="18" t="n">
         <f aca="false">G575/G576</f>
-        <v>20.1609232165523</v>
+        <v>20.0465584137886</v>
       </c>
     </row>
     <row r="578" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62011,15 +62011,15 @@
       </c>
       <c r="E578" s="11" t="n">
         <f aca="false">E557/E569</f>
-        <v>0.654305138730523</v>
+        <v>0.657640790066815</v>
       </c>
       <c r="F578" s="11" t="n">
         <f aca="false">F557/F569</f>
-        <v>0.638679017979199</v>
+        <v>0.641845631555813</v>
       </c>
       <c r="G578" s="11" t="n">
         <f aca="false">G557/G569</f>
-        <v>0.627131376400865</v>
+        <v>0.629980566687679</v>
       </c>
     </row>
     <row r="579" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62039,15 +62039,15 @@
       </c>
       <c r="E579" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(E578-D578)</f>
-        <v>0.600140940959489</v>
+        <v>0.601175024106483</v>
       </c>
       <c r="F579" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(F578-D578)</f>
-        <v>0.595296697214342</v>
+        <v>0.596278377073082</v>
       </c>
       <c r="G579" s="11" t="n">
         <f aca="false">f26_gm+(Q!J13-a25_gp/a25_rev)/(Q!J4/Q!J10-a25_soc/a25_rev)*(G578-D578)</f>
-        <v>0.591716820200892</v>
+        <v>0.592600095867661</v>
       </c>
       <c r="H579" s="8" t="s">
         <v>509</v>
@@ -62087,15 +62087,15 @@
       </c>
       <c r="C584" s="14" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B95*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B96*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B97*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B100*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C95*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C96*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C97*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C100*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D95*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D96*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D97*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D100*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>219.296780421947</v>
+        <v>218.286112877241</v>
       </c>
       <c r="D584" s="14" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>493.436352755451</v>
+        <v>490.217794593997</v>
       </c>
       <c r="E584" s="14" t="n">
         <f aca="false">tp_w_dcf*C584+(1-tp_w_dcf)*D584</f>
-        <v>356.366566588699</v>
+        <v>354.251953735619</v>
       </c>
       <c r="F584" s="11" t="n">
         <f aca="false">E584/E$584-1</f>
@@ -62111,19 +62111,19 @@
       </c>
       <c r="C585" s="14" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B95*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!B96*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!B97*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!B98*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B99*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B100*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B100*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*MAX(0,Val!C95*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!C96*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!C97*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!C98*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C99*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C100*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C100*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*MAX(0,Val!D95*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!D96*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!D97*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!D98*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D99*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D100*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D100*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
-        <v>189.708988648371</v>
+        <v>188.826183557931</v>
       </c>
       <c r="D585" s="14" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>493.436352755451</v>
+        <v>490.217794593997</v>
       </c>
       <c r="E585" s="14" t="n">
         <f aca="false">tp_w_dcf*C585+(1-tp_w_dcf)*D585</f>
-        <v>341.572670701911</v>
+        <v>339.521989075964</v>
       </c>
       <c r="F585" s="11" t="n">
         <f aca="false">E585/E$584-1</f>
-        <v>-0.0415131420110536</v>
+        <v>-0.0415804754337306</v>
       </c>
     </row>
     <row r="586" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62135,19 +62135,19 @@
       </c>
       <c r="C586" s="14" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B95*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!B96*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!B97*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!B98*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B99*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B100*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B100*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*MAX(0,Val!C95*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!C96*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!C97*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!C98*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C99*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C100*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C100*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*MAX(0,Val!D95*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!D96*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!D97*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!D98*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D99*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D100*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D100*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
-        <v>260.698855705457</v>
+        <v>259.509481325414</v>
       </c>
       <c r="D586" s="14" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>493.436352755451</v>
+        <v>490.217794593997</v>
       </c>
       <c r="E586" s="14" t="n">
         <f aca="false">tp_w_dcf*C586+(1-tp_w_dcf)*D586</f>
-        <v>377.067604230454</v>
+        <v>374.863637959706</v>
       </c>
       <c r="F586" s="11" t="n">
         <f aca="false">E586/E$584-1</f>
-        <v>0.0580891688014242</v>
+        <v>0.0581836853875732</v>
       </c>
     </row>
     <row r="587" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62159,19 +62159,19 @@
       </c>
       <c r="C587" s="14" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B95*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B96*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B97*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B98*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B99*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B100*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B100*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*MAX(0,Val!C95*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C96*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C97*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C98*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C99*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C100*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C100*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*MAX(0,Val!D95*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D96*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D97*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D98*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D99*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D100*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D100*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>235.895749830529</v>
+        <v>234.818043724302</v>
       </c>
       <c r="D587" s="14" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>493.436352755451</v>
+        <v>490.217794593997</v>
       </c>
       <c r="E587" s="14" t="n">
         <f aca="false">tp_w_dcf*C587+(1-tp_w_dcf)*D587</f>
-        <v>364.66605129299</v>
+        <v>362.517919159149</v>
       </c>
       <c r="F587" s="11" t="n">
         <f aca="false">E587/E$584-1</f>
-        <v>0.0232891788467626</v>
+        <v>0.0233335775183876</v>
       </c>
     </row>
     <row r="588" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62183,19 +62183,19 @@
       </c>
       <c r="C588" s="14" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B95*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B96*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B97*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B98*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B99*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B100*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B100*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*MAX(0,Val!C95*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C96*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C97*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C98*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C99*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C100*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C100*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*MAX(0,Val!D95*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D96*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D97*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D98*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D99*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D100*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D100*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>208.447666252015</v>
+        <v>207.479299532946</v>
       </c>
       <c r="D588" s="14" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>493.436352755451</v>
+        <v>490.217794593997</v>
       </c>
       <c r="E588" s="14" t="n">
         <f aca="false">tp_w_dcf*C588+(1-tp_w_dcf)*D588</f>
-        <v>350.942009503733</v>
+        <v>348.848547063472</v>
       </c>
       <c r="F588" s="11" t="n">
         <f aca="false">E588/E$584-1</f>
-        <v>-0.015221846249193</v>
+        <v>-0.0152530045781486</v>
       </c>
     </row>
     <row r="589" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62207,19 +62207,19 @@
       </c>
       <c r="C589" s="14" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B95*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B96*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B97*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B100*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C95*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C96*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C97*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C100*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D95*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D96*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D97*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D100*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>219.296780421947</v>
+        <v>218.286112877241</v>
       </c>
       <c r="D589" s="14" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>493.436352755451</v>
+        <v>490.217794593997</v>
       </c>
       <c r="E589" s="14" t="n">
         <f aca="false">0.3*C589+(1-0.3)*D589</f>
-        <v>411.1944810554</v>
+        <v>408.63829007897</v>
       </c>
       <c r="F589" s="11" t="n">
         <f aca="false">E589/E$584-1</f>
-        <v>0.153852576552111</v>
+        <v>0.153524449956711</v>
       </c>
     </row>
     <row r="590" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62231,19 +62231,19 @@
       </c>
       <c r="C590" s="14" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B95*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B96*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B97*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B100*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C95*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C96*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C97*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C100*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D95*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D96*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D97*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D98*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D99*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D100*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D100*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>219.296780421947</v>
+        <v>218.286112877241</v>
       </c>
       <c r="D590" s="14" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>493.436352755451</v>
+        <v>490.217794593997</v>
       </c>
       <c r="E590" s="14" t="n">
         <f aca="false">0.7*C590+(1-0.7)*D590</f>
-        <v>301.538652121998</v>
+        <v>299.865617392268</v>
       </c>
       <c r="F590" s="11" t="n">
         <f aca="false">E590/E$584-1</f>
-        <v>-0.153852576552111</v>
+        <v>-0.153524449956711</v>
       </c>
     </row>
   </sheetData>
